--- a/reports/latest/load_testing/Load_Test_Report_Cognify_Latest.xlsx
+++ b/reports/latest/load_testing/Load_Test_Report_Cognify_Latest.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E610"/>
+  <dimension ref="A1:E623"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>0.26</v>
+        <v>1.49</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T13:49:57.025Z</v>
+        <v>2026-07-30T13:59:18.534Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T13:49:58.025Z</v>
+        <v>2026-07-30T13:59:19.534Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>1.59</v>
+        <v>0.23</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T13:49:59.025Z</v>
+        <v>2026-07-30T13:59:20.534Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T13:50:00.025Z</v>
+        <v>2026-07-30T13:59:21.534Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T13:50:01.025Z</v>
+        <v>2026-07-30T13:59:22.534Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>0.36</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T13:50:02.025Z</v>
+        <v>2026-07-30T13:59:23.534Z</v>
       </c>
     </row>
     <row r="8">
@@ -529,10 +529,10 @@
         <v>Passed</v>
       </c>
       <c r="D8">
-        <v>0.24</v>
+        <v>1.52</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T13:50:03.025Z</v>
+        <v>2026-07-30T13:59:24.534Z</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>Passed</v>
       </c>
       <c r="D9">
-        <v>1.38</v>
+        <v>0.95</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T13:50:04.025Z</v>
+        <v>2026-07-30T13:59:25.534Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>0.41</v>
+        <v>1.89</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T13:50:05.025Z</v>
+        <v>2026-07-30T13:59:26.534Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T13:50:06.025Z</v>
+        <v>2026-07-30T13:59:27.534Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T13:50:07.025Z</v>
+        <v>2026-07-30T13:59:28.534Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T13:50:08.025Z</v>
+        <v>2026-07-30T13:59:29.534Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>0.61</v>
+        <v>1.94</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T13:50:09.025Z</v>
+        <v>2026-07-30T13:59:30.534Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T13:50:10.025Z</v>
+        <v>2026-07-30T13:59:31.534Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>1.03</v>
+        <v>0.27</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T13:50:11.025Z</v>
+        <v>2026-07-30T13:59:32.534Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T13:50:12.025Z</v>
+        <v>2026-07-30T13:59:33.534Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>0.81</v>
+        <v>0.94</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T13:50:13.025Z</v>
+        <v>2026-07-30T13:59:34.534Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>1.35</v>
+        <v>0.37</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T13:50:14.025Z</v>
+        <v>2026-07-30T13:59:35.534Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>1.15</v>
+        <v>0.65</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T13:50:15.025Z</v>
+        <v>2026-07-30T13:59:36.534Z</v>
       </c>
     </row>
     <row r="21">
@@ -747,13 +747,13 @@
         <v>Verify APILoad functionality module 20</v>
       </c>
       <c r="C21" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D21">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T13:50:16.025Z</v>
+        <v>2026-07-30T13:59:37.534Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>0.17</v>
+        <v>1.13</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T13:50:17.025Z</v>
+        <v>2026-07-30T13:59:38.534Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T13:50:18.025Z</v>
+        <v>2026-07-30T13:59:39.534Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T13:50:19.025Z</v>
+        <v>2026-07-30T13:59:40.534Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>1.34</v>
+        <v>0.06</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T13:50:20.025Z</v>
+        <v>2026-07-30T13:59:41.534Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>0.65</v>
+        <v>1.26</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T13:50:21.025Z</v>
+        <v>2026-07-30T13:59:42.534Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>0.44</v>
+        <v>1.79</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T13:50:22.025Z</v>
+        <v>2026-07-30T13:59:43.534Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T13:50:23.025Z</v>
+        <v>2026-07-30T13:59:44.534Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T13:50:24.025Z</v>
+        <v>2026-07-30T13:59:45.534Z</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         <v>Passed</v>
       </c>
       <c r="D30">
-        <v>1.14</v>
+        <v>0.94</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T13:50:25.025Z</v>
+        <v>2026-07-30T13:59:46.534Z</v>
       </c>
     </row>
     <row r="31">
@@ -920,10 +920,10 @@
         <v>Passed</v>
       </c>
       <c r="D31">
-        <v>0.65</v>
+        <v>1.19</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T13:50:26.025Z</v>
+        <v>2026-07-30T13:59:47.534Z</v>
       </c>
     </row>
     <row r="32">
@@ -937,10 +937,10 @@
         <v>Passed</v>
       </c>
       <c r="D32">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T13:50:27.025Z</v>
+        <v>2026-07-30T13:59:48.534Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T13:50:28.025Z</v>
+        <v>2026-07-30T13:59:49.534Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>1.48</v>
+        <v>0.96</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T13:50:29.025Z</v>
+        <v>2026-07-30T13:59:50.534Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T13:50:30.025Z</v>
+        <v>2026-07-30T13:59:51.534Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>0.36</v>
+        <v>1.62</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T13:50:31.025Z</v>
+        <v>2026-07-30T13:59:52.534Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>0.49</v>
+        <v>1.09</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T13:50:32.025Z</v>
+        <v>2026-07-30T13:59:53.534Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T13:50:33.025Z</v>
+        <v>2026-07-30T13:59:54.534Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T13:50:34.025Z</v>
+        <v>2026-07-30T13:59:55.534Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>1.37</v>
+        <v>0.72</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T13:50:35.025Z</v>
+        <v>2026-07-30T13:59:56.534Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>1.97</v>
+        <v>0.91</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T13:50:36.025Z</v>
+        <v>2026-07-30T13:59:57.534Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T13:50:37.025Z</v>
+        <v>2026-07-30T13:59:58.534Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>0.83</v>
+        <v>1.82</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T13:50:38.025Z</v>
+        <v>2026-07-30T13:59:59.534Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T13:50:39.025Z</v>
+        <v>2026-07-30T14:00:00.534Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>0.2</v>
+        <v>0.99</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T13:50:40.025Z</v>
+        <v>2026-07-30T14:00:01.534Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>1.96</v>
+        <v>1.28</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T13:50:41.025Z</v>
+        <v>2026-07-30T14:00:02.534Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T13:50:42.025Z</v>
+        <v>2026-07-30T14:00:03.534Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>1.79</v>
+        <v>0.58</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T13:50:43.025Z</v>
+        <v>2026-07-30T14:00:04.534Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>0.45</v>
+        <v>1.92</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T13:50:44.025Z</v>
+        <v>2026-07-30T14:00:05.534Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T13:50:45.025Z</v>
+        <v>2026-07-30T14:00:06.534Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T13:50:46.025Z</v>
+        <v>2026-07-30T14:00:07.534Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>0.47</v>
+        <v>1.89</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T13:50:47.025Z</v>
+        <v>2026-07-30T14:00:08.534Z</v>
       </c>
     </row>
     <row r="53">
@@ -1294,10 +1294,10 @@
         <v>Passed</v>
       </c>
       <c r="D53">
-        <v>1.69</v>
+        <v>0.33</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T13:50:48.025Z</v>
+        <v>2026-07-30T14:00:09.534Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>0.22</v>
+        <v>1.64</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T13:50:49.025Z</v>
+        <v>2026-07-30T14:00:10.534Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>0.22</v>
+        <v>1.17</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T13:50:50.025Z</v>
+        <v>2026-07-30T14:00:11.534Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T13:50:51.025Z</v>
+        <v>2026-07-30T14:00:12.534Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T13:50:52.025Z</v>
+        <v>2026-07-30T14:00:13.534Z</v>
       </c>
     </row>
     <row r="58">
@@ -1379,10 +1379,10 @@
         <v>Passed</v>
       </c>
       <c r="D58">
-        <v>0.94</v>
+        <v>1.46</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T13:50:53.025Z</v>
+        <v>2026-07-30T14:00:14.534Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T13:50:54.025Z</v>
+        <v>2026-07-30T14:00:15.534Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>1.6</v>
+        <v>0.51</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T13:50:55.025Z</v>
+        <v>2026-07-30T14:00:16.534Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T13:50:56.025Z</v>
+        <v>2026-07-30T14:00:17.534Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T13:50:57.025Z</v>
+        <v>2026-07-30T14:00:18.534Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>0.1</v>
+        <v>0.98</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T13:50:58.025Z</v>
+        <v>2026-07-30T14:00:19.534Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>0.8</v>
+        <v>1.71</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T13:50:59.025Z</v>
+        <v>2026-07-30T14:00:20.534Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T13:51:00.025Z</v>
+        <v>2026-07-30T14:00:21.534Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T13:51:01.025Z</v>
+        <v>2026-07-30T14:00:22.534Z</v>
       </c>
     </row>
     <row r="67">
@@ -1532,10 +1532,10 @@
         <v>Passed</v>
       </c>
       <c r="D67">
-        <v>1.36</v>
+        <v>0.77</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T13:51:02.025Z</v>
+        <v>2026-07-30T14:00:23.534Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T13:51:03.025Z</v>
+        <v>2026-07-30T14:00:24.534Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T13:51:04.025Z</v>
+        <v>2026-07-30T14:00:25.534Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T13:51:05.025Z</v>
+        <v>2026-07-30T14:00:26.534Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>1.43</v>
+        <v>0.43</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T13:51:06.025Z</v>
+        <v>2026-07-30T14:00:27.534Z</v>
       </c>
     </row>
     <row r="72">
@@ -1617,10 +1617,10 @@
         <v>Passed</v>
       </c>
       <c r="D72">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T13:51:07.025Z</v>
+        <v>2026-07-30T14:00:28.534Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T13:51:08.025Z</v>
+        <v>2026-07-30T14:00:29.534Z</v>
       </c>
     </row>
     <row r="74">
@@ -1651,10 +1651,10 @@
         <v>Passed</v>
       </c>
       <c r="D74">
-        <v>1.77</v>
+        <v>0.24</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T13:51:09.025Z</v>
+        <v>2026-07-30T14:00:30.534Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>1.3</v>
+        <v>0.68</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T13:51:10.025Z</v>
+        <v>2026-07-30T14:00:31.534Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T13:51:11.025Z</v>
+        <v>2026-07-30T14:00:32.534Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T13:51:12.025Z</v>
+        <v>2026-07-30T14:00:33.534Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T13:51:13.025Z</v>
+        <v>2026-07-30T14:00:34.534Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T13:51:14.025Z</v>
+        <v>2026-07-30T14:00:35.534Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T13:51:15.025Z</v>
+        <v>2026-07-30T14:00:36.534Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T13:51:16.025Z</v>
+        <v>2026-07-30T14:00:37.534Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T13:51:17.025Z</v>
+        <v>2026-07-30T14:00:38.534Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>0.42</v>
+        <v>1.17</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T13:51:18.025Z</v>
+        <v>2026-07-30T14:00:39.534Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T13:51:19.025Z</v>
+        <v>2026-07-30T14:00:40.534Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>0.12</v>
+        <v>1.6</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T13:51:20.025Z</v>
+        <v>2026-07-30T14:00:41.534Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>0.83</v>
+        <v>1.88</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T13:51:21.025Z</v>
+        <v>2026-07-30T14:00:42.534Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>0.17</v>
+        <v>1.49</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T13:51:22.025Z</v>
+        <v>2026-07-30T14:00:43.534Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T13:51:23.025Z</v>
+        <v>2026-07-30T14:00:44.534Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>0.41</v>
+        <v>0.79</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T13:51:24.025Z</v>
+        <v>2026-07-30T14:00:45.534Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T13:51:25.025Z</v>
+        <v>2026-07-30T14:00:46.534Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>0.76</v>
+        <v>1.25</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T13:51:26.025Z</v>
+        <v>2026-07-30T14:00:47.534Z</v>
       </c>
     </row>
     <row r="92">
@@ -1957,10 +1957,10 @@
         <v>Passed</v>
       </c>
       <c r="D92">
-        <v>0.91</v>
+        <v>0.33</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T13:51:27.025Z</v>
+        <v>2026-07-30T14:00:48.534Z</v>
       </c>
     </row>
     <row r="93">
@@ -1974,10 +1974,10 @@
         <v>Passed</v>
       </c>
       <c r="D93">
-        <v>1.22</v>
+        <v>0.95</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T13:51:28.025Z</v>
+        <v>2026-07-30T14:00:49.534Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>1.97</v>
+        <v>0.93</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T13:51:29.025Z</v>
+        <v>2026-07-30T14:00:50.534Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>0.98</v>
+        <v>1.98</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T13:51:30.025Z</v>
+        <v>2026-07-30T14:00:51.534Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>0.48</v>
+        <v>1.34</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T13:51:31.025Z</v>
+        <v>2026-07-30T14:00:52.534Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>0.37</v>
+        <v>1.8</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T13:51:32.025Z</v>
+        <v>2026-07-30T14:00:53.534Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>1.15</v>
+        <v>0.09</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T13:51:33.025Z</v>
+        <v>2026-07-30T14:00:54.534Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T13:51:34.025Z</v>
+        <v>2026-07-30T14:00:55.534Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T13:51:35.025Z</v>
+        <v>2026-07-30T14:00:56.534Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>1.7</v>
+        <v>0.15</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T13:51:36.025Z</v>
+        <v>2026-07-30T14:00:57.534Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>1.56</v>
+        <v>0.05</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T13:51:37.025Z</v>
+        <v>2026-07-30T14:00:58.534Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>0.44</v>
+        <v>1.98</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T13:51:38.025Z</v>
+        <v>2026-07-30T14:00:59.534Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T13:51:39.025Z</v>
+        <v>2026-07-30T14:01:00.534Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>1.63</v>
+        <v>0.76</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T13:51:40.025Z</v>
+        <v>2026-07-30T14:01:01.534Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>0.19</v>
+        <v>0.69</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T13:51:41.025Z</v>
+        <v>2026-07-30T14:01:02.534Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>1.27</v>
+        <v>0.28</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T13:51:42.025Z</v>
+        <v>2026-07-30T14:01:03.534Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T13:51:43.025Z</v>
+        <v>2026-07-30T14:01:04.534Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T13:51:44.025Z</v>
+        <v>2026-07-30T14:01:05.534Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>1.73</v>
+        <v>0.04</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T13:51:45.025Z</v>
+        <v>2026-07-30T14:01:06.534Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T13:51:46.025Z</v>
+        <v>2026-07-30T14:01:07.534Z</v>
       </c>
     </row>
     <row r="112">
@@ -2300,7 +2300,7 @@
         <v>1.59</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T13:51:47.025Z</v>
+        <v>2026-07-30T14:01:08.534Z</v>
       </c>
     </row>
     <row r="113">
@@ -2314,10 +2314,10 @@
         <v>Passed</v>
       </c>
       <c r="D113">
-        <v>0.57</v>
+        <v>0.81</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T13:51:48.025Z</v>
+        <v>2026-07-30T14:01:09.534Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>1.34</v>
+        <v>0.17</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T13:51:49.025Z</v>
+        <v>2026-07-30T14:01:10.534Z</v>
       </c>
     </row>
     <row r="115">
@@ -2348,10 +2348,10 @@
         <v>Passed</v>
       </c>
       <c r="D115">
-        <v>0.11</v>
+        <v>0.89</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T13:51:50.025Z</v>
+        <v>2026-07-30T14:01:11.534Z</v>
       </c>
     </row>
     <row r="116">
@@ -2365,10 +2365,10 @@
         <v>Passed</v>
       </c>
       <c r="D116">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T13:51:51.025Z</v>
+        <v>2026-07-30T14:01:12.534Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>0.41</v>
+        <v>1.04</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T13:51:52.025Z</v>
+        <v>2026-07-30T14:01:13.534Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T13:51:53.025Z</v>
+        <v>2026-07-30T14:01:14.534Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>0.4</v>
+        <v>1.37</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T13:51:54.025Z</v>
+        <v>2026-07-30T14:01:15.534Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T13:51:55.025Z</v>
+        <v>2026-07-30T14:01:16.534Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T13:51:56.025Z</v>
+        <v>2026-07-30T14:01:17.534Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T13:51:57.025Z</v>
+        <v>2026-07-30T14:01:18.534Z</v>
       </c>
     </row>
     <row r="123">
@@ -2481,13 +2481,13 @@
         <v>Verify APILoad functionality module 122</v>
       </c>
       <c r="C123" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D123">
-        <v>0.53</v>
+        <v>1.14</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T13:51:58.025Z</v>
+        <v>2026-07-30T14:01:19.534Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>0.31</v>
+        <v>0.13</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T13:51:59.025Z</v>
+        <v>2026-07-30T14:01:20.534Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>0.45</v>
+        <v>1.18</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T13:52:00.025Z</v>
+        <v>2026-07-30T14:01:21.534Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T13:52:01.025Z</v>
+        <v>2026-07-30T14:01:22.534Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>0.1</v>
+        <v>1.26</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T13:52:02.025Z</v>
+        <v>2026-07-30T14:01:23.534Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T13:52:03.025Z</v>
+        <v>2026-07-30T14:01:24.534Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>0.98</v>
+        <v>1.5</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T13:52:04.025Z</v>
+        <v>2026-07-30T14:01:25.534Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>1.59</v>
+        <v>0.27</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T13:52:05.025Z</v>
+        <v>2026-07-30T14:01:26.534Z</v>
       </c>
     </row>
     <row r="131">
@@ -2620,10 +2620,10 @@
         <v>Passed</v>
       </c>
       <c r="D131">
-        <v>1.98</v>
+        <v>1.12</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T13:52:06.025Z</v>
+        <v>2026-07-30T14:01:27.534Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>1.42</v>
+        <v>0.75</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T13:52:07.025Z</v>
+        <v>2026-07-30T14:01:28.534Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>1.51</v>
+        <v>0.81</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T13:52:08.025Z</v>
+        <v>2026-07-30T14:01:29.534Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T13:52:09.025Z</v>
+        <v>2026-07-30T14:01:30.534Z</v>
       </c>
     </row>
     <row r="135">
@@ -2688,10 +2688,10 @@
         <v>Passed</v>
       </c>
       <c r="D135">
-        <v>1.05</v>
+        <v>1.92</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T13:52:10.025Z</v>
+        <v>2026-07-30T14:01:31.534Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>0.24</v>
+        <v>1.68</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T13:52:11.025Z</v>
+        <v>2026-07-30T14:01:32.534Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>0.08</v>
+        <v>1.67</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T13:52:12.025Z</v>
+        <v>2026-07-30T14:01:33.534Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T13:52:13.025Z</v>
+        <v>2026-07-30T14:01:34.534Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T13:52:14.025Z</v>
+        <v>2026-07-30T14:01:35.534Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>0.78</v>
+        <v>1.25</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T13:52:15.025Z</v>
+        <v>2026-07-30T14:01:36.534Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>0.59</v>
+        <v>1.47</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T13:52:16.025Z</v>
+        <v>2026-07-30T14:01:37.534Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>1.34</v>
+        <v>0.44</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T13:52:17.025Z</v>
+        <v>2026-07-30T14:01:38.534Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>1.15</v>
+        <v>1.9</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T13:52:18.025Z</v>
+        <v>2026-07-30T14:01:39.534Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T13:52:19.025Z</v>
+        <v>2026-07-30T14:01:40.534Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>1.78</v>
+        <v>0.19</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T13:52:20.025Z</v>
+        <v>2026-07-30T14:01:41.534Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>1.63</v>
+        <v>0.79</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T13:52:21.025Z</v>
+        <v>2026-07-30T14:01:42.534Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>1.85</v>
+        <v>0.95</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T13:52:22.025Z</v>
+        <v>2026-07-30T14:01:43.534Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T13:52:23.025Z</v>
+        <v>2026-07-30T14:01:44.534Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T13:52:24.025Z</v>
+        <v>2026-07-30T14:01:45.534Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T13:52:25.025Z</v>
+        <v>2026-07-30T14:01:46.534Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>0.91</v>
+        <v>1.09</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T13:52:26.025Z</v>
+        <v>2026-07-30T14:01:47.534Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T13:52:27.025Z</v>
+        <v>2026-07-30T14:01:48.534Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T13:52:28.025Z</v>
+        <v>2026-07-30T14:01:49.534Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>1.13</v>
+        <v>0.16</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T13:52:29.025Z</v>
+        <v>2026-07-30T14:01:50.534Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T13:52:30.025Z</v>
+        <v>2026-07-30T14:01:51.534Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T13:52:31.025Z</v>
+        <v>2026-07-30T14:01:52.534Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T13:52:32.025Z</v>
+        <v>2026-07-30T14:01:53.534Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T13:52:33.025Z</v>
+        <v>2026-07-30T14:01:54.534Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>1.56</v>
+        <v>0.51</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T13:52:34.025Z</v>
+        <v>2026-07-30T14:01:55.534Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>1.48</v>
+        <v>0.55</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T13:52:35.025Z</v>
+        <v>2026-07-30T14:01:56.534Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>0.29</v>
+        <v>1.78</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T13:52:36.025Z</v>
+        <v>2026-07-30T14:01:57.534Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T13:52:37.025Z</v>
+        <v>2026-07-30T14:01:58.534Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T13:52:38.025Z</v>
+        <v>2026-07-30T14:01:59.534Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>1.68</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T13:52:39.025Z</v>
+        <v>2026-07-30T14:02:00.534Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>1.47</v>
+        <v>1.88</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T13:52:40.025Z</v>
+        <v>2026-07-30T14:02:01.534Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>0.84</v>
+        <v>0.28</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T13:52:41.025Z</v>
+        <v>2026-07-30T14:02:02.534Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T13:52:42.025Z</v>
+        <v>2026-07-30T14:02:03.534Z</v>
       </c>
     </row>
     <row r="168">
@@ -3249,10 +3249,10 @@
         <v>Passed</v>
       </c>
       <c r="D168">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T13:52:43.025Z</v>
+        <v>2026-07-30T14:02:04.534Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T13:52:44.025Z</v>
+        <v>2026-07-30T14:02:05.534Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>1.02</v>
+        <v>0.16</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T13:52:45.025Z</v>
+        <v>2026-07-30T14:02:06.534Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T13:52:46.025Z</v>
+        <v>2026-07-30T14:02:07.534Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>0.25</v>
+        <v>1.54</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T13:52:47.025Z</v>
+        <v>2026-07-30T14:02:08.534Z</v>
       </c>
     </row>
     <row r="173">
@@ -3334,10 +3334,10 @@
         <v>Passed</v>
       </c>
       <c r="D173">
-        <v>0.94</v>
+        <v>0.81</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T13:52:48.025Z</v>
+        <v>2026-07-30T14:02:09.534Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>0.2</v>
+        <v>1.28</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T13:52:49.025Z</v>
+        <v>2026-07-30T14:02:10.534Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>1.87</v>
+        <v>0.07</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T13:52:50.025Z</v>
+        <v>2026-07-30T14:02:11.534Z</v>
       </c>
     </row>
     <row r="176">
@@ -3385,10 +3385,10 @@
         <v>Passed</v>
       </c>
       <c r="D176">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T13:52:51.025Z</v>
+        <v>2026-07-30T14:02:12.534Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>1.12</v>
+        <v>0.12</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T13:52:52.025Z</v>
+        <v>2026-07-30T14:02:13.534Z</v>
       </c>
     </row>
     <row r="178">
@@ -3416,13 +3416,13 @@
         <v>Verify APILoad functionality module 177</v>
       </c>
       <c r="C178" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D178">
-        <v>1.68</v>
+        <v>0.01</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T13:52:53.025Z</v>
+        <v>2026-07-30T14:02:14.534Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>1.27</v>
+        <v>0.33</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T13:52:54.025Z</v>
+        <v>2026-07-30T14:02:15.534Z</v>
       </c>
     </row>
     <row r="180">
@@ -3453,10 +3453,10 @@
         <v>Passed</v>
       </c>
       <c r="D180">
-        <v>0.68</v>
+        <v>0.15</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T13:52:55.025Z</v>
+        <v>2026-07-30T14:02:16.534Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>0.4</v>
+        <v>1.65</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T13:52:56.025Z</v>
+        <v>2026-07-30T14:02:17.534Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>1.18</v>
+        <v>0.63</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T13:52:57.025Z</v>
+        <v>2026-07-30T14:02:18.534Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T13:52:58.025Z</v>
+        <v>2026-07-30T14:02:19.534Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>1.87</v>
+        <v>0.38</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T13:52:59.025Z</v>
+        <v>2026-07-30T14:02:20.534Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T13:53:00.025Z</v>
+        <v>2026-07-30T14:02:21.534Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>1.43</v>
+        <v>0.32</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T13:53:01.025Z</v>
+        <v>2026-07-30T14:02:22.534Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>0.4</v>
+        <v>1.25</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T13:53:02.025Z</v>
+        <v>2026-07-30T14:02:23.534Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>0.7</v>
+        <v>0.42</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T13:53:03.025Z</v>
+        <v>2026-07-30T14:02:24.534Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T13:53:04.025Z</v>
+        <v>2026-07-30T14:02:25.534Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T13:53:05.025Z</v>
+        <v>2026-07-30T14:02:26.534Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>0.24</v>
+        <v>1.66</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T13:53:06.025Z</v>
+        <v>2026-07-30T14:02:27.534Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T13:53:07.025Z</v>
+        <v>2026-07-30T14:02:28.534Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T13:53:08.025Z</v>
+        <v>2026-07-30T14:02:29.534Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>1.18</v>
+        <v>0.28</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T13:53:09.025Z</v>
+        <v>2026-07-30T14:02:30.534Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T13:53:10.025Z</v>
+        <v>2026-07-30T14:02:31.534Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T13:53:11.025Z</v>
+        <v>2026-07-30T14:02:32.534Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>1.48</v>
+        <v>0.34</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T13:53:12.025Z</v>
+        <v>2026-07-30T14:02:33.534Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>0.73</v>
+        <v>1.05</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T13:53:13.025Z</v>
+        <v>2026-07-30T14:02:34.534Z</v>
       </c>
     </row>
     <row r="199">
@@ -3776,10 +3776,10 @@
         <v>Passed</v>
       </c>
       <c r="D199">
-        <v>0.05</v>
+        <v>0.68</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T13:53:14.025Z</v>
+        <v>2026-07-30T14:02:35.534Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>1.84</v>
+        <v>0.6</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T13:53:15.025Z</v>
+        <v>2026-07-30T14:02:36.534Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>0.84</v>
+        <v>0.43</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T13:53:16.025Z</v>
+        <v>2026-07-30T14:02:37.534Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T13:53:17.025Z</v>
+        <v>2026-07-30T14:02:38.534Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>1.07</v>
+        <v>0.69</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T13:53:18.025Z</v>
+        <v>2026-07-30T14:02:39.534Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>0.57</v>
+        <v>1.2</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T13:53:19.025Z</v>
+        <v>2026-07-30T14:02:40.534Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T13:53:20.025Z</v>
+        <v>2026-07-30T14:02:41.534Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>0.24</v>
+        <v>1.02</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T13:53:21.025Z</v>
+        <v>2026-07-30T14:02:42.534Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T13:53:22.025Z</v>
+        <v>2026-07-30T14:02:43.534Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T13:53:23.025Z</v>
+        <v>2026-07-30T14:02:44.534Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T13:53:24.025Z</v>
+        <v>2026-07-30T14:02:45.534Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>0.83</v>
+        <v>1.66</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T13:53:25.025Z</v>
+        <v>2026-07-30T14:02:46.534Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>0.11</v>
+        <v>1.2</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T13:53:26.025Z</v>
+        <v>2026-07-30T14:02:47.534Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>1.72</v>
+        <v>0.02</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T13:53:27.025Z</v>
+        <v>2026-07-30T14:02:48.534Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>0.08</v>
+        <v>0.74</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T13:53:28.025Z</v>
+        <v>2026-07-30T14:02:49.534Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>1.12</v>
+        <v>0.14</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T13:53:29.025Z</v>
+        <v>2026-07-30T14:02:50.534Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T13:53:30.025Z</v>
+        <v>2026-07-30T14:02:51.534Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T13:53:31.025Z</v>
+        <v>2026-07-30T14:02:52.534Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>0.32</v>
+        <v>0.03</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T13:53:32.025Z</v>
+        <v>2026-07-30T14:02:53.534Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T13:53:33.025Z</v>
+        <v>2026-07-30T14:02:54.534Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>1.2</v>
+        <v>0.36</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T13:53:34.025Z</v>
+        <v>2026-07-30T14:02:55.534Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>1.26</v>
+        <v>0.57</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T13:53:35.025Z</v>
+        <v>2026-07-30T14:02:56.534Z</v>
       </c>
     </row>
     <row r="221">
@@ -4150,10 +4150,10 @@
         <v>Passed</v>
       </c>
       <c r="D221">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T13:53:36.025Z</v>
+        <v>2026-07-30T14:02:57.534Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>0.99</v>
+        <v>1.58</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T13:53:37.025Z</v>
+        <v>2026-07-30T14:02:58.534Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T13:53:38.025Z</v>
+        <v>2026-07-30T14:02:59.534Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>0.06</v>
+        <v>1.73</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T13:53:39.025Z</v>
+        <v>2026-07-30T14:03:00.534Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>0.54</v>
+        <v>1.65</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T13:53:40.025Z</v>
+        <v>2026-07-30T14:03:01.534Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>0.33</v>
+        <v>0.99</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T13:53:41.025Z</v>
+        <v>2026-07-30T14:03:02.534Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T13:53:42.025Z</v>
+        <v>2026-07-30T14:03:03.534Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T13:53:43.025Z</v>
+        <v>2026-07-30T14:03:04.534Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>0.86</v>
+        <v>1.34</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T13:53:44.025Z</v>
+        <v>2026-07-30T14:03:05.534Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>0.12</v>
+        <v>1.24</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T13:53:45.025Z</v>
+        <v>2026-07-30T14:03:06.534Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>1.47</v>
+        <v>0.3</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T13:53:46.025Z</v>
+        <v>2026-07-30T14:03:07.534Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>1.29</v>
+        <v>0.81</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T13:53:47.025Z</v>
+        <v>2026-07-30T14:03:08.534Z</v>
       </c>
     </row>
     <row r="233">
@@ -4354,10 +4354,10 @@
         <v>Passed</v>
       </c>
       <c r="D233">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T13:53:48.025Z</v>
+        <v>2026-07-30T14:03:09.534Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T13:53:49.025Z</v>
+        <v>2026-07-30T14:03:10.534Z</v>
       </c>
     </row>
     <row r="235">
@@ -4388,10 +4388,10 @@
         <v>Passed</v>
       </c>
       <c r="D235">
-        <v>1.8</v>
+        <v>0.87</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T13:53:50.025Z</v>
+        <v>2026-07-30T14:03:11.534Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>1.56</v>
+        <v>0.86</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T13:53:51.025Z</v>
+        <v>2026-07-30T14:03:12.534Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>0.77</v>
+        <v>0.19</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T13:53:52.025Z</v>
+        <v>2026-07-30T14:03:13.534Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>1.44</v>
+        <v>0.45</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T13:53:53.025Z</v>
+        <v>2026-07-30T14:03:14.534Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T13:53:54.025Z</v>
+        <v>2026-07-30T14:03:15.534Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T13:53:55.025Z</v>
+        <v>2026-07-30T14:03:16.534Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>1.72</v>
+        <v>0.72</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T13:53:56.025Z</v>
+        <v>2026-07-30T14:03:17.534Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T13:53:57.025Z</v>
+        <v>2026-07-30T14:03:18.534Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T13:53:58.025Z</v>
+        <v>2026-07-30T14:03:19.534Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>1.55</v>
+        <v>0.31</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T13:53:59.025Z</v>
+        <v>2026-07-30T14:03:20.534Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>1.78</v>
+        <v>0.66</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T13:54:00.025Z</v>
+        <v>2026-07-30T14:03:21.534Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>0.43</v>
+        <v>0.85</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T13:54:01.025Z</v>
+        <v>2026-07-30T14:03:22.534Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T13:54:02.025Z</v>
+        <v>2026-07-30T14:03:23.534Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T13:54:03.025Z</v>
+        <v>2026-07-30T14:03:24.534Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>0.39</v>
+        <v>0.8</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T13:54:04.025Z</v>
+        <v>2026-07-30T14:03:25.534Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T13:54:05.025Z</v>
+        <v>2026-07-30T14:03:26.534Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T13:54:06.025Z</v>
+        <v>2026-07-30T14:03:27.534Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>0.37</v>
+        <v>1.98</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T13:54:07.025Z</v>
+        <v>2026-07-30T14:03:28.534Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T13:54:08.025Z</v>
+        <v>2026-07-30T14:03:29.534Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>1.79</v>
+        <v>0.75</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T13:54:09.025Z</v>
+        <v>2026-07-30T14:03:30.534Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>0.45</v>
+        <v>1.26</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T13:54:10.025Z</v>
+        <v>2026-07-30T14:03:31.534Z</v>
       </c>
     </row>
     <row r="256">
@@ -4745,10 +4745,10 @@
         <v>Passed</v>
       </c>
       <c r="D256">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T13:54:11.025Z</v>
+        <v>2026-07-30T14:03:32.534Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>1.97</v>
+        <v>1.06</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T13:54:12.025Z</v>
+        <v>2026-07-30T14:03:33.534Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>1.62</v>
+        <v>0.65</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T13:54:13.025Z</v>
+        <v>2026-07-30T14:03:34.534Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T13:54:14.025Z</v>
+        <v>2026-07-30T14:03:35.534Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T13:54:15.025Z</v>
+        <v>2026-07-30T14:03:36.534Z</v>
       </c>
     </row>
     <row r="261">
@@ -4833,7 +4833,7 @@
         <v>1.04</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T13:54:16.025Z</v>
+        <v>2026-07-30T14:03:37.534Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>0.12</v>
+        <v>0.61</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T13:54:17.025Z</v>
+        <v>2026-07-30T14:03:38.534Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T13:54:18.025Z</v>
+        <v>2026-07-30T14:03:39.534Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T13:54:19.025Z</v>
+        <v>2026-07-30T14:03:40.534Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>1.61</v>
+        <v>0.01</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T13:54:20.025Z</v>
+        <v>2026-07-30T14:03:41.534Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T13:54:21.025Z</v>
+        <v>2026-07-30T14:03:42.534Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>0.27</v>
+        <v>0.63</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T13:54:22.025Z</v>
+        <v>2026-07-30T14:03:43.534Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>1.65</v>
+        <v>0.44</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T13:54:23.025Z</v>
+        <v>2026-07-30T14:03:44.534Z</v>
       </c>
     </row>
     <row r="269">
@@ -4966,10 +4966,10 @@
         <v>Passed</v>
       </c>
       <c r="D269">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T13:54:24.025Z</v>
+        <v>2026-07-30T14:03:45.534Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T13:54:25.025Z</v>
+        <v>2026-07-30T14:03:46.534Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>1.11</v>
+        <v>0.19</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T13:54:26.025Z</v>
+        <v>2026-07-30T14:03:47.534Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T13:54:27.025Z</v>
+        <v>2026-07-30T14:03:48.534Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>0.95</v>
+        <v>1.42</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T13:54:28.025Z</v>
+        <v>2026-07-30T14:03:49.534Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>0.37</v>
+        <v>1.17</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T13:54:29.025Z</v>
+        <v>2026-07-30T14:03:50.534Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>1.63</v>
+        <v>0.24</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T13:54:30.025Z</v>
+        <v>2026-07-30T14:03:51.534Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>0.27</v>
+        <v>1.61</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T13:54:31.025Z</v>
+        <v>2026-07-30T14:03:52.534Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T13:54:32.025Z</v>
+        <v>2026-07-30T14:03:53.534Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T13:54:33.025Z</v>
+        <v>2026-07-30T14:03:54.534Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T13:54:34.025Z</v>
+        <v>2026-07-30T14:03:55.534Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>1.15</v>
+        <v>1.77</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T13:54:35.025Z</v>
+        <v>2026-07-30T14:03:56.534Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>1.81</v>
+        <v>0.95</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T13:54:36.025Z</v>
+        <v>2026-07-30T14:03:57.534Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T13:54:37.025Z</v>
+        <v>2026-07-30T14:03:58.534Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>0.64</v>
+        <v>1.21</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T13:54:38.025Z</v>
+        <v>2026-07-30T14:03:59.534Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T13:54:39.025Z</v>
+        <v>2026-07-30T14:04:00.534Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>1.94</v>
+        <v>1.12</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T13:54:40.025Z</v>
+        <v>2026-07-30T14:04:01.534Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.95</v>
+        <v>0.81</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T13:54:41.025Z</v>
+        <v>2026-07-30T14:04:02.534Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>1.74</v>
+        <v>0.71</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T13:54:42.025Z</v>
+        <v>2026-07-30T14:04:03.534Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>0.13</v>
+        <v>1.38</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T13:54:43.025Z</v>
+        <v>2026-07-30T14:04:04.534Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>1.89</v>
+        <v>0.76</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T13:54:44.025Z</v>
+        <v>2026-07-30T14:04:05.534Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>0.65</v>
+        <v>1.51</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T13:54:45.025Z</v>
+        <v>2026-07-30T14:04:06.534Z</v>
       </c>
     </row>
     <row r="291">
@@ -5340,10 +5340,10 @@
         <v>Passed</v>
       </c>
       <c r="D291">
-        <v>1.03</v>
+        <v>0.5</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T13:54:46.025Z</v>
+        <v>2026-07-30T14:04:07.534Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>0.19</v>
+        <v>1.51</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T13:54:47.025Z</v>
+        <v>2026-07-30T14:04:08.534Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>1.24</v>
+        <v>0.09</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T13:54:48.025Z</v>
+        <v>2026-07-30T14:04:09.534Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T13:54:49.025Z</v>
+        <v>2026-07-30T14:04:10.534Z</v>
       </c>
     </row>
     <row r="295">
@@ -5405,13 +5405,13 @@
         <v>Verify APILoad functionality module 294</v>
       </c>
       <c r="C295" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D295">
-        <v>1.93</v>
+        <v>0.31</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T13:54:50.025Z</v>
+        <v>2026-07-30T14:04:11.534Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>0.16</v>
+        <v>1.33</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T13:54:51.025Z</v>
+        <v>2026-07-30T14:04:12.534Z</v>
       </c>
     </row>
     <row r="297">
@@ -5439,13 +5439,13 @@
         <v>Verify APILoad functionality module 296</v>
       </c>
       <c r="C297" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D297">
-        <v>1.57</v>
+        <v>0.77</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T13:54:52.025Z</v>
+        <v>2026-07-30T14:04:13.534Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T13:54:53.025Z</v>
+        <v>2026-07-30T14:04:14.534Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>1.12</v>
+        <v>0.17</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T13:54:54.025Z</v>
+        <v>2026-07-30T14:04:15.534Z</v>
       </c>
     </row>
     <row r="300">
@@ -5493,10 +5493,10 @@
         <v>Passed</v>
       </c>
       <c r="D300">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T13:54:55.025Z</v>
+        <v>2026-07-30T14:04:16.534Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T13:54:56.025Z</v>
+        <v>2026-07-30T14:04:17.534Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>0.15</v>
+        <v>1.38</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T13:54:57.025Z</v>
+        <v>2026-07-30T14:04:18.534Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>0.23</v>
+        <v>0.65</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T13:54:58.025Z</v>
+        <v>2026-07-30T14:04:19.534Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>0.77</v>
+        <v>0.14</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T13:54:59.025Z</v>
+        <v>2026-07-30T14:04:20.534Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T13:55:00.025Z</v>
+        <v>2026-07-30T14:04:21.534Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>1.66</v>
+        <v>0.23</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T13:55:01.025Z</v>
+        <v>2026-07-30T14:04:22.534Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T13:55:02.025Z</v>
+        <v>2026-07-30T14:04:23.534Z</v>
       </c>
     </row>
     <row r="308">
@@ -5629,10 +5629,10 @@
         <v>Passed</v>
       </c>
       <c r="D308">
-        <v>0.54</v>
+        <v>1.53</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T13:55:03.025Z</v>
+        <v>2026-07-30T14:04:24.534Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T13:55:04.025Z</v>
+        <v>2026-07-30T14:04:25.534Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>1.01</v>
+        <v>0.29</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T13:55:05.025Z</v>
+        <v>2026-07-30T14:04:26.534Z</v>
       </c>
     </row>
     <row r="311">
@@ -5677,13 +5677,13 @@
         <v>Verify APILoad functionality module 310</v>
       </c>
       <c r="C311" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D311">
-        <v>1.33</v>
+        <v>0.85</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T13:55:06.025Z</v>
+        <v>2026-07-30T14:04:27.534Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>0.3</v>
+        <v>0.81</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T13:55:07.025Z</v>
+        <v>2026-07-30T14:04:28.534Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>1.28</v>
+        <v>0.47</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T13:55:08.025Z</v>
+        <v>2026-07-30T14:04:29.534Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>0.96</v>
+        <v>0.44</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T13:55:09.025Z</v>
+        <v>2026-07-30T14:04:30.534Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T13:55:10.025Z</v>
+        <v>2026-07-30T14:04:31.534Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>0.38</v>
+        <v>1.59</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T13:55:11.025Z</v>
+        <v>2026-07-30T14:04:32.534Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>1.13</v>
+        <v>1.95</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T13:55:12.025Z</v>
+        <v>2026-07-30T14:04:33.534Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T13:55:13.025Z</v>
+        <v>2026-07-30T14:04:34.534Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>0.11</v>
+        <v>0.81</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T13:55:14.025Z</v>
+        <v>2026-07-30T14:04:35.534Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T13:55:15.025Z</v>
+        <v>2026-07-30T14:04:36.534Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>0.68</v>
+        <v>1.03</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T13:55:16.025Z</v>
+        <v>2026-07-30T14:04:37.534Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T13:55:17.025Z</v>
+        <v>2026-07-30T14:04:38.534Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>1.28</v>
+        <v>0.97</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T13:55:18.025Z</v>
+        <v>2026-07-30T14:04:39.534Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>0.34</v>
+        <v>1.17</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T13:55:19.025Z</v>
+        <v>2026-07-30T14:04:40.534Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T13:55:20.025Z</v>
+        <v>2026-07-30T14:04:41.534Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>0.66</v>
+        <v>1.28</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T13:55:21.025Z</v>
+        <v>2026-07-30T14:04:42.534Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>1.74</v>
+        <v>0.4</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T13:55:22.025Z</v>
+        <v>2026-07-30T14:04:43.534Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>1.34</v>
+        <v>0.27</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T13:55:23.025Z</v>
+        <v>2026-07-30T14:04:44.534Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>1.35</v>
+        <v>0.43</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T13:55:24.025Z</v>
+        <v>2026-07-30T14:04:45.534Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T13:55:25.025Z</v>
+        <v>2026-07-30T14:04:46.534Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>1.72</v>
+        <v>0.71</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T13:55:26.025Z</v>
+        <v>2026-07-30T14:04:47.534Z</v>
       </c>
     </row>
     <row r="332">
@@ -6037,10 +6037,10 @@
         <v>Passed</v>
       </c>
       <c r="D332">
-        <v>1.66</v>
+        <v>0.64</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T13:55:27.025Z</v>
+        <v>2026-07-30T14:04:48.534Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T13:55:28.025Z</v>
+        <v>2026-07-30T14:04:49.534Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>1.63</v>
+        <v>0.59</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T13:55:29.025Z</v>
+        <v>2026-07-30T14:04:50.534Z</v>
       </c>
     </row>
     <row r="335">
@@ -6088,10 +6088,10 @@
         <v>Passed</v>
       </c>
       <c r="D335">
-        <v>0.15</v>
+        <v>1.13</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T13:55:30.025Z</v>
+        <v>2026-07-30T14:04:51.534Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>1.53</v>
+        <v>0.91</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T13:55:31.025Z</v>
+        <v>2026-07-30T14:04:52.534Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T13:55:32.025Z</v>
+        <v>2026-07-30T14:04:53.534Z</v>
       </c>
     </row>
     <row r="338">
@@ -6139,10 +6139,10 @@
         <v>Passed</v>
       </c>
       <c r="D338">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T13:55:33.025Z</v>
+        <v>2026-07-30T14:04:54.534Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>1.94</v>
+        <v>0.36</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T13:55:34.025Z</v>
+        <v>2026-07-30T14:04:55.534Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T13:55:35.025Z</v>
+        <v>2026-07-30T14:04:56.534Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T13:55:36.025Z</v>
+        <v>2026-07-30T14:04:57.534Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T13:55:37.025Z</v>
+        <v>2026-07-30T14:04:58.534Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>1.31</v>
+        <v>0.61</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T13:55:38.025Z</v>
+        <v>2026-07-30T14:04:59.534Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>1.32</v>
+        <v>0.49</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T13:55:39.025Z</v>
+        <v>2026-07-30T14:05:00.534Z</v>
       </c>
     </row>
     <row r="345">
@@ -6258,10 +6258,10 @@
         <v>Passed</v>
       </c>
       <c r="D345">
-        <v>0.87</v>
+        <v>0.1</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T13:55:40.025Z</v>
+        <v>2026-07-30T14:05:01.534Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T13:55:41.025Z</v>
+        <v>2026-07-30T14:05:02.534Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T13:55:42.025Z</v>
+        <v>2026-07-30T14:05:03.534Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>1.13</v>
+        <v>0.18</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T13:55:43.025Z</v>
+        <v>2026-07-30T14:05:04.534Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T13:55:44.025Z</v>
+        <v>2026-07-30T14:05:05.534Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>1.9</v>
+        <v>0.57</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T13:55:45.025Z</v>
+        <v>2026-07-30T14:05:06.534Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>0.15</v>
+        <v>1.6</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T13:55:46.025Z</v>
+        <v>2026-07-30T14:05:07.534Z</v>
       </c>
     </row>
     <row r="352">
@@ -6377,10 +6377,10 @@
         <v>Passed</v>
       </c>
       <c r="D352">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T13:55:47.025Z</v>
+        <v>2026-07-30T14:05:08.534Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T13:55:48.025Z</v>
+        <v>2026-07-30T14:05:09.534Z</v>
       </c>
     </row>
     <row r="354">
@@ -6411,10 +6411,10 @@
         <v>Passed</v>
       </c>
       <c r="D354">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T13:55:49.025Z</v>
+        <v>2026-07-30T14:05:10.534Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>1.12</v>
+        <v>1.95</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T13:55:50.025Z</v>
+        <v>2026-07-30T14:05:11.534Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>0.9</v>
+        <v>0.23</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T13:55:51.025Z</v>
+        <v>2026-07-30T14:05:12.534Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>0.86</v>
+        <v>1.66</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T13:55:52.025Z</v>
+        <v>2026-07-30T14:05:13.534Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>0.69</v>
+        <v>0.01</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T13:55:53.025Z</v>
+        <v>2026-07-30T14:05:14.534Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T13:55:54.025Z</v>
+        <v>2026-07-30T14:05:15.534Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>0.29</v>
+        <v>0.76</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T13:55:55.025Z</v>
+        <v>2026-07-30T14:05:16.534Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>1.79</v>
+        <v>0.36</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T13:55:56.025Z</v>
+        <v>2026-07-30T14:05:17.534Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T13:55:57.025Z</v>
+        <v>2026-07-30T14:05:18.534Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T13:55:58.025Z</v>
+        <v>2026-07-30T14:05:19.534Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T13:55:59.025Z</v>
+        <v>2026-07-30T14:05:20.534Z</v>
       </c>
     </row>
     <row r="365">
@@ -6598,10 +6598,10 @@
         <v>Passed</v>
       </c>
       <c r="D365">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T13:56:00.025Z</v>
+        <v>2026-07-30T14:05:21.534Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>0.47</v>
+        <v>0.83</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T13:56:01.025Z</v>
+        <v>2026-07-30T14:05:22.534Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T13:56:02.025Z</v>
+        <v>2026-07-30T14:05:23.534Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>0.12</v>
+        <v>1.25</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T13:56:03.025Z</v>
+        <v>2026-07-30T14:05:24.534Z</v>
       </c>
     </row>
     <row r="369">
@@ -6666,10 +6666,10 @@
         <v>Passed</v>
       </c>
       <c r="D369">
-        <v>0.65</v>
+        <v>0.38</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T13:56:04.025Z</v>
+        <v>2026-07-30T14:05:25.534Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>1.81</v>
+        <v>0.82</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T13:56:05.025Z</v>
+        <v>2026-07-30T14:05:26.534Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T13:56:06.025Z</v>
+        <v>2026-07-30T14:05:27.534Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>0.37</v>
+        <v>1.63</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T13:56:07.025Z</v>
+        <v>2026-07-30T14:05:28.534Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>1.69</v>
+        <v>0.65</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T13:56:08.025Z</v>
+        <v>2026-07-30T14:05:29.534Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T13:56:09.025Z</v>
+        <v>2026-07-30T14:05:30.534Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>1.92</v>
+        <v>1.29</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T13:56:10.025Z</v>
+        <v>2026-07-30T14:05:31.534Z</v>
       </c>
     </row>
     <row r="376">
@@ -6785,10 +6785,10 @@
         <v>Passed</v>
       </c>
       <c r="D376">
-        <v>0.21</v>
+        <v>1.1</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T13:56:11.025Z</v>
+        <v>2026-07-30T14:05:32.534Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T13:56:12.025Z</v>
+        <v>2026-07-30T14:05:33.534Z</v>
       </c>
     </row>
     <row r="378">
@@ -6816,13 +6816,13 @@
         <v>Verify APILoad functionality module 377</v>
       </c>
       <c r="C378" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D378">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T13:56:13.025Z</v>
+        <v>2026-07-30T14:05:34.534Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T13:56:14.025Z</v>
+        <v>2026-07-30T14:05:35.534Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T13:56:15.025Z</v>
+        <v>2026-07-30T14:05:36.534Z</v>
       </c>
     </row>
     <row r="381">
@@ -6870,10 +6870,10 @@
         <v>Passed</v>
       </c>
       <c r="D381">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T13:56:16.025Z</v>
+        <v>2026-07-30T14:05:37.534Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T13:56:17.025Z</v>
+        <v>2026-07-30T14:05:38.534Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>0.21</v>
+        <v>1.74</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T13:56:18.025Z</v>
+        <v>2026-07-30T14:05:39.534Z</v>
       </c>
     </row>
     <row r="384">
@@ -6921,10 +6921,10 @@
         <v>Passed</v>
       </c>
       <c r="D384">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T13:56:19.025Z</v>
+        <v>2026-07-30T14:05:40.534Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>0.89</v>
+        <v>1.62</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T13:56:20.025Z</v>
+        <v>2026-07-30T14:05:41.534Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>1.88</v>
+        <v>1.05</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T13:56:21.025Z</v>
+        <v>2026-07-30T14:05:42.534Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T13:56:22.025Z</v>
+        <v>2026-07-30T14:05:43.534Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>1.54</v>
+        <v>1.06</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T13:56:23.025Z</v>
+        <v>2026-07-30T14:05:44.534Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T13:56:24.025Z</v>
+        <v>2026-07-30T14:05:45.534Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T13:56:25.025Z</v>
+        <v>2026-07-30T14:05:46.534Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T13:56:26.025Z</v>
+        <v>2026-07-30T14:05:47.534Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>0.45</v>
+        <v>1.04</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T13:56:27.025Z</v>
+        <v>2026-07-30T14:05:48.534Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>1.53</v>
+        <v>0.26</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T13:56:28.025Z</v>
+        <v>2026-07-30T14:05:49.534Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>1.34</v>
+        <v>0.96</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T13:56:29.025Z</v>
+        <v>2026-07-30T14:05:50.534Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T13:56:30.025Z</v>
+        <v>2026-07-30T14:05:51.534Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T13:56:31.025Z</v>
+        <v>2026-07-30T14:05:52.534Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T13:56:32.025Z</v>
+        <v>2026-07-30T14:05:53.534Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T13:56:33.025Z</v>
+        <v>2026-07-30T14:05:54.534Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>0.07</v>
+        <v>1.09</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T13:56:34.025Z</v>
+        <v>2026-07-30T14:05:55.534Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>1.59</v>
+        <v>0.78</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T13:56:35.025Z</v>
+        <v>2026-07-30T14:05:56.534Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T13:56:36.025Z</v>
+        <v>2026-07-30T14:05:57.534Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>1.08</v>
+        <v>0.25</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T13:56:37.025Z</v>
+        <v>2026-07-30T14:05:58.534Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>0.2</v>
+        <v>1.11</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T13:56:38.025Z</v>
+        <v>2026-07-30T14:05:59.534Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>0.28</v>
+        <v>1.73</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T13:56:39.025Z</v>
+        <v>2026-07-30T14:06:00.534Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>1.84</v>
+        <v>0.92</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T13:56:40.025Z</v>
+        <v>2026-07-30T14:06:01.534Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T13:56:41.025Z</v>
+        <v>2026-07-30T14:06:02.534Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>0.57</v>
+        <v>1.47</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T13:56:42.025Z</v>
+        <v>2026-07-30T14:06:03.534Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T13:56:43.025Z</v>
+        <v>2026-07-30T14:06:04.534Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T13:56:44.025Z</v>
+        <v>2026-07-30T14:06:05.534Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>0.71</v>
+        <v>0.08</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T13:56:45.025Z</v>
+        <v>2026-07-30T14:06:06.534Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T13:56:46.025Z</v>
+        <v>2026-07-30T14:06:07.534Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T13:56:47.025Z</v>
+        <v>2026-07-30T14:06:08.534Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T13:56:48.025Z</v>
+        <v>2026-07-30T14:06:09.534Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T13:56:49.025Z</v>
+        <v>2026-07-30T14:06:10.534Z</v>
       </c>
     </row>
     <row r="415">
@@ -7448,10 +7448,10 @@
         <v>Passed</v>
       </c>
       <c r="D415">
-        <v>0.99</v>
+        <v>1.8</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T13:56:50.025Z</v>
+        <v>2026-07-30T14:06:11.534Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>1.2</v>
+        <v>0.01</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T13:56:51.025Z</v>
+        <v>2026-07-30T14:06:12.534Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>1.08</v>
+        <v>0.28</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T13:56:52.025Z</v>
+        <v>2026-07-30T14:06:13.534Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>1.81</v>
+        <v>0.29</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T13:56:53.025Z</v>
+        <v>2026-07-30T14:06:14.534Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>0.77</v>
+        <v>1.33</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T13:56:54.025Z</v>
+        <v>2026-07-30T14:06:15.534Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>1.25</v>
+        <v>0.39</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T13:56:55.025Z</v>
+        <v>2026-07-30T14:06:16.534Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>1.77</v>
+        <v>0.34</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T13:56:56.025Z</v>
+        <v>2026-07-30T14:06:17.534Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>0.5</v>
+        <v>1.34</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T13:56:57.025Z</v>
+        <v>2026-07-30T14:06:18.534Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>0.37</v>
+        <v>1.42</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T13:56:58.025Z</v>
+        <v>2026-07-30T14:06:19.534Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T13:56:59.025Z</v>
+        <v>2026-07-30T14:06:20.534Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T13:57:00.025Z</v>
+        <v>2026-07-30T14:06:21.534Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>0.4</v>
+        <v>1.44</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T13:57:01.025Z</v>
+        <v>2026-07-30T14:06:22.534Z</v>
       </c>
     </row>
     <row r="427">
@@ -7649,13 +7649,13 @@
         <v>Verify APILoad functionality module 426</v>
       </c>
       <c r="C427" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D427">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T13:57:02.025Z</v>
+        <v>2026-07-30T14:06:23.534Z</v>
       </c>
     </row>
     <row r="428">
@@ -7669,10 +7669,10 @@
         <v>Passed</v>
       </c>
       <c r="D428">
-        <v>0.88</v>
+        <v>1.15</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T13:57:03.025Z</v>
+        <v>2026-07-30T14:06:24.534Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>0.07</v>
+        <v>0.72</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T13:57:04.025Z</v>
+        <v>2026-07-30T14:06:25.534Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T13:57:05.025Z</v>
+        <v>2026-07-30T14:06:26.534Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T13:57:06.025Z</v>
+        <v>2026-07-30T14:06:27.534Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T13:57:07.025Z</v>
+        <v>2026-07-30T14:06:28.534Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T13:57:08.025Z</v>
+        <v>2026-07-30T14:06:29.534Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>1.34</v>
+        <v>0.61</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T13:57:09.025Z</v>
+        <v>2026-07-30T14:06:30.534Z</v>
       </c>
     </row>
     <row r="435">
@@ -7785,13 +7785,13 @@
         <v>Verify APILoad functionality module 434</v>
       </c>
       <c r="C435" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D435">
-        <v>1.92</v>
+        <v>0.57</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T13:57:10.025Z</v>
+        <v>2026-07-30T14:06:31.534Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>0.13</v>
+        <v>1.05</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T13:57:11.025Z</v>
+        <v>2026-07-30T14:06:32.534Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>0.07</v>
+        <v>1.18</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T13:57:12.025Z</v>
+        <v>2026-07-30T14:06:33.534Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T13:57:13.025Z</v>
+        <v>2026-07-30T14:06:34.534Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>1.59</v>
+        <v>0.09</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T13:57:14.025Z</v>
+        <v>2026-07-30T14:06:35.534Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T13:57:15.025Z</v>
+        <v>2026-07-30T14:06:36.534Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>1.57</v>
+        <v>0.66</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T13:57:16.025Z</v>
+        <v>2026-07-30T14:06:37.534Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T13:57:17.025Z</v>
+        <v>2026-07-30T14:06:38.534Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>0.17</v>
+        <v>1.39</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T13:57:18.025Z</v>
+        <v>2026-07-30T14:06:39.534Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T13:57:19.025Z</v>
+        <v>2026-07-30T14:06:40.534Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>1.17</v>
+        <v>0.73</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T13:57:20.025Z</v>
+        <v>2026-07-30T14:06:41.534Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>0.41</v>
+        <v>1.7</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T13:57:21.025Z</v>
+        <v>2026-07-30T14:06:42.534Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T13:57:22.025Z</v>
+        <v>2026-07-30T14:06:43.534Z</v>
       </c>
     </row>
     <row r="448">
@@ -8009,10 +8009,10 @@
         <v>Passed</v>
       </c>
       <c r="D448">
-        <v>1.12</v>
+        <v>0.37</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T13:57:23.025Z</v>
+        <v>2026-07-30T14:06:44.534Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>0.92</v>
+        <v>0.22</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T13:57:24.025Z</v>
+        <v>2026-07-30T14:06:45.534Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T13:57:25.025Z</v>
+        <v>2026-07-30T14:06:46.534Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T13:57:26.025Z</v>
+        <v>2026-07-30T14:06:47.534Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>0.4</v>
+        <v>1.82</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T13:57:27.025Z</v>
+        <v>2026-07-30T14:06:48.534Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>0.94</v>
+        <v>1.49</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T13:57:28.025Z</v>
+        <v>2026-07-30T14:06:49.534Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>0.25</v>
+        <v>1.85</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T13:57:29.025Z</v>
+        <v>2026-07-30T14:06:50.534Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T13:57:30.025Z</v>
+        <v>2026-07-30T14:06:51.534Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,10 +8145,10 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>1.08</v>
+        <v>1.92</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T13:57:31.025Z</v>
+        <v>2026-07-30T14:06:52.534Z</v>
       </c>
     </row>
     <row r="457">
@@ -8162,10 +8162,10 @@
         <v>Passed</v>
       </c>
       <c r="D457">
-        <v>0.94</v>
+        <v>1.35</v>
       </c>
       <c r="E457" t="str">
-        <v>2026-07-30T13:57:32.025Z</v>
+        <v>2026-07-30T14:06:53.534Z</v>
       </c>
     </row>
     <row r="458">
@@ -8179,10 +8179,10 @@
         <v>Passed</v>
       </c>
       <c r="D458">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="E458" t="str">
-        <v>2026-07-30T13:57:33.025Z</v>
+        <v>2026-07-30T14:06:54.534Z</v>
       </c>
     </row>
     <row r="459">
@@ -8196,10 +8196,10 @@
         <v>Passed</v>
       </c>
       <c r="D459">
-        <v>0.34</v>
+        <v>1.5</v>
       </c>
       <c r="E459" t="str">
-        <v>2026-07-30T13:57:34.025Z</v>
+        <v>2026-07-30T14:06:55.534Z</v>
       </c>
     </row>
     <row r="460">
@@ -8213,10 +8213,10 @@
         <v>Passed</v>
       </c>
       <c r="D460">
-        <v>0.56</v>
+        <v>1.27</v>
       </c>
       <c r="E460" t="str">
-        <v>2026-07-30T13:57:35.025Z</v>
+        <v>2026-07-30T14:06:56.534Z</v>
       </c>
     </row>
     <row r="461">
@@ -8230,10 +8230,10 @@
         <v>Passed</v>
       </c>
       <c r="D461">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="E461" t="str">
-        <v>2026-07-30T13:57:36.025Z</v>
+        <v>2026-07-30T14:06:57.534Z</v>
       </c>
     </row>
     <row r="462">
@@ -8247,10 +8247,10 @@
         <v>Passed</v>
       </c>
       <c r="D462">
-        <v>1.78</v>
+        <v>0.64</v>
       </c>
       <c r="E462" t="str">
-        <v>2026-07-30T13:57:37.025Z</v>
+        <v>2026-07-30T14:06:58.534Z</v>
       </c>
     </row>
     <row r="463">
@@ -8264,10 +8264,10 @@
         <v>Passed</v>
       </c>
       <c r="D463">
-        <v>1.22</v>
+        <v>0.33</v>
       </c>
       <c r="E463" t="str">
-        <v>2026-07-30T13:57:38.025Z</v>
+        <v>2026-07-30T14:06:59.534Z</v>
       </c>
     </row>
     <row r="464">
@@ -8281,10 +8281,10 @@
         <v>Passed</v>
       </c>
       <c r="D464">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="E464" t="str">
-        <v>2026-07-30T13:57:39.025Z</v>
+        <v>2026-07-30T14:07:00.534Z</v>
       </c>
     </row>
     <row r="465">
@@ -8298,10 +8298,10 @@
         <v>Passed</v>
       </c>
       <c r="D465">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="E465" t="str">
-        <v>2026-07-30T13:57:40.025Z</v>
+        <v>2026-07-30T14:07:01.534Z</v>
       </c>
     </row>
     <row r="466">
@@ -8312,13 +8312,13 @@
         <v>Verify APILoad functionality module 465</v>
       </c>
       <c r="C466" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D466">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E466" t="str">
-        <v>2026-07-30T13:57:41.025Z</v>
+        <v>2026-07-30T14:07:02.534Z</v>
       </c>
     </row>
     <row r="467">
@@ -8332,10 +8332,10 @@
         <v>Passed</v>
       </c>
       <c r="D467">
-        <v>0.62</v>
+        <v>1.13</v>
       </c>
       <c r="E467" t="str">
-        <v>2026-07-30T13:57:42.025Z</v>
+        <v>2026-07-30T14:07:03.534Z</v>
       </c>
     </row>
     <row r="468">
@@ -8349,10 +8349,10 @@
         <v>Passed</v>
       </c>
       <c r="D468">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="E468" t="str">
-        <v>2026-07-30T13:57:43.025Z</v>
+        <v>2026-07-30T14:07:04.534Z</v>
       </c>
     </row>
     <row r="469">
@@ -8366,10 +8366,10 @@
         <v>Passed</v>
       </c>
       <c r="D469">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="E469" t="str">
-        <v>2026-07-30T13:57:44.025Z</v>
+        <v>2026-07-30T14:07:05.534Z</v>
       </c>
     </row>
     <row r="470">
@@ -8383,10 +8383,10 @@
         <v>Passed</v>
       </c>
       <c r="D470">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="E470" t="str">
-        <v>2026-07-30T13:57:45.025Z</v>
+        <v>2026-07-30T14:07:06.534Z</v>
       </c>
     </row>
     <row r="471">
@@ -8400,10 +8400,10 @@
         <v>Passed</v>
       </c>
       <c r="D471">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="E471" t="str">
-        <v>2026-07-30T13:57:46.025Z</v>
+        <v>2026-07-30T14:07:07.534Z</v>
       </c>
     </row>
     <row r="472">
@@ -8417,10 +8417,10 @@
         <v>Passed</v>
       </c>
       <c r="D472">
-        <v>0.47</v>
+        <v>0.81</v>
       </c>
       <c r="E472" t="str">
-        <v>2026-07-30T13:57:47.025Z</v>
+        <v>2026-07-30T14:07:08.534Z</v>
       </c>
     </row>
     <row r="473">
@@ -8434,10 +8434,10 @@
         <v>Passed</v>
       </c>
       <c r="D473">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="E473" t="str">
-        <v>2026-07-30T13:57:48.025Z</v>
+        <v>2026-07-30T14:07:09.534Z</v>
       </c>
     </row>
     <row r="474">
@@ -8451,10 +8451,10 @@
         <v>Passed</v>
       </c>
       <c r="D474">
-        <v>1.79</v>
+        <v>0.73</v>
       </c>
       <c r="E474" t="str">
-        <v>2026-07-30T13:57:49.025Z</v>
+        <v>2026-07-30T14:07:10.534Z</v>
       </c>
     </row>
     <row r="475">
@@ -8468,10 +8468,10 @@
         <v>Passed</v>
       </c>
       <c r="D475">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="E475" t="str">
-        <v>2026-07-30T13:57:50.025Z</v>
+        <v>2026-07-30T14:07:11.534Z</v>
       </c>
     </row>
     <row r="476">
@@ -8485,10 +8485,10 @@
         <v>Passed</v>
       </c>
       <c r="D476">
-        <v>0.07</v>
+        <v>0.92</v>
       </c>
       <c r="E476" t="str">
-        <v>2026-07-30T13:57:51.025Z</v>
+        <v>2026-07-30T14:07:12.534Z</v>
       </c>
     </row>
     <row r="477">
@@ -8502,10 +8502,10 @@
         <v>Passed</v>
       </c>
       <c r="D477">
-        <v>0.36</v>
+        <v>1.44</v>
       </c>
       <c r="E477" t="str">
-        <v>2026-07-30T13:57:52.025Z</v>
+        <v>2026-07-30T14:07:13.534Z</v>
       </c>
     </row>
     <row r="478">
@@ -8519,10 +8519,10 @@
         <v>Passed</v>
       </c>
       <c r="D478">
-        <v>0.86</v>
+        <v>1.47</v>
       </c>
       <c r="E478" t="str">
-        <v>2026-07-30T13:57:53.025Z</v>
+        <v>2026-07-30T14:07:14.534Z</v>
       </c>
     </row>
     <row r="479">
@@ -8536,10 +8536,10 @@
         <v>Passed</v>
       </c>
       <c r="D479">
-        <v>1.59</v>
+        <v>0.17</v>
       </c>
       <c r="E479" t="str">
-        <v>2026-07-30T13:57:54.025Z</v>
+        <v>2026-07-30T14:07:15.534Z</v>
       </c>
     </row>
     <row r="480">
@@ -8553,10 +8553,10 @@
         <v>Passed</v>
       </c>
       <c r="D480">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E480" t="str">
-        <v>2026-07-30T13:57:55.025Z</v>
+        <v>2026-07-30T14:07:16.534Z</v>
       </c>
     </row>
     <row r="481">
@@ -8570,10 +8570,10 @@
         <v>Passed</v>
       </c>
       <c r="D481">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="E481" t="str">
-        <v>2026-07-30T13:57:56.025Z</v>
+        <v>2026-07-30T14:07:17.534Z</v>
       </c>
     </row>
     <row r="482">
@@ -8587,10 +8587,10 @@
         <v>Passed</v>
       </c>
       <c r="D482">
-        <v>0.91</v>
+        <v>1.12</v>
       </c>
       <c r="E482" t="str">
-        <v>2026-07-30T13:57:57.025Z</v>
+        <v>2026-07-30T14:07:18.534Z</v>
       </c>
     </row>
     <row r="483">
@@ -8604,10 +8604,10 @@
         <v>Passed</v>
       </c>
       <c r="D483">
-        <v>0.02</v>
+        <v>0.47</v>
       </c>
       <c r="E483" t="str">
-        <v>2026-07-30T13:57:58.025Z</v>
+        <v>2026-07-30T14:07:19.534Z</v>
       </c>
     </row>
     <row r="484">
@@ -8621,10 +8621,10 @@
         <v>Passed</v>
       </c>
       <c r="D484">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="E484" t="str">
-        <v>2026-07-30T13:57:59.025Z</v>
+        <v>2026-07-30T14:07:20.534Z</v>
       </c>
     </row>
     <row r="485">
@@ -8638,10 +8638,10 @@
         <v>Passed</v>
       </c>
       <c r="D485">
-        <v>1.83</v>
+        <v>0.31</v>
       </c>
       <c r="E485" t="str">
-        <v>2026-07-30T13:58:00.025Z</v>
+        <v>2026-07-30T14:07:21.534Z</v>
       </c>
     </row>
     <row r="486">
@@ -8655,10 +8655,10 @@
         <v>Passed</v>
       </c>
       <c r="D486">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="E486" t="str">
-        <v>2026-07-30T13:58:01.025Z</v>
+        <v>2026-07-30T14:07:22.534Z</v>
       </c>
     </row>
     <row r="487">
@@ -8669,13 +8669,13 @@
         <v>Verify APILoad functionality module 486</v>
       </c>
       <c r="C487" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D487">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="E487" t="str">
-        <v>2026-07-30T13:58:02.025Z</v>
+        <v>2026-07-30T14:07:23.534Z</v>
       </c>
     </row>
     <row r="488">
@@ -8689,10 +8689,10 @@
         <v>Passed</v>
       </c>
       <c r="D488">
-        <v>0.44</v>
+        <v>1.52</v>
       </c>
       <c r="E488" t="str">
-        <v>2026-07-30T13:58:03.025Z</v>
+        <v>2026-07-30T14:07:24.534Z</v>
       </c>
     </row>
     <row r="489">
@@ -8706,10 +8706,10 @@
         <v>Passed</v>
       </c>
       <c r="D489">
-        <v>0.91</v>
+        <v>0.26</v>
       </c>
       <c r="E489" t="str">
-        <v>2026-07-30T13:58:04.025Z</v>
+        <v>2026-07-30T14:07:25.534Z</v>
       </c>
     </row>
     <row r="490">
@@ -8723,10 +8723,10 @@
         <v>Passed</v>
       </c>
       <c r="D490">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="E490" t="str">
-        <v>2026-07-30T13:58:05.025Z</v>
+        <v>2026-07-30T14:07:26.534Z</v>
       </c>
     </row>
     <row r="491">
@@ -8737,13 +8737,13 @@
         <v>Verify APILoad functionality module 490</v>
       </c>
       <c r="C491" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D491">
-        <v>0.45</v>
+        <v>1.16</v>
       </c>
       <c r="E491" t="str">
-        <v>2026-07-30T13:58:06.025Z</v>
+        <v>2026-07-30T14:07:27.534Z</v>
       </c>
     </row>
     <row r="492">
@@ -8757,10 +8757,10 @@
         <v>Passed</v>
       </c>
       <c r="D492">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="E492" t="str">
-        <v>2026-07-30T13:58:07.025Z</v>
+        <v>2026-07-30T14:07:28.534Z</v>
       </c>
     </row>
     <row r="493">
@@ -8771,13 +8771,13 @@
         <v>Verify APILoad functionality module 492</v>
       </c>
       <c r="C493" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D493">
-        <v>1.28</v>
+        <v>0.53</v>
       </c>
       <c r="E493" t="str">
-        <v>2026-07-30T13:58:08.025Z</v>
+        <v>2026-07-30T14:07:29.534Z</v>
       </c>
     </row>
     <row r="494">
@@ -8791,10 +8791,10 @@
         <v>Passed</v>
       </c>
       <c r="D494">
-        <v>1.4</v>
+        <v>0.03</v>
       </c>
       <c r="E494" t="str">
-        <v>2026-07-30T13:58:09.025Z</v>
+        <v>2026-07-30T14:07:30.534Z</v>
       </c>
     </row>
     <row r="495">
@@ -8808,10 +8808,10 @@
         <v>Passed</v>
       </c>
       <c r="D495">
-        <v>0.74</v>
+        <v>1.54</v>
       </c>
       <c r="E495" t="str">
-        <v>2026-07-30T13:58:10.025Z</v>
+        <v>2026-07-30T14:07:31.534Z</v>
       </c>
     </row>
     <row r="496">
@@ -8825,10 +8825,10 @@
         <v>Passed</v>
       </c>
       <c r="D496">
-        <v>0.5</v>
+        <v>0.56</v>
       </c>
       <c r="E496" t="str">
-        <v>2026-07-30T13:58:11.025Z</v>
+        <v>2026-07-30T14:07:32.534Z</v>
       </c>
     </row>
     <row r="497">
@@ -8842,10 +8842,10 @@
         <v>Passed</v>
       </c>
       <c r="D497">
-        <v>1.41</v>
+        <v>0.31</v>
       </c>
       <c r="E497" t="str">
-        <v>2026-07-30T13:58:12.025Z</v>
+        <v>2026-07-30T14:07:33.534Z</v>
       </c>
     </row>
     <row r="498">
@@ -8859,10 +8859,10 @@
         <v>Passed</v>
       </c>
       <c r="D498">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="E498" t="str">
-        <v>2026-07-30T13:58:13.025Z</v>
+        <v>2026-07-30T14:07:34.534Z</v>
       </c>
     </row>
     <row r="499">
@@ -8876,10 +8876,10 @@
         <v>Passed</v>
       </c>
       <c r="D499">
-        <v>1.93</v>
+        <v>0.85</v>
       </c>
       <c r="E499" t="str">
-        <v>2026-07-30T13:58:14.025Z</v>
+        <v>2026-07-30T14:07:35.534Z</v>
       </c>
     </row>
     <row r="500">
@@ -8893,10 +8893,10 @@
         <v>Passed</v>
       </c>
       <c r="D500">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="E500" t="str">
-        <v>2026-07-30T13:58:15.025Z</v>
+        <v>2026-07-30T14:07:36.534Z</v>
       </c>
     </row>
     <row r="501">
@@ -8910,10 +8910,10 @@
         <v>Passed</v>
       </c>
       <c r="D501">
-        <v>0.92</v>
+        <v>1.74</v>
       </c>
       <c r="E501" t="str">
-        <v>2026-07-30T13:58:16.025Z</v>
+        <v>2026-07-30T14:07:37.534Z</v>
       </c>
     </row>
     <row r="502">
@@ -8927,10 +8927,10 @@
         <v>Passed</v>
       </c>
       <c r="D502">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="E502" t="str">
-        <v>2026-07-30T13:58:17.025Z</v>
+        <v>2026-07-30T14:07:38.534Z</v>
       </c>
     </row>
     <row r="503">
@@ -8944,10 +8944,10 @@
         <v>Passed</v>
       </c>
       <c r="D503">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="E503" t="str">
-        <v>2026-07-30T13:58:18.025Z</v>
+        <v>2026-07-30T14:07:39.534Z</v>
       </c>
     </row>
     <row r="504">
@@ -8961,10 +8961,10 @@
         <v>Passed</v>
       </c>
       <c r="D504">
-        <v>0.66</v>
+        <v>1.68</v>
       </c>
       <c r="E504" t="str">
-        <v>2026-07-30T13:58:19.025Z</v>
+        <v>2026-07-30T14:07:40.534Z</v>
       </c>
     </row>
     <row r="505">
@@ -8978,10 +8978,10 @@
         <v>Passed</v>
       </c>
       <c r="D505">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="E505" t="str">
-        <v>2026-07-30T13:58:20.025Z</v>
+        <v>2026-07-30T14:07:41.534Z</v>
       </c>
     </row>
     <row r="506">
@@ -8995,10 +8995,10 @@
         <v>Passed</v>
       </c>
       <c r="D506">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E506" t="str">
-        <v>2026-07-30T13:58:21.025Z</v>
+        <v>2026-07-30T14:07:42.534Z</v>
       </c>
     </row>
     <row r="507">
@@ -9012,10 +9012,10 @@
         <v>Passed</v>
       </c>
       <c r="D507">
-        <v>0.41</v>
+        <v>1.44</v>
       </c>
       <c r="E507" t="str">
-        <v>2026-07-30T13:58:22.025Z</v>
+        <v>2026-07-30T14:07:43.534Z</v>
       </c>
     </row>
     <row r="508">
@@ -9029,10 +9029,10 @@
         <v>Passed</v>
       </c>
       <c r="D508">
-        <v>0.63</v>
+        <v>1.2</v>
       </c>
       <c r="E508" t="str">
-        <v>2026-07-30T13:58:23.025Z</v>
+        <v>2026-07-30T14:07:44.534Z</v>
       </c>
     </row>
     <row r="509">
@@ -9046,10 +9046,10 @@
         <v>Passed</v>
       </c>
       <c r="D509">
-        <v>1.8</v>
+        <v>0.11</v>
       </c>
       <c r="E509" t="str">
-        <v>2026-07-30T13:58:24.025Z</v>
+        <v>2026-07-30T14:07:45.534Z</v>
       </c>
     </row>
     <row r="510">
@@ -9063,10 +9063,10 @@
         <v>Passed</v>
       </c>
       <c r="D510">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="E510" t="str">
-        <v>2026-07-30T13:58:25.025Z</v>
+        <v>2026-07-30T14:07:46.534Z</v>
       </c>
     </row>
     <row r="511">
@@ -9080,10 +9080,10 @@
         <v>Passed</v>
       </c>
       <c r="D511">
-        <v>1.78</v>
+        <v>0.14</v>
       </c>
       <c r="E511" t="str">
-        <v>2026-07-30T13:58:26.025Z</v>
+        <v>2026-07-30T14:07:47.534Z</v>
       </c>
     </row>
     <row r="512">
@@ -9097,10 +9097,10 @@
         <v>Passed</v>
       </c>
       <c r="D512">
-        <v>1.7</v>
+        <v>0.56</v>
       </c>
       <c r="E512" t="str">
-        <v>2026-07-30T13:58:27.025Z</v>
+        <v>2026-07-30T14:07:48.534Z</v>
       </c>
     </row>
     <row r="513">
@@ -9114,10 +9114,10 @@
         <v>Passed</v>
       </c>
       <c r="D513">
-        <v>0.61</v>
+        <v>1.78</v>
       </c>
       <c r="E513" t="str">
-        <v>2026-07-30T13:58:28.025Z</v>
+        <v>2026-07-30T14:07:49.534Z</v>
       </c>
     </row>
     <row r="514">
@@ -9131,10 +9131,10 @@
         <v>Passed</v>
       </c>
       <c r="D514">
-        <v>0.08</v>
+        <v>1.77</v>
       </c>
       <c r="E514" t="str">
-        <v>2026-07-30T13:58:29.025Z</v>
+        <v>2026-07-30T14:07:50.534Z</v>
       </c>
     </row>
     <row r="515">
@@ -9148,10 +9148,10 @@
         <v>Passed</v>
       </c>
       <c r="D515">
-        <v>0.85</v>
+        <v>1.31</v>
       </c>
       <c r="E515" t="str">
-        <v>2026-07-30T13:58:30.025Z</v>
+        <v>2026-07-30T14:07:51.534Z</v>
       </c>
     </row>
     <row r="516">
@@ -9165,10 +9165,10 @@
         <v>Passed</v>
       </c>
       <c r="D516">
-        <v>0.49</v>
+        <v>0.74</v>
       </c>
       <c r="E516" t="str">
-        <v>2026-07-30T13:58:31.025Z</v>
+        <v>2026-07-30T14:07:52.534Z</v>
       </c>
     </row>
     <row r="517">
@@ -9182,10 +9182,10 @@
         <v>Passed</v>
       </c>
       <c r="D517">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="E517" t="str">
-        <v>2026-07-30T13:58:32.025Z</v>
+        <v>2026-07-30T14:07:53.534Z</v>
       </c>
     </row>
     <row r="518">
@@ -9199,10 +9199,10 @@
         <v>Passed</v>
       </c>
       <c r="D518">
-        <v>0.19</v>
+        <v>1.64</v>
       </c>
       <c r="E518" t="str">
-        <v>2026-07-30T13:58:33.025Z</v>
+        <v>2026-07-30T14:07:54.534Z</v>
       </c>
     </row>
     <row r="519">
@@ -9216,10 +9216,10 @@
         <v>Passed</v>
       </c>
       <c r="D519">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="E519" t="str">
-        <v>2026-07-30T13:58:34.025Z</v>
+        <v>2026-07-30T14:07:55.534Z</v>
       </c>
     </row>
     <row r="520">
@@ -9233,10 +9233,10 @@
         <v>Passed</v>
       </c>
       <c r="D520">
-        <v>1.31</v>
+        <v>0.38</v>
       </c>
       <c r="E520" t="str">
-        <v>2026-07-30T13:58:35.025Z</v>
+        <v>2026-07-30T14:07:56.534Z</v>
       </c>
     </row>
     <row r="521">
@@ -9250,10 +9250,10 @@
         <v>Passed</v>
       </c>
       <c r="D521">
-        <v>0.89</v>
+        <v>1.71</v>
       </c>
       <c r="E521" t="str">
-        <v>2026-07-30T13:58:36.025Z</v>
+        <v>2026-07-30T14:07:57.534Z</v>
       </c>
     </row>
     <row r="522">
@@ -9267,10 +9267,10 @@
         <v>Passed</v>
       </c>
       <c r="D522">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="E522" t="str">
-        <v>2026-07-30T13:58:37.025Z</v>
+        <v>2026-07-30T14:07:58.534Z</v>
       </c>
     </row>
     <row r="523">
@@ -9284,10 +9284,10 @@
         <v>Passed</v>
       </c>
       <c r="D523">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="E523" t="str">
-        <v>2026-07-30T13:58:38.025Z</v>
+        <v>2026-07-30T14:07:59.534Z</v>
       </c>
     </row>
     <row r="524">
@@ -9301,10 +9301,10 @@
         <v>Passed</v>
       </c>
       <c r="D524">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="E524" t="str">
-        <v>2026-07-30T13:58:39.025Z</v>
+        <v>2026-07-30T14:08:00.534Z</v>
       </c>
     </row>
     <row r="525">
@@ -9318,10 +9318,10 @@
         <v>Passed</v>
       </c>
       <c r="D525">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="E525" t="str">
-        <v>2026-07-30T13:58:40.025Z</v>
+        <v>2026-07-30T14:08:01.534Z</v>
       </c>
     </row>
     <row r="526">
@@ -9335,10 +9335,10 @@
         <v>Passed</v>
       </c>
       <c r="D526">
-        <v>1.63</v>
+        <v>0.01</v>
       </c>
       <c r="E526" t="str">
-        <v>2026-07-30T13:58:41.025Z</v>
+        <v>2026-07-30T14:08:02.534Z</v>
       </c>
     </row>
     <row r="527">
@@ -9352,10 +9352,10 @@
         <v>Passed</v>
       </c>
       <c r="D527">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="E527" t="str">
-        <v>2026-07-30T13:58:42.025Z</v>
+        <v>2026-07-30T14:08:03.534Z</v>
       </c>
     </row>
     <row r="528">
@@ -9369,10 +9369,10 @@
         <v>Passed</v>
       </c>
       <c r="D528">
-        <v>0.33</v>
+        <v>1.98</v>
       </c>
       <c r="E528" t="str">
-        <v>2026-07-30T13:58:43.025Z</v>
+        <v>2026-07-30T14:08:04.534Z</v>
       </c>
     </row>
     <row r="529">
@@ -9386,10 +9386,10 @@
         <v>Passed</v>
       </c>
       <c r="D529">
-        <v>0.81</v>
+        <v>0.46</v>
       </c>
       <c r="E529" t="str">
-        <v>2026-07-30T13:58:44.025Z</v>
+        <v>2026-07-30T14:08:05.534Z</v>
       </c>
     </row>
     <row r="530">
@@ -9403,10 +9403,10 @@
         <v>Passed</v>
       </c>
       <c r="D530">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="E530" t="str">
-        <v>2026-07-30T13:58:45.025Z</v>
+        <v>2026-07-30T14:08:06.534Z</v>
       </c>
     </row>
     <row r="531">
@@ -9420,10 +9420,10 @@
         <v>Passed</v>
       </c>
       <c r="D531">
-        <v>1.22</v>
+        <v>0.39</v>
       </c>
       <c r="E531" t="str">
-        <v>2026-07-30T13:58:46.025Z</v>
+        <v>2026-07-30T14:08:07.534Z</v>
       </c>
     </row>
     <row r="532">
@@ -9437,10 +9437,10 @@
         <v>Passed</v>
       </c>
       <c r="D532">
-        <v>1.99</v>
+        <v>0.49</v>
       </c>
       <c r="E532" t="str">
-        <v>2026-07-30T13:58:47.025Z</v>
+        <v>2026-07-30T14:08:08.534Z</v>
       </c>
     </row>
     <row r="533">
@@ -9454,10 +9454,10 @@
         <v>Passed</v>
       </c>
       <c r="D533">
-        <v>1.15</v>
+        <v>0.47</v>
       </c>
       <c r="E533" t="str">
-        <v>2026-07-30T13:58:48.025Z</v>
+        <v>2026-07-30T14:08:09.534Z</v>
       </c>
     </row>
     <row r="534">
@@ -9471,10 +9471,10 @@
         <v>Passed</v>
       </c>
       <c r="D534">
-        <v>0.56</v>
+        <v>1.55</v>
       </c>
       <c r="E534" t="str">
-        <v>2026-07-30T13:58:49.025Z</v>
+        <v>2026-07-30T14:08:10.534Z</v>
       </c>
     </row>
     <row r="535">
@@ -9488,10 +9488,10 @@
         <v>Passed</v>
       </c>
       <c r="D535">
-        <v>0.34</v>
+        <v>0.58</v>
       </c>
       <c r="E535" t="str">
-        <v>2026-07-30T13:58:50.025Z</v>
+        <v>2026-07-30T14:08:11.534Z</v>
       </c>
     </row>
     <row r="536">
@@ -9505,10 +9505,10 @@
         <v>Passed</v>
       </c>
       <c r="D536">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="E536" t="str">
-        <v>2026-07-30T13:58:51.025Z</v>
+        <v>2026-07-30T14:08:12.534Z</v>
       </c>
     </row>
     <row r="537">
@@ -9522,10 +9522,10 @@
         <v>Passed</v>
       </c>
       <c r="D537">
-        <v>1.1</v>
+        <v>0.25</v>
       </c>
       <c r="E537" t="str">
-        <v>2026-07-30T13:58:52.025Z</v>
+        <v>2026-07-30T14:08:13.534Z</v>
       </c>
     </row>
     <row r="538">
@@ -9539,10 +9539,10 @@
         <v>Passed</v>
       </c>
       <c r="D538">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="E538" t="str">
-        <v>2026-07-30T13:58:53.025Z</v>
+        <v>2026-07-30T14:08:14.534Z</v>
       </c>
     </row>
     <row r="539">
@@ -9556,10 +9556,10 @@
         <v>Passed</v>
       </c>
       <c r="D539">
-        <v>1.62</v>
+        <v>0.97</v>
       </c>
       <c r="E539" t="str">
-        <v>2026-07-30T13:58:54.025Z</v>
+        <v>2026-07-30T14:08:15.534Z</v>
       </c>
     </row>
     <row r="540">
@@ -9570,13 +9570,13 @@
         <v>Verify APILoad functionality module 539</v>
       </c>
       <c r="C540" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D540">
-        <v>0.86</v>
+        <v>1.48</v>
       </c>
       <c r="E540" t="str">
-        <v>2026-07-30T13:58:55.025Z</v>
+        <v>2026-07-30T14:08:16.534Z</v>
       </c>
     </row>
     <row r="541">
@@ -9590,10 +9590,10 @@
         <v>Passed</v>
       </c>
       <c r="D541">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="E541" t="str">
-        <v>2026-07-30T13:58:56.025Z</v>
+        <v>2026-07-30T14:08:17.534Z</v>
       </c>
     </row>
     <row r="542">
@@ -9607,10 +9607,10 @@
         <v>Passed</v>
       </c>
       <c r="D542">
-        <v>1.84</v>
+        <v>0.09</v>
       </c>
       <c r="E542" t="str">
-        <v>2026-07-30T13:58:57.025Z</v>
+        <v>2026-07-30T14:08:18.534Z</v>
       </c>
     </row>
     <row r="543">
@@ -9624,10 +9624,10 @@
         <v>Passed</v>
       </c>
       <c r="D543">
-        <v>0.34</v>
+        <v>1.57</v>
       </c>
       <c r="E543" t="str">
-        <v>2026-07-30T13:58:58.025Z</v>
+        <v>2026-07-30T14:08:19.534Z</v>
       </c>
     </row>
     <row r="544">
@@ -9641,10 +9641,10 @@
         <v>Passed</v>
       </c>
       <c r="D544">
-        <v>0.06</v>
+        <v>1.57</v>
       </c>
       <c r="E544" t="str">
-        <v>2026-07-30T13:58:59.025Z</v>
+        <v>2026-07-30T14:08:20.534Z</v>
       </c>
     </row>
     <row r="545">
@@ -9658,10 +9658,10 @@
         <v>Passed</v>
       </c>
       <c r="D545">
-        <v>0.73</v>
+        <v>1.5</v>
       </c>
       <c r="E545" t="str">
-        <v>2026-07-30T13:59:00.025Z</v>
+        <v>2026-07-30T14:08:21.534Z</v>
       </c>
     </row>
     <row r="546">
@@ -9675,10 +9675,10 @@
         <v>Passed</v>
       </c>
       <c r="D546">
-        <v>0.81</v>
+        <v>1.97</v>
       </c>
       <c r="E546" t="str">
-        <v>2026-07-30T13:59:01.025Z</v>
+        <v>2026-07-30T14:08:22.534Z</v>
       </c>
     </row>
     <row r="547">
@@ -9692,10 +9692,10 @@
         <v>Passed</v>
       </c>
       <c r="D547">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="E547" t="str">
-        <v>2026-07-30T13:59:02.025Z</v>
+        <v>2026-07-30T14:08:23.534Z</v>
       </c>
     </row>
     <row r="548">
@@ -9709,10 +9709,10 @@
         <v>Passed</v>
       </c>
       <c r="D548">
-        <v>0.69</v>
+        <v>0.76</v>
       </c>
       <c r="E548" t="str">
-        <v>2026-07-30T13:59:03.025Z</v>
+        <v>2026-07-30T14:08:24.534Z</v>
       </c>
     </row>
     <row r="549">
@@ -9726,10 +9726,10 @@
         <v>Passed</v>
       </c>
       <c r="D549">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="E549" t="str">
-        <v>2026-07-30T13:59:04.025Z</v>
+        <v>2026-07-30T14:08:25.534Z</v>
       </c>
     </row>
     <row r="550">
@@ -9743,10 +9743,10 @@
         <v>Passed</v>
       </c>
       <c r="D550">
-        <v>1.99</v>
+        <v>0.28</v>
       </c>
       <c r="E550" t="str">
-        <v>2026-07-30T13:59:05.025Z</v>
+        <v>2026-07-30T14:08:26.534Z</v>
       </c>
     </row>
     <row r="551">
@@ -9760,10 +9760,10 @@
         <v>Passed</v>
       </c>
       <c r="D551">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="E551" t="str">
-        <v>2026-07-30T13:59:06.025Z</v>
+        <v>2026-07-30T14:08:27.534Z</v>
       </c>
     </row>
     <row r="552">
@@ -9777,10 +9777,10 @@
         <v>Passed</v>
       </c>
       <c r="D552">
-        <v>0.43</v>
+        <v>0.05</v>
       </c>
       <c r="E552" t="str">
-        <v>2026-07-30T13:59:07.025Z</v>
+        <v>2026-07-30T14:08:28.534Z</v>
       </c>
     </row>
     <row r="553">
@@ -9794,10 +9794,10 @@
         <v>Passed</v>
       </c>
       <c r="D553">
-        <v>0.74</v>
+        <v>1.42</v>
       </c>
       <c r="E553" t="str">
-        <v>2026-07-30T13:59:08.025Z</v>
+        <v>2026-07-30T14:08:29.534Z</v>
       </c>
     </row>
     <row r="554">
@@ -9811,10 +9811,10 @@
         <v>Passed</v>
       </c>
       <c r="D554">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="E554" t="str">
-        <v>2026-07-30T13:59:09.025Z</v>
+        <v>2026-07-30T14:08:30.534Z</v>
       </c>
     </row>
     <row r="555">
@@ -9828,10 +9828,10 @@
         <v>Passed</v>
       </c>
       <c r="D555">
-        <v>1.42</v>
+        <v>0.07</v>
       </c>
       <c r="E555" t="str">
-        <v>2026-07-30T13:59:10.025Z</v>
+        <v>2026-07-30T14:08:31.534Z</v>
       </c>
     </row>
     <row r="556">
@@ -9845,10 +9845,10 @@
         <v>Passed</v>
       </c>
       <c r="D556">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="E556" t="str">
-        <v>2026-07-30T13:59:11.025Z</v>
+        <v>2026-07-30T14:08:32.534Z</v>
       </c>
     </row>
     <row r="557">
@@ -9862,10 +9862,10 @@
         <v>Passed</v>
       </c>
       <c r="D557">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="E557" t="str">
-        <v>2026-07-30T13:59:12.025Z</v>
+        <v>2026-07-30T14:08:33.534Z</v>
       </c>
     </row>
     <row r="558">
@@ -9879,10 +9879,10 @@
         <v>Passed</v>
       </c>
       <c r="D558">
-        <v>0.67</v>
+        <v>0.99</v>
       </c>
       <c r="E558" t="str">
-        <v>2026-07-30T13:59:13.025Z</v>
+        <v>2026-07-30T14:08:34.534Z</v>
       </c>
     </row>
     <row r="559">
@@ -9896,10 +9896,10 @@
         <v>Passed</v>
       </c>
       <c r="D559">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="E559" t="str">
-        <v>2026-07-30T13:59:14.025Z</v>
+        <v>2026-07-30T14:08:35.534Z</v>
       </c>
     </row>
     <row r="560">
@@ -9913,10 +9913,10 @@
         <v>Passed</v>
       </c>
       <c r="D560">
-        <v>1.91</v>
+        <v>0.21</v>
       </c>
       <c r="E560" t="str">
-        <v>2026-07-30T13:59:15.025Z</v>
+        <v>2026-07-30T14:08:36.534Z</v>
       </c>
     </row>
     <row r="561">
@@ -9930,10 +9930,10 @@
         <v>Passed</v>
       </c>
       <c r="D561">
-        <v>1.12</v>
+        <v>1.86</v>
       </c>
       <c r="E561" t="str">
-        <v>2026-07-30T13:59:16.025Z</v>
+        <v>2026-07-30T14:08:37.534Z</v>
       </c>
     </row>
     <row r="562">
@@ -9947,10 +9947,10 @@
         <v>Passed</v>
       </c>
       <c r="D562">
-        <v>0.97</v>
+        <v>1.99</v>
       </c>
       <c r="E562" t="str">
-        <v>2026-07-30T13:59:17.025Z</v>
+        <v>2026-07-30T14:08:38.534Z</v>
       </c>
     </row>
     <row r="563">
@@ -9964,10 +9964,10 @@
         <v>Passed</v>
       </c>
       <c r="D563">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="E563" t="str">
-        <v>2026-07-30T13:59:18.025Z</v>
+        <v>2026-07-30T14:08:39.534Z</v>
       </c>
     </row>
     <row r="564">
@@ -9981,10 +9981,10 @@
         <v>Passed</v>
       </c>
       <c r="D564">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="E564" t="str">
-        <v>2026-07-30T13:59:19.025Z</v>
+        <v>2026-07-30T14:08:40.534Z</v>
       </c>
     </row>
     <row r="565">
@@ -9998,10 +9998,10 @@
         <v>Passed</v>
       </c>
       <c r="D565">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="E565" t="str">
-        <v>2026-07-30T13:59:20.025Z</v>
+        <v>2026-07-30T14:08:41.534Z</v>
       </c>
     </row>
     <row r="566">
@@ -10015,10 +10015,10 @@
         <v>Passed</v>
       </c>
       <c r="D566">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="E566" t="str">
-        <v>2026-07-30T13:59:21.025Z</v>
+        <v>2026-07-30T14:08:42.534Z</v>
       </c>
     </row>
     <row r="567">
@@ -10032,10 +10032,10 @@
         <v>Passed</v>
       </c>
       <c r="D567">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="E567" t="str">
-        <v>2026-07-30T13:59:22.025Z</v>
+        <v>2026-07-30T14:08:43.534Z</v>
       </c>
     </row>
     <row r="568">
@@ -10052,7 +10052,7 @@
         <v>0.88</v>
       </c>
       <c r="E568" t="str">
-        <v>2026-07-30T13:59:23.025Z</v>
+        <v>2026-07-30T14:08:44.534Z</v>
       </c>
     </row>
     <row r="569">
@@ -10066,10 +10066,10 @@
         <v>Passed</v>
       </c>
       <c r="D569">
-        <v>0.3</v>
+        <v>0.07</v>
       </c>
       <c r="E569" t="str">
-        <v>2026-07-30T13:59:24.025Z</v>
+        <v>2026-07-30T14:08:45.534Z</v>
       </c>
     </row>
     <row r="570">
@@ -10083,10 +10083,10 @@
         <v>Passed</v>
       </c>
       <c r="D570">
-        <v>1.09</v>
+        <v>1.69</v>
       </c>
       <c r="E570" t="str">
-        <v>2026-07-30T13:59:25.025Z</v>
+        <v>2026-07-30T14:08:46.534Z</v>
       </c>
     </row>
     <row r="571">
@@ -10100,10 +10100,10 @@
         <v>Passed</v>
       </c>
       <c r="D571">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="E571" t="str">
-        <v>2026-07-30T13:59:26.025Z</v>
+        <v>2026-07-30T14:08:47.534Z</v>
       </c>
     </row>
     <row r="572">
@@ -10117,10 +10117,10 @@
         <v>Passed</v>
       </c>
       <c r="D572">
-        <v>0.14</v>
+        <v>1.45</v>
       </c>
       <c r="E572" t="str">
-        <v>2026-07-30T13:59:27.025Z</v>
+        <v>2026-07-30T14:08:48.534Z</v>
       </c>
     </row>
     <row r="573">
@@ -10134,10 +10134,10 @@
         <v>Passed</v>
       </c>
       <c r="D573">
-        <v>0.69</v>
+        <v>1.16</v>
       </c>
       <c r="E573" t="str">
-        <v>2026-07-30T13:59:28.025Z</v>
+        <v>2026-07-30T14:08:49.534Z</v>
       </c>
     </row>
     <row r="574">
@@ -10151,10 +10151,10 @@
         <v>Passed</v>
       </c>
       <c r="D574">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="E574" t="str">
-        <v>2026-07-30T13:59:29.025Z</v>
+        <v>2026-07-30T14:08:50.534Z</v>
       </c>
     </row>
     <row r="575">
@@ -10165,13 +10165,13 @@
         <v>Verify APILoad functionality module 574</v>
       </c>
       <c r="C575" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D575">
-        <v>0.54</v>
+        <v>1.12</v>
       </c>
       <c r="E575" t="str">
-        <v>2026-07-30T13:59:30.025Z</v>
+        <v>2026-07-30T14:08:51.534Z</v>
       </c>
     </row>
     <row r="576">
@@ -10185,10 +10185,10 @@
         <v>Passed</v>
       </c>
       <c r="D576">
-        <v>0.15</v>
+        <v>1.54</v>
       </c>
       <c r="E576" t="str">
-        <v>2026-07-30T13:59:31.025Z</v>
+        <v>2026-07-30T14:08:52.534Z</v>
       </c>
     </row>
     <row r="577">
@@ -10202,10 +10202,10 @@
         <v>Passed</v>
       </c>
       <c r="D577">
-        <v>0.96</v>
+        <v>0.34</v>
       </c>
       <c r="E577" t="str">
-        <v>2026-07-30T13:59:32.025Z</v>
+        <v>2026-07-30T14:08:53.534Z</v>
       </c>
     </row>
     <row r="578">
@@ -10219,10 +10219,10 @@
         <v>Passed</v>
       </c>
       <c r="D578">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="E578" t="str">
-        <v>2026-07-30T13:59:33.025Z</v>
+        <v>2026-07-30T14:08:54.534Z</v>
       </c>
     </row>
     <row r="579">
@@ -10236,10 +10236,10 @@
         <v>Passed</v>
       </c>
       <c r="D579">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="E579" t="str">
-        <v>2026-07-30T13:59:34.025Z</v>
+        <v>2026-07-30T14:08:55.534Z</v>
       </c>
     </row>
     <row r="580">
@@ -10253,10 +10253,10 @@
         <v>Passed</v>
       </c>
       <c r="D580">
-        <v>0.01</v>
+        <v>1.29</v>
       </c>
       <c r="E580" t="str">
-        <v>2026-07-30T13:59:35.025Z</v>
+        <v>2026-07-30T14:08:56.534Z</v>
       </c>
     </row>
     <row r="581">
@@ -10270,10 +10270,10 @@
         <v>Passed</v>
       </c>
       <c r="D581">
-        <v>0.7</v>
+        <v>1.71</v>
       </c>
       <c r="E581" t="str">
-        <v>2026-07-30T13:59:36.025Z</v>
+        <v>2026-07-30T14:08:57.534Z</v>
       </c>
     </row>
     <row r="582">
@@ -10287,10 +10287,10 @@
         <v>Passed</v>
       </c>
       <c r="D582">
-        <v>1.34</v>
+        <v>0.38</v>
       </c>
       <c r="E582" t="str">
-        <v>2026-07-30T13:59:37.025Z</v>
+        <v>2026-07-30T14:08:58.534Z</v>
       </c>
     </row>
     <row r="583">
@@ -10304,10 +10304,10 @@
         <v>Passed</v>
       </c>
       <c r="D583">
-        <v>0.95</v>
+        <v>0.12</v>
       </c>
       <c r="E583" t="str">
-        <v>2026-07-30T13:59:38.025Z</v>
+        <v>2026-07-30T14:08:59.534Z</v>
       </c>
     </row>
     <row r="584">
@@ -10324,7 +10324,7 @@
         <v>0.4</v>
       </c>
       <c r="E584" t="str">
-        <v>2026-07-30T13:59:39.025Z</v>
+        <v>2026-07-30T14:09:00.534Z</v>
       </c>
     </row>
     <row r="585">
@@ -10338,10 +10338,10 @@
         <v>Passed</v>
       </c>
       <c r="D585">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="E585" t="str">
-        <v>2026-07-30T13:59:40.025Z</v>
+        <v>2026-07-30T14:09:01.534Z</v>
       </c>
     </row>
     <row r="586">
@@ -10355,10 +10355,10 @@
         <v>Passed</v>
       </c>
       <c r="D586">
-        <v>1</v>
+        <v>0.81</v>
       </c>
       <c r="E586" t="str">
-        <v>2026-07-30T13:59:41.025Z</v>
+        <v>2026-07-30T14:09:02.534Z</v>
       </c>
     </row>
     <row r="587">
@@ -10372,10 +10372,10 @@
         <v>Passed</v>
       </c>
       <c r="D587">
-        <v>1.32</v>
+        <v>0.86</v>
       </c>
       <c r="E587" t="str">
-        <v>2026-07-30T13:59:42.025Z</v>
+        <v>2026-07-30T14:09:03.534Z</v>
       </c>
     </row>
     <row r="588">
@@ -10389,10 +10389,10 @@
         <v>Passed</v>
       </c>
       <c r="D588">
-        <v>0.73</v>
+        <v>0.25</v>
       </c>
       <c r="E588" t="str">
-        <v>2026-07-30T13:59:43.025Z</v>
+        <v>2026-07-30T14:09:04.534Z</v>
       </c>
     </row>
     <row r="589">
@@ -10406,10 +10406,10 @@
         <v>Passed</v>
       </c>
       <c r="D589">
-        <v>0.69</v>
+        <v>1.02</v>
       </c>
       <c r="E589" t="str">
-        <v>2026-07-30T13:59:44.025Z</v>
+        <v>2026-07-30T14:09:05.534Z</v>
       </c>
     </row>
     <row r="590">
@@ -10423,10 +10423,10 @@
         <v>Passed</v>
       </c>
       <c r="D590">
-        <v>0.43</v>
+        <v>1.4</v>
       </c>
       <c r="E590" t="str">
-        <v>2026-07-30T13:59:45.025Z</v>
+        <v>2026-07-30T14:09:06.534Z</v>
       </c>
     </row>
     <row r="591">
@@ -10440,10 +10440,10 @@
         <v>Passed</v>
       </c>
       <c r="D591">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="E591" t="str">
-        <v>2026-07-30T13:59:46.025Z</v>
+        <v>2026-07-30T14:09:07.534Z</v>
       </c>
     </row>
     <row r="592">
@@ -10457,10 +10457,10 @@
         <v>Passed</v>
       </c>
       <c r="D592">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="E592" t="str">
-        <v>2026-07-30T13:59:47.025Z</v>
+        <v>2026-07-30T14:09:08.534Z</v>
       </c>
     </row>
     <row r="593">
@@ -10474,10 +10474,10 @@
         <v>Passed</v>
       </c>
       <c r="D593">
-        <v>1.52</v>
+        <v>0.45</v>
       </c>
       <c r="E593" t="str">
-        <v>2026-07-30T13:59:48.025Z</v>
+        <v>2026-07-30T14:09:09.534Z</v>
       </c>
     </row>
     <row r="594">
@@ -10491,10 +10491,10 @@
         <v>Passed</v>
       </c>
       <c r="D594">
-        <v>1.82</v>
+        <v>0.28</v>
       </c>
       <c r="E594" t="str">
-        <v>2026-07-30T13:59:49.025Z</v>
+        <v>2026-07-30T14:09:10.534Z</v>
       </c>
     </row>
     <row r="595">
@@ -10508,10 +10508,10 @@
         <v>Passed</v>
       </c>
       <c r="D595">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="E595" t="str">
-        <v>2026-07-30T13:59:50.025Z</v>
+        <v>2026-07-30T14:09:11.534Z</v>
       </c>
     </row>
     <row r="596">
@@ -10525,10 +10525,10 @@
         <v>Passed</v>
       </c>
       <c r="D596">
-        <v>1.61</v>
+        <v>0.98</v>
       </c>
       <c r="E596" t="str">
-        <v>2026-07-30T13:59:51.025Z</v>
+        <v>2026-07-30T14:09:12.534Z</v>
       </c>
     </row>
     <row r="597">
@@ -10542,10 +10542,10 @@
         <v>Passed</v>
       </c>
       <c r="D597">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="E597" t="str">
-        <v>2026-07-30T13:59:52.025Z</v>
+        <v>2026-07-30T14:09:13.534Z</v>
       </c>
     </row>
     <row r="598">
@@ -10559,10 +10559,10 @@
         <v>Passed</v>
       </c>
       <c r="D598">
-        <v>0.27</v>
+        <v>1.59</v>
       </c>
       <c r="E598" t="str">
-        <v>2026-07-30T13:59:53.025Z</v>
+        <v>2026-07-30T14:09:14.534Z</v>
       </c>
     </row>
     <row r="599">
@@ -10576,10 +10576,10 @@
         <v>Passed</v>
       </c>
       <c r="D599">
-        <v>1.86</v>
+        <v>0.04</v>
       </c>
       <c r="E599" t="str">
-        <v>2026-07-30T13:59:54.025Z</v>
+        <v>2026-07-30T14:09:15.534Z</v>
       </c>
     </row>
     <row r="600">
@@ -10593,10 +10593,10 @@
         <v>Passed</v>
       </c>
       <c r="D600">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="E600" t="str">
-        <v>2026-07-30T13:59:55.025Z</v>
+        <v>2026-07-30T14:09:16.534Z</v>
       </c>
     </row>
     <row r="601">
@@ -10610,10 +10610,10 @@
         <v>Passed</v>
       </c>
       <c r="D601">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="E601" t="str">
-        <v>2026-07-30T13:59:56.025Z</v>
+        <v>2026-07-30T14:09:17.534Z</v>
       </c>
     </row>
     <row r="602">
@@ -10627,10 +10627,10 @@
         <v>Passed</v>
       </c>
       <c r="D602">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="E602" t="str">
-        <v>2026-07-30T13:59:57.025Z</v>
+        <v>2026-07-30T14:09:18.534Z</v>
       </c>
     </row>
     <row r="603">
@@ -10644,10 +10644,10 @@
         <v>Passed</v>
       </c>
       <c r="D603">
-        <v>0.81</v>
+        <v>0.97</v>
       </c>
       <c r="E603" t="str">
-        <v>2026-07-30T13:59:58.025Z</v>
+        <v>2026-07-30T14:09:19.534Z</v>
       </c>
     </row>
     <row r="604">
@@ -10661,10 +10661,10 @@
         <v>Passed</v>
       </c>
       <c r="D604">
-        <v>1.04</v>
+        <v>0.65</v>
       </c>
       <c r="E604" t="str">
-        <v>2026-07-30T13:59:59.025Z</v>
+        <v>2026-07-30T14:09:20.534Z</v>
       </c>
     </row>
     <row r="605">
@@ -10678,10 +10678,10 @@
         <v>Passed</v>
       </c>
       <c r="D605">
-        <v>1.4</v>
+        <v>0.92</v>
       </c>
       <c r="E605" t="str">
-        <v>2026-07-30T14:00:00.025Z</v>
+        <v>2026-07-30T14:09:21.534Z</v>
       </c>
     </row>
     <row r="606">
@@ -10695,10 +10695,10 @@
         <v>Passed</v>
       </c>
       <c r="D606">
-        <v>1.43</v>
+        <v>0.52</v>
       </c>
       <c r="E606" t="str">
-        <v>2026-07-30T14:00:01.025Z</v>
+        <v>2026-07-30T14:09:22.534Z</v>
       </c>
     </row>
     <row r="607">
@@ -10712,10 +10712,10 @@
         <v>Passed</v>
       </c>
       <c r="D607">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="E607" t="str">
-        <v>2026-07-30T14:00:02.025Z</v>
+        <v>2026-07-30T14:09:23.534Z</v>
       </c>
     </row>
     <row r="608">
@@ -10729,10 +10729,10 @@
         <v>Passed</v>
       </c>
       <c r="D608">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="E608" t="str">
-        <v>2026-07-30T14:00:03.025Z</v>
+        <v>2026-07-30T14:09:24.534Z</v>
       </c>
     </row>
     <row r="609">
@@ -10746,10 +10746,10 @@
         <v>Passed</v>
       </c>
       <c r="D609">
-        <v>1.41</v>
+        <v>0.85</v>
       </c>
       <c r="E609" t="str">
-        <v>2026-07-30T14:00:04.025Z</v>
+        <v>2026-07-30T14:09:25.534Z</v>
       </c>
     </row>
     <row r="610">
@@ -10763,15 +10763,236 @@
         <v>Passed</v>
       </c>
       <c r="D610">
-        <v>0.48</v>
+        <v>1.2</v>
       </c>
       <c r="E610" t="str">
-        <v>2026-07-30T14:00:05.025Z</v>
+        <v>2026-07-30T14:09:26.534Z</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>APILoad-TC-0610</v>
+      </c>
+      <c r="B611" t="str">
+        <v>Verify APILoad functionality module 610</v>
+      </c>
+      <c r="C611" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D611">
+        <v>0.14</v>
+      </c>
+      <c r="E611" t="str">
+        <v>2026-07-30T14:09:27.534Z</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v>APILoad-TC-0611</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Verify APILoad functionality module 611</v>
+      </c>
+      <c r="C612" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D612">
+        <v>0.24</v>
+      </c>
+      <c r="E612" t="str">
+        <v>2026-07-30T14:09:28.534Z</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>APILoad-TC-0612</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Verify APILoad functionality module 612</v>
+      </c>
+      <c r="C613" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D613">
+        <v>1.96</v>
+      </c>
+      <c r="E613" t="str">
+        <v>2026-07-30T14:09:29.534Z</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>APILoad-TC-0613</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Verify APILoad functionality module 613</v>
+      </c>
+      <c r="C614" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D614">
+        <v>1.44</v>
+      </c>
+      <c r="E614" t="str">
+        <v>2026-07-30T14:09:30.534Z</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>APILoad-TC-0614</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Verify APILoad functionality module 614</v>
+      </c>
+      <c r="C615" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D615">
+        <v>0.56</v>
+      </c>
+      <c r="E615" t="str">
+        <v>2026-07-30T14:09:31.534Z</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>APILoad-TC-0615</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Verify APILoad functionality module 615</v>
+      </c>
+      <c r="C616" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D616">
+        <v>0.24</v>
+      </c>
+      <c r="E616" t="str">
+        <v>2026-07-30T14:09:32.534Z</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>APILoad-TC-0616</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Verify APILoad functionality module 616</v>
+      </c>
+      <c r="C617" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D617">
+        <v>1.49</v>
+      </c>
+      <c r="E617" t="str">
+        <v>2026-07-30T14:09:33.534Z</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>APILoad-TC-0617</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Verify APILoad functionality module 617</v>
+      </c>
+      <c r="C618" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D618">
+        <v>1.68</v>
+      </c>
+      <c r="E618" t="str">
+        <v>2026-07-30T14:09:34.534Z</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>APILoad-TC-0618</v>
+      </c>
+      <c r="B619" t="str">
+        <v>Verify APILoad functionality module 618</v>
+      </c>
+      <c r="C619" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D619">
+        <v>0.59</v>
+      </c>
+      <c r="E619" t="str">
+        <v>2026-07-30T14:09:35.534Z</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>APILoad-TC-0619</v>
+      </c>
+      <c r="B620" t="str">
+        <v>Verify APILoad functionality module 619</v>
+      </c>
+      <c r="C620" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D620">
+        <v>0.87</v>
+      </c>
+      <c r="E620" t="str">
+        <v>2026-07-30T14:09:36.534Z</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>APILoad-TC-0620</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Verify APILoad functionality module 620</v>
+      </c>
+      <c r="C621" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D621">
+        <v>1.58</v>
+      </c>
+      <c r="E621" t="str">
+        <v>2026-07-30T14:09:37.534Z</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>APILoad-TC-0621</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Verify APILoad functionality module 621</v>
+      </c>
+      <c r="C622" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D622">
+        <v>1.63</v>
+      </c>
+      <c r="E622" t="str">
+        <v>2026-07-30T14:09:38.534Z</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>APILoad-TC-0622</v>
+      </c>
+      <c r="B623" t="str">
+        <v>Verify APILoad functionality module 622</v>
+      </c>
+      <c r="C623" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D623">
+        <v>1.57</v>
+      </c>
+      <c r="E623" t="str">
+        <v>2026-07-30T14:09:39.534Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E610"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E623"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest/load_testing/Load_Test_Report_Cognify_Latest.xlsx
+++ b/reports/latest/load_testing/Load_Test_Report_Cognify_Latest.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E623"/>
+  <dimension ref="A1:E601"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T13:59:18.534Z</v>
+        <v>2026-07-30T21:39:10.487Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T13:59:19.534Z</v>
+        <v>2026-07-30T21:39:11.487Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>0.23</v>
+        <v>1.97</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T13:59:20.534Z</v>
+        <v>2026-07-30T21:39:12.487Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T13:59:21.534Z</v>
+        <v>2026-07-30T21:39:13.487Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>1.35</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T13:59:22.534Z</v>
+        <v>2026-07-30T21:39:14.487Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>0.05</v>
+        <v>1.74</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T13:59:23.534Z</v>
+        <v>2026-07-30T21:39:15.487Z</v>
       </c>
     </row>
     <row r="8">
@@ -526,13 +526,13 @@
         <v>Verify APILoad functionality module 7</v>
       </c>
       <c r="C8" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D8">
-        <v>1.52</v>
+        <v>0.48</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T13:59:24.534Z</v>
+        <v>2026-07-30T21:39:16.487Z</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>Passed</v>
       </c>
       <c r="D9">
-        <v>0.95</v>
+        <v>1.53</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T13:59:25.534Z</v>
+        <v>2026-07-30T21:39:17.487Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>1.89</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T13:59:26.534Z</v>
+        <v>2026-07-30T21:39:18.487Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>1.5</v>
+        <v>0.48</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T13:59:27.534Z</v>
+        <v>2026-07-30T21:39:19.487Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T13:59:28.534Z</v>
+        <v>2026-07-30T21:39:20.487Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>0.75</v>
+        <v>0.18</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T13:59:29.534Z</v>
+        <v>2026-07-30T21:39:21.487Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>1.94</v>
+        <v>0.25</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T13:59:30.534Z</v>
+        <v>2026-07-30T21:39:22.487Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>1.94</v>
+        <v>1.1</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T13:59:31.534Z</v>
+        <v>2026-07-30T21:39:23.487Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>0.27</v>
+        <v>0.82</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T13:59:32.534Z</v>
+        <v>2026-07-30T21:39:24.487Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T13:59:33.534Z</v>
+        <v>2026-07-30T21:39:25.487Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>0.94</v>
+        <v>1.82</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T13:59:34.534Z</v>
+        <v>2026-07-30T21:39:26.487Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>0.37</v>
+        <v>0.84</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T13:59:35.534Z</v>
+        <v>2026-07-30T21:39:27.487Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T13:59:36.534Z</v>
+        <v>2026-07-30T21:39:28.487Z</v>
       </c>
     </row>
     <row r="21">
@@ -750,10 +750,10 @@
         <v>Passed</v>
       </c>
       <c r="D21">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T13:59:37.534Z</v>
+        <v>2026-07-30T21:39:29.487Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>1.13</v>
+        <v>0.4</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T13:59:38.534Z</v>
+        <v>2026-07-30T21:39:30.487Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T13:59:39.534Z</v>
+        <v>2026-07-30T21:39:31.487Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>0.07</v>
+        <v>0.65</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T13:59:40.534Z</v>
+        <v>2026-07-30T21:39:32.487Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>0.06</v>
+        <v>1.68</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T13:59:41.534Z</v>
+        <v>2026-07-30T21:39:33.487Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>1.26</v>
+        <v>0.11</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T13:59:42.534Z</v>
+        <v>2026-07-30T21:39:34.487Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>1.79</v>
+        <v>0.94</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T13:59:43.534Z</v>
+        <v>2026-07-30T21:39:35.487Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>1.8</v>
+        <v>0.47</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T13:59:44.534Z</v>
+        <v>2026-07-30T21:39:36.487Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T13:59:45.534Z</v>
+        <v>2026-07-30T21:39:37.487Z</v>
       </c>
     </row>
     <row r="30">
@@ -900,13 +900,13 @@
         <v>Verify APILoad functionality module 29</v>
       </c>
       <c r="C30" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D30">
-        <v>0.94</v>
+        <v>1.99</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T13:59:46.534Z</v>
+        <v>2026-07-30T21:39:38.487Z</v>
       </c>
     </row>
     <row r="31">
@@ -920,10 +920,10 @@
         <v>Passed</v>
       </c>
       <c r="D31">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T13:59:47.534Z</v>
+        <v>2026-07-30T21:39:39.487Z</v>
       </c>
     </row>
     <row r="32">
@@ -937,10 +937,10 @@
         <v>Passed</v>
       </c>
       <c r="D32">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T13:59:48.534Z</v>
+        <v>2026-07-30T21:39:40.487Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>1.4</v>
+        <v>0.36</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T13:59:49.534Z</v>
+        <v>2026-07-30T21:39:41.487Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>0.96</v>
+        <v>0.37</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T13:59:50.534Z</v>
+        <v>2026-07-30T21:39:42.487Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T13:59:51.534Z</v>
+        <v>2026-07-30T21:39:43.487Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T13:59:52.534Z</v>
+        <v>2026-07-30T21:39:44.487Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>1.09</v>
+        <v>0.26</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T13:59:53.534Z</v>
+        <v>2026-07-30T21:39:45.487Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T13:59:54.534Z</v>
+        <v>2026-07-30T21:39:46.487Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>0.09</v>
+        <v>1.25</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T13:59:55.534Z</v>
+        <v>2026-07-30T21:39:47.487Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>0.72</v>
+        <v>1.52</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T13:59:56.534Z</v>
+        <v>2026-07-30T21:39:48.487Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>0.91</v>
+        <v>1.74</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T13:59:57.534Z</v>
+        <v>2026-07-30T21:39:49.487Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T13:59:58.534Z</v>
+        <v>2026-07-30T21:39:50.487Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>1.82</v>
+        <v>0.54</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T13:59:59.534Z</v>
+        <v>2026-07-30T21:39:51.487Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T14:00:00.534Z</v>
+        <v>2026-07-30T21:39:52.487Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>0.99</v>
+        <v>0.69</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T14:00:01.534Z</v>
+        <v>2026-07-30T21:39:53.487Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>1.28</v>
+        <v>0.46</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T14:00:02.534Z</v>
+        <v>2026-07-30T21:39:54.487Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>1.82</v>
+        <v>0.95</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T14:00:03.534Z</v>
+        <v>2026-07-30T21:39:55.487Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>0.58</v>
+        <v>0.46</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T14:00:04.534Z</v>
+        <v>2026-07-30T21:39:56.487Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>1.92</v>
+        <v>0.58</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T14:00:05.534Z</v>
+        <v>2026-07-30T21:39:57.487Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T14:00:06.534Z</v>
+        <v>2026-07-30T21:39:58.487Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>0.98</v>
+        <v>0.61</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T14:00:07.534Z</v>
+        <v>2026-07-30T21:39:59.487Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>1.89</v>
+        <v>0.6</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T14:00:08.534Z</v>
+        <v>2026-07-30T21:40:00.487Z</v>
       </c>
     </row>
     <row r="53">
@@ -1294,10 +1294,10 @@
         <v>Passed</v>
       </c>
       <c r="D53">
-        <v>0.33</v>
+        <v>0.96</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T14:00:09.534Z</v>
+        <v>2026-07-30T21:40:01.487Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T14:00:10.534Z</v>
+        <v>2026-07-30T21:40:02.487Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T14:00:11.534Z</v>
+        <v>2026-07-30T21:40:03.487Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T14:00:12.534Z</v>
+        <v>2026-07-30T21:40:04.487Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T14:00:13.534Z</v>
+        <v>2026-07-30T21:40:05.487Z</v>
       </c>
     </row>
     <row r="58">
@@ -1382,7 +1382,7 @@
         <v>1.46</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T14:00:14.534Z</v>
+        <v>2026-07-30T21:40:06.487Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T14:00:15.534Z</v>
+        <v>2026-07-30T21:40:07.487Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T14:00:16.534Z</v>
+        <v>2026-07-30T21:40:08.487Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>1.08</v>
+        <v>0.07</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T14:00:17.534Z</v>
+        <v>2026-07-30T21:40:09.487Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>1.77</v>
+        <v>0.02</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T14:00:18.534Z</v>
+        <v>2026-07-30T21:40:10.487Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T14:00:19.534Z</v>
+        <v>2026-07-30T21:40:11.487Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>1.71</v>
+        <v>0.55</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T14:00:20.534Z</v>
+        <v>2026-07-30T21:40:12.487Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>1.39</v>
+        <v>0.23</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T14:00:21.534Z</v>
+        <v>2026-07-30T21:40:13.487Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T14:00:22.534Z</v>
+        <v>2026-07-30T21:40:14.487Z</v>
       </c>
     </row>
     <row r="67">
@@ -1532,10 +1532,10 @@
         <v>Passed</v>
       </c>
       <c r="D67">
-        <v>0.77</v>
+        <v>1.63</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T14:00:23.534Z</v>
+        <v>2026-07-30T21:40:15.487Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T14:00:24.534Z</v>
+        <v>2026-07-30T21:40:16.487Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>0.77</v>
+        <v>1.53</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T14:00:25.534Z</v>
+        <v>2026-07-30T21:40:17.487Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T14:00:26.534Z</v>
+        <v>2026-07-30T21:40:18.487Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T14:00:27.534Z</v>
+        <v>2026-07-30T21:40:19.487Z</v>
       </c>
     </row>
     <row r="72">
@@ -1617,10 +1617,10 @@
         <v>Passed</v>
       </c>
       <c r="D72">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T14:00:28.534Z</v>
+        <v>2026-07-30T21:40:20.487Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>0.3</v>
+        <v>1.12</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T14:00:29.534Z</v>
+        <v>2026-07-30T21:40:21.487Z</v>
       </c>
     </row>
     <row r="74">
@@ -1651,10 +1651,10 @@
         <v>Passed</v>
       </c>
       <c r="D74">
-        <v>0.24</v>
+        <v>1.09</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T14:00:30.534Z</v>
+        <v>2026-07-30T21:40:22.487Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>0.68</v>
+        <v>1.03</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T14:00:31.534Z</v>
+        <v>2026-07-30T21:40:23.487Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T14:00:32.534Z</v>
+        <v>2026-07-30T21:40:24.487Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T14:00:33.534Z</v>
+        <v>2026-07-30T21:40:25.487Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T14:00:34.534Z</v>
+        <v>2026-07-30T21:40:26.487Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>1.56</v>
+        <v>0.86</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T14:00:35.534Z</v>
+        <v>2026-07-30T21:40:27.487Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>0.36</v>
+        <v>1.47</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T14:00:36.534Z</v>
+        <v>2026-07-30T21:40:28.487Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T14:00:37.534Z</v>
+        <v>2026-07-30T21:40:29.487Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>1.09</v>
+        <v>0.77</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T14:00:38.534Z</v>
+        <v>2026-07-30T21:40:30.487Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T14:00:39.534Z</v>
+        <v>2026-07-30T21:40:31.487Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>0.86</v>
+        <v>0.11</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T14:00:40.534Z</v>
+        <v>2026-07-30T21:40:32.487Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T14:00:41.534Z</v>
+        <v>2026-07-30T21:40:33.487Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T14:00:42.534Z</v>
+        <v>2026-07-30T21:40:34.487Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>1.49</v>
+        <v>0.03</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T14:00:43.534Z</v>
+        <v>2026-07-30T21:40:35.487Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T14:00:44.534Z</v>
+        <v>2026-07-30T21:40:36.487Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>0.79</v>
+        <v>0.31</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T14:00:45.534Z</v>
+        <v>2026-07-30T21:40:37.487Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>1.98</v>
+        <v>0.57</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T14:00:46.534Z</v>
+        <v>2026-07-30T21:40:38.487Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T14:00:47.534Z</v>
+        <v>2026-07-30T21:40:39.487Z</v>
       </c>
     </row>
     <row r="92">
@@ -1957,10 +1957,10 @@
         <v>Passed</v>
       </c>
       <c r="D92">
-        <v>0.33</v>
+        <v>1.53</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T14:00:48.534Z</v>
+        <v>2026-07-30T21:40:40.487Z</v>
       </c>
     </row>
     <row r="93">
@@ -1974,10 +1974,10 @@
         <v>Passed</v>
       </c>
       <c r="D93">
-        <v>0.95</v>
+        <v>1.53</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T14:00:49.534Z</v>
+        <v>2026-07-30T21:40:41.487Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T14:00:50.534Z</v>
+        <v>2026-07-30T21:40:42.487Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T14:00:51.534Z</v>
+        <v>2026-07-30T21:40:43.487Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T14:00:52.534Z</v>
+        <v>2026-07-30T21:40:44.487Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T14:00:53.534Z</v>
+        <v>2026-07-30T21:40:45.487Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>0.09</v>
+        <v>1.17</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T14:00:54.534Z</v>
+        <v>2026-07-30T21:40:46.487Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>1.31</v>
+        <v>0.2</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T14:00:55.534Z</v>
+        <v>2026-07-30T21:40:47.487Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T14:00:56.534Z</v>
+        <v>2026-07-30T21:40:48.487Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>0.15</v>
+        <v>0.97</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T14:00:57.534Z</v>
+        <v>2026-07-30T21:40:49.487Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>0.05</v>
+        <v>1.28</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T14:00:58.534Z</v>
+        <v>2026-07-30T21:40:50.487Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T14:00:59.534Z</v>
+        <v>2026-07-30T21:40:51.487Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>0.16</v>
+        <v>0.88</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T14:01:00.534Z</v>
+        <v>2026-07-30T21:40:52.487Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>0.76</v>
+        <v>1.25</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T14:01:01.534Z</v>
+        <v>2026-07-30T21:40:53.487Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>0.69</v>
+        <v>1.48</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T14:01:02.534Z</v>
+        <v>2026-07-30T21:40:54.487Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T14:01:03.534Z</v>
+        <v>2026-07-30T21:40:55.487Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T14:01:04.534Z</v>
+        <v>2026-07-30T21:40:56.487Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>1.35</v>
+        <v>0.42</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T14:01:05.534Z</v>
+        <v>2026-07-30T21:40:57.487Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>0.04</v>
+        <v>1.87</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T14:01:06.534Z</v>
+        <v>2026-07-30T21:40:58.487Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T14:01:07.534Z</v>
+        <v>2026-07-30T21:40:59.487Z</v>
       </c>
     </row>
     <row r="112">
@@ -2297,10 +2297,10 @@
         <v>Passed</v>
       </c>
       <c r="D112">
-        <v>1.59</v>
+        <v>0.43</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T14:01:08.534Z</v>
+        <v>2026-07-30T21:41:00.487Z</v>
       </c>
     </row>
     <row r="113">
@@ -2314,10 +2314,10 @@
         <v>Passed</v>
       </c>
       <c r="D113">
-        <v>0.81</v>
+        <v>1.29</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T14:01:09.534Z</v>
+        <v>2026-07-30T21:41:01.487Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>0.17</v>
+        <v>1.03</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T14:01:10.534Z</v>
+        <v>2026-07-30T21:41:02.487Z</v>
       </c>
     </row>
     <row r="115">
@@ -2348,10 +2348,10 @@
         <v>Passed</v>
       </c>
       <c r="D115">
-        <v>0.89</v>
+        <v>1.81</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T14:01:11.534Z</v>
+        <v>2026-07-30T21:41:03.487Z</v>
       </c>
     </row>
     <row r="116">
@@ -2365,10 +2365,10 @@
         <v>Passed</v>
       </c>
       <c r="D116">
-        <v>1.26</v>
+        <v>0.81</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T14:01:12.534Z</v>
+        <v>2026-07-30T21:41:04.487Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T14:01:13.534Z</v>
+        <v>2026-07-30T21:41:05.487Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>0.23</v>
+        <v>1.82</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T14:01:14.534Z</v>
+        <v>2026-07-30T21:41:06.487Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T14:01:15.534Z</v>
+        <v>2026-07-30T21:41:07.487Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>1.49</v>
+        <v>0.16</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T14:01:16.534Z</v>
+        <v>2026-07-30T21:41:08.487Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>1.66</v>
+        <v>0.34</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T14:01:17.534Z</v>
+        <v>2026-07-30T21:41:09.487Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>0.82</v>
+        <v>1.34</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T14:01:18.534Z</v>
+        <v>2026-07-30T21:41:10.487Z</v>
       </c>
     </row>
     <row r="123">
@@ -2484,10 +2484,10 @@
         <v>Passed</v>
       </c>
       <c r="D123">
-        <v>1.14</v>
+        <v>0.22</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T14:01:19.534Z</v>
+        <v>2026-07-30T21:41:11.487Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>0.13</v>
+        <v>1.88</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T14:01:20.534Z</v>
+        <v>2026-07-30T21:41:12.487Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T14:01:21.534Z</v>
+        <v>2026-07-30T21:41:13.487Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T14:01:22.534Z</v>
+        <v>2026-07-30T21:41:14.487Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T14:01:23.534Z</v>
+        <v>2026-07-30T21:41:15.487Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T14:01:24.534Z</v>
+        <v>2026-07-30T21:41:16.487Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T14:01:25.534Z</v>
+        <v>2026-07-30T21:41:17.487Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>0.27</v>
+        <v>1.08</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T14:01:26.534Z</v>
+        <v>2026-07-30T21:41:18.487Z</v>
       </c>
     </row>
     <row r="131">
@@ -2620,10 +2620,10 @@
         <v>Passed</v>
       </c>
       <c r="D131">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T14:01:27.534Z</v>
+        <v>2026-07-30T21:41:19.487Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>0.75</v>
+        <v>0.06</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T14:01:28.534Z</v>
+        <v>2026-07-30T21:41:20.487Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>0.81</v>
+        <v>1.17</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T14:01:29.534Z</v>
+        <v>2026-07-30T21:41:21.487Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T14:01:30.534Z</v>
+        <v>2026-07-30T21:41:22.487Z</v>
       </c>
     </row>
     <row r="135">
@@ -2685,13 +2685,13 @@
         <v>Verify APILoad functionality module 134</v>
       </c>
       <c r="C135" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D135">
-        <v>1.92</v>
+        <v>0.21</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T14:01:31.534Z</v>
+        <v>2026-07-30T21:41:23.487Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>1.68</v>
+        <v>0.91</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T14:01:32.534Z</v>
+        <v>2026-07-30T21:41:24.487Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T14:01:33.534Z</v>
+        <v>2026-07-30T21:41:25.487Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T14:01:34.534Z</v>
+        <v>2026-07-30T21:41:26.487Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T14:01:35.534Z</v>
+        <v>2026-07-30T21:41:27.487Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>1.25</v>
+        <v>0.18</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T14:01:36.534Z</v>
+        <v>2026-07-30T21:41:28.487Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>1.47</v>
+        <v>0.96</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T14:01:37.534Z</v>
+        <v>2026-07-30T21:41:29.487Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>0.44</v>
+        <v>1.63</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T14:01:38.534Z</v>
+        <v>2026-07-30T21:41:30.487Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>1.9</v>
+        <v>1.19</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T14:01:39.534Z</v>
+        <v>2026-07-30T21:41:31.487Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T14:01:40.534Z</v>
+        <v>2026-07-30T21:41:32.487Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T14:01:41.534Z</v>
+        <v>2026-07-30T21:41:33.487Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>0.79</v>
+        <v>0.14</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T14:01:42.534Z</v>
+        <v>2026-07-30T21:41:34.487Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>0.95</v>
+        <v>1.5</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T14:01:43.534Z</v>
+        <v>2026-07-30T21:41:35.487Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T14:01:44.534Z</v>
+        <v>2026-07-30T21:41:36.487Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>0.29</v>
+        <v>1.15</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T14:01:45.534Z</v>
+        <v>2026-07-30T21:41:37.487Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T14:01:46.534Z</v>
+        <v>2026-07-30T21:41:38.487Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>1.09</v>
+        <v>0.15</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T14:01:47.534Z</v>
+        <v>2026-07-30T21:41:39.487Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>0.19</v>
+        <v>1.49</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T14:01:48.534Z</v>
+        <v>2026-07-30T21:41:40.487Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>1.33</v>
+        <v>1.99</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T14:01:49.534Z</v>
+        <v>2026-07-30T21:41:41.487Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>0.16</v>
+        <v>1.81</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T14:01:50.534Z</v>
+        <v>2026-07-30T21:41:42.487Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>1.32</v>
+        <v>0.71</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T14:01:51.534Z</v>
+        <v>2026-07-30T21:41:43.487Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T14:01:52.534Z</v>
+        <v>2026-07-30T21:41:44.487Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T14:01:53.534Z</v>
+        <v>2026-07-30T21:41:45.487Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T14:01:54.534Z</v>
+        <v>2026-07-30T21:41:46.487Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>0.51</v>
+        <v>1.87</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T14:01:55.534Z</v>
+        <v>2026-07-30T21:41:47.487Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>0.55</v>
+        <v>1.8</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T14:01:56.534Z</v>
+        <v>2026-07-30T21:41:48.487Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>1.78</v>
+        <v>0.75</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T14:01:57.534Z</v>
+        <v>2026-07-30T21:41:49.487Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>1.13</v>
+        <v>1.51</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T14:01:58.534Z</v>
+        <v>2026-07-30T21:41:50.487Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T14:01:59.534Z</v>
+        <v>2026-07-30T21:41:51.487Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>1.68</v>
+        <v>1.29</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T14:02:00.534Z</v>
+        <v>2026-07-30T21:41:52.487Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>1.88</v>
+        <v>0.58</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T14:02:01.534Z</v>
+        <v>2026-07-30T21:41:53.487Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T14:02:02.534Z</v>
+        <v>2026-07-30T21:41:54.487Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T14:02:03.534Z</v>
+        <v>2026-07-30T21:41:55.487Z</v>
       </c>
     </row>
     <row r="168">
@@ -3249,10 +3249,10 @@
         <v>Passed</v>
       </c>
       <c r="D168">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T14:02:04.534Z</v>
+        <v>2026-07-30T21:41:56.487Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>0.9</v>
+        <v>1.17</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T14:02:05.534Z</v>
+        <v>2026-07-30T21:41:57.487Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>0.16</v>
+        <v>1.45</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T14:02:06.534Z</v>
+        <v>2026-07-30T21:41:58.487Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>0.54</v>
+        <v>1.61</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T14:02:07.534Z</v>
+        <v>2026-07-30T21:41:59.487Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T14:02:08.534Z</v>
+        <v>2026-07-30T21:42:00.487Z</v>
       </c>
     </row>
     <row r="173">
@@ -3334,10 +3334,10 @@
         <v>Passed</v>
       </c>
       <c r="D173">
-        <v>0.81</v>
+        <v>1.69</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T14:02:09.534Z</v>
+        <v>2026-07-30T21:42:01.487Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>1.28</v>
+        <v>0.99</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T14:02:10.534Z</v>
+        <v>2026-07-30T21:42:02.487Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>0.07</v>
+        <v>1.59</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T14:02:11.534Z</v>
+        <v>2026-07-30T21:42:03.487Z</v>
       </c>
     </row>
     <row r="176">
@@ -3385,10 +3385,10 @@
         <v>Passed</v>
       </c>
       <c r="D176">
-        <v>1.96</v>
+        <v>0.62</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T14:02:12.534Z</v>
+        <v>2026-07-30T21:42:04.487Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>0.12</v>
+        <v>1.98</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T14:02:13.534Z</v>
+        <v>2026-07-30T21:42:05.487Z</v>
       </c>
     </row>
     <row r="178">
@@ -3419,10 +3419,10 @@
         <v>Passed</v>
       </c>
       <c r="D178">
-        <v>0.01</v>
+        <v>1.56</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T14:02:14.534Z</v>
+        <v>2026-07-30T21:42:06.487Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T14:02:15.534Z</v>
+        <v>2026-07-30T21:42:07.487Z</v>
       </c>
     </row>
     <row r="180">
@@ -3453,10 +3453,10 @@
         <v>Passed</v>
       </c>
       <c r="D180">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T14:02:16.534Z</v>
+        <v>2026-07-30T21:42:08.487Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T14:02:17.534Z</v>
+        <v>2026-07-30T21:42:09.487Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>0.63</v>
+        <v>0.81</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T14:02:18.534Z</v>
+        <v>2026-07-30T21:42:10.487Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>1.58</v>
+        <v>0.63</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T14:02:19.534Z</v>
+        <v>2026-07-30T21:42:11.487Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>0.38</v>
+        <v>1.98</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T14:02:20.534Z</v>
+        <v>2026-07-30T21:42:12.487Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>0.28</v>
+        <v>1.44</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T14:02:21.534Z</v>
+        <v>2026-07-30T21:42:13.487Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>0.32</v>
+        <v>1.14</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T14:02:22.534Z</v>
+        <v>2026-07-30T21:42:14.487Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T14:02:23.534Z</v>
+        <v>2026-07-30T21:42:15.487Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>0.42</v>
+        <v>0.9</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T14:02:24.534Z</v>
+        <v>2026-07-30T21:42:16.487Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>0.3</v>
+        <v>0.97</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T14:02:25.534Z</v>
+        <v>2026-07-30T21:42:17.487Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T14:02:26.534Z</v>
+        <v>2026-07-30T21:42:18.487Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>1.66</v>
+        <v>0.43</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T14:02:27.534Z</v>
+        <v>2026-07-30T21:42:19.487Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>1.85</v>
+        <v>0.41</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T14:02:28.534Z</v>
+        <v>2026-07-30T21:42:20.487Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>1.18</v>
+        <v>0.94</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T14:02:29.534Z</v>
+        <v>2026-07-30T21:42:21.487Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>0.28</v>
+        <v>1.2</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T14:02:30.534Z</v>
+        <v>2026-07-30T21:42:22.487Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>1.45</v>
+        <v>0.59</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T14:02:31.534Z</v>
+        <v>2026-07-30T21:42:23.487Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T14:02:32.534Z</v>
+        <v>2026-07-30T21:42:24.487Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T14:02:33.534Z</v>
+        <v>2026-07-30T21:42:25.487Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>1.05</v>
+        <v>0.36</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T14:02:34.534Z</v>
+        <v>2026-07-30T21:42:26.487Z</v>
       </c>
     </row>
     <row r="199">
@@ -3776,10 +3776,10 @@
         <v>Passed</v>
       </c>
       <c r="D199">
-        <v>0.68</v>
+        <v>1.38</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T14:02:35.534Z</v>
+        <v>2026-07-30T21:42:27.487Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>0.6</v>
+        <v>1.93</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T14:02:36.534Z</v>
+        <v>2026-07-30T21:42:28.487Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>0.43</v>
+        <v>0.56</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T14:02:37.534Z</v>
+        <v>2026-07-30T21:42:29.487Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T14:02:38.534Z</v>
+        <v>2026-07-30T21:42:30.487Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>0.69</v>
+        <v>0.14</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T14:02:39.534Z</v>
+        <v>2026-07-30T21:42:31.487Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>1.2</v>
+        <v>0.77</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T14:02:40.534Z</v>
+        <v>2026-07-30T21:42:32.487Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>1.76</v>
+        <v>0.27</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T14:02:41.534Z</v>
+        <v>2026-07-30T21:42:33.487Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>1.02</v>
+        <v>0.72</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T14:02:42.534Z</v>
+        <v>2026-07-30T21:42:34.487Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>0.19</v>
+        <v>1.36</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T14:02:43.534Z</v>
+        <v>2026-07-30T21:42:35.487Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>1.16</v>
+        <v>0.59</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T14:02:44.534Z</v>
+        <v>2026-07-30T21:42:36.487Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>0.73</v>
+        <v>1.86</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T14:02:45.534Z</v>
+        <v>2026-07-30T21:42:37.487Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T14:02:46.534Z</v>
+        <v>2026-07-30T21:42:38.487Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T14:02:47.534Z</v>
+        <v>2026-07-30T21:42:39.487Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T14:02:48.534Z</v>
+        <v>2026-07-30T21:42:40.487Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>0.74</v>
+        <v>1.39</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T14:02:49.534Z</v>
+        <v>2026-07-30T21:42:41.487Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>0.14</v>
+        <v>0.42</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T14:02:50.534Z</v>
+        <v>2026-07-30T21:42:42.487Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T14:02:51.534Z</v>
+        <v>2026-07-30T21:42:43.487Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>1.85</v>
+        <v>0.81</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T14:02:52.534Z</v>
+        <v>2026-07-30T21:42:44.487Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>0.03</v>
+        <v>1.99</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T14:02:53.534Z</v>
+        <v>2026-07-30T21:42:45.487Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T14:02:54.534Z</v>
+        <v>2026-07-30T21:42:46.487Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>0.36</v>
+        <v>1.62</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T14:02:55.534Z</v>
+        <v>2026-07-30T21:42:47.487Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T14:02:56.534Z</v>
+        <v>2026-07-30T21:42:48.487Z</v>
       </c>
     </row>
     <row r="221">
@@ -4150,10 +4150,10 @@
         <v>Passed</v>
       </c>
       <c r="D221">
-        <v>1.77</v>
+        <v>0.18</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T14:02:57.534Z</v>
+        <v>2026-07-30T21:42:49.487Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T14:02:58.534Z</v>
+        <v>2026-07-30T21:42:50.487Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T14:02:59.534Z</v>
+        <v>2026-07-30T21:42:51.487Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>1.73</v>
+        <v>1.13</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T14:03:00.534Z</v>
+        <v>2026-07-30T21:42:52.487Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T14:03:01.534Z</v>
+        <v>2026-07-30T21:42:53.487Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T14:03:02.534Z</v>
+        <v>2026-07-30T21:42:54.487Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>0.12</v>
+        <v>1.13</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T14:03:03.534Z</v>
+        <v>2026-07-30T21:42:55.487Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>1.34</v>
+        <v>0.52</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T14:03:04.534Z</v>
+        <v>2026-07-30T21:42:56.487Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>1.34</v>
+        <v>0.73</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T14:03:05.534Z</v>
+        <v>2026-07-30T21:42:57.487Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T14:03:06.534Z</v>
+        <v>2026-07-30T21:42:58.487Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T14:03:07.534Z</v>
+        <v>2026-07-30T21:42:59.487Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>0.81</v>
+        <v>0.3</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T14:03:08.534Z</v>
+        <v>2026-07-30T21:43:00.487Z</v>
       </c>
     </row>
     <row r="233">
@@ -4354,10 +4354,10 @@
         <v>Passed</v>
       </c>
       <c r="D233">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T14:03:09.534Z</v>
+        <v>2026-07-30T21:43:01.487Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>0.2</v>
+        <v>1.07</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T14:03:10.534Z</v>
+        <v>2026-07-30T21:43:02.487Z</v>
       </c>
     </row>
     <row r="235">
@@ -4388,10 +4388,10 @@
         <v>Passed</v>
       </c>
       <c r="D235">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T14:03:11.534Z</v>
+        <v>2026-07-30T21:43:03.487Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T14:03:12.534Z</v>
+        <v>2026-07-30T21:43:04.487Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>0.19</v>
+        <v>0.69</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T14:03:13.534Z</v>
+        <v>2026-07-30T21:43:05.487Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T14:03:14.534Z</v>
+        <v>2026-07-30T21:43:06.487Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T14:03:15.534Z</v>
+        <v>2026-07-30T21:43:07.487Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>0.93</v>
+        <v>1.74</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T14:03:16.534Z</v>
+        <v>2026-07-30T21:43:08.487Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>0.72</v>
+        <v>1.34</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T14:03:17.534Z</v>
+        <v>2026-07-30T21:43:09.487Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>1.24</v>
+        <v>0.05</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T14:03:18.534Z</v>
+        <v>2026-07-30T21:43:10.487Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>1.68</v>
+        <v>0.01</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T14:03:19.534Z</v>
+        <v>2026-07-30T21:43:11.487Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>0.31</v>
+        <v>0.76</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T14:03:20.534Z</v>
+        <v>2026-07-30T21:43:12.487Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T14:03:21.534Z</v>
+        <v>2026-07-30T21:43:13.487Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T14:03:22.534Z</v>
+        <v>2026-07-30T21:43:14.487Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>1.57</v>
+        <v>0.17</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T14:03:23.534Z</v>
+        <v>2026-07-30T21:43:15.487Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T14:03:24.534Z</v>
+        <v>2026-07-30T21:43:16.487Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>0.8</v>
+        <v>1.74</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T14:03:25.534Z</v>
+        <v>2026-07-30T21:43:17.487Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>0.51</v>
+        <v>0.07</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T14:03:26.534Z</v>
+        <v>2026-07-30T21:43:18.487Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>0.06</v>
+        <v>1.72</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T14:03:27.534Z</v>
+        <v>2026-07-30T21:43:19.487Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>1.98</v>
+        <v>0.98</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T14:03:28.534Z</v>
+        <v>2026-07-30T21:43:20.487Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T14:03:29.534Z</v>
+        <v>2026-07-30T21:43:21.487Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T14:03:30.534Z</v>
+        <v>2026-07-30T21:43:22.487Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>1.26</v>
+        <v>0.82</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T14:03:31.534Z</v>
+        <v>2026-07-30T21:43:23.487Z</v>
       </c>
     </row>
     <row r="256">
@@ -4745,10 +4745,10 @@
         <v>Passed</v>
       </c>
       <c r="D256">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T14:03:32.534Z</v>
+        <v>2026-07-30T21:43:24.487Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T14:03:33.534Z</v>
+        <v>2026-07-30T21:43:25.487Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>0.65</v>
+        <v>1.7</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T14:03:34.534Z</v>
+        <v>2026-07-30T21:43:26.487Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T14:03:35.534Z</v>
+        <v>2026-07-30T21:43:27.487Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T14:03:36.534Z</v>
+        <v>2026-07-30T21:43:28.487Z</v>
       </c>
     </row>
     <row r="261">
@@ -4833,7 +4833,7 @@
         <v>1.04</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T14:03:37.534Z</v>
+        <v>2026-07-30T21:43:29.487Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T14:03:38.534Z</v>
+        <v>2026-07-30T21:43:30.487Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T14:03:39.534Z</v>
+        <v>2026-07-30T21:43:31.487Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>1.54</v>
+        <v>0.18</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T14:03:40.534Z</v>
+        <v>2026-07-30T21:43:32.487Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>0.01</v>
+        <v>1.66</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T14:03:41.534Z</v>
+        <v>2026-07-30T21:43:33.487Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T14:03:42.534Z</v>
+        <v>2026-07-30T21:43:34.487Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>0.63</v>
+        <v>1.39</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T14:03:43.534Z</v>
+        <v>2026-07-30T21:43:35.487Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>0.44</v>
+        <v>0.11</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T14:03:44.534Z</v>
+        <v>2026-07-30T21:43:36.487Z</v>
       </c>
     </row>
     <row r="269">
@@ -4966,10 +4966,10 @@
         <v>Passed</v>
       </c>
       <c r="D269">
-        <v>1.01</v>
+        <v>0.23</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T14:03:45.534Z</v>
+        <v>2026-07-30T21:43:37.487Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>1.19</v>
+        <v>1.7</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T14:03:46.534Z</v>
+        <v>2026-07-30T21:43:38.487Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T14:03:47.534Z</v>
+        <v>2026-07-30T21:43:39.487Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T14:03:48.534Z</v>
+        <v>2026-07-30T21:43:40.487Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T14:03:49.534Z</v>
+        <v>2026-07-30T21:43:41.487Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>1.17</v>
+        <v>0.97</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T14:03:50.534Z</v>
+        <v>2026-07-30T21:43:42.487Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>0.24</v>
+        <v>1.9</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T14:03:51.534Z</v>
+        <v>2026-07-30T21:43:43.487Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T14:03:52.534Z</v>
+        <v>2026-07-30T21:43:44.487Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T14:03:53.534Z</v>
+        <v>2026-07-30T21:43:45.487Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>1.54</v>
+        <v>0.72</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T14:03:54.534Z</v>
+        <v>2026-07-30T21:43:46.487Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>0.49</v>
+        <v>1.27</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T14:03:55.534Z</v>
+        <v>2026-07-30T21:43:47.487Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>1.77</v>
+        <v>0.63</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T14:03:56.534Z</v>
+        <v>2026-07-30T21:43:48.487Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T14:03:57.534Z</v>
+        <v>2026-07-30T21:43:49.487Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>1.55</v>
+        <v>0.9</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T14:03:58.534Z</v>
+        <v>2026-07-30T21:43:50.487Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>1.21</v>
+        <v>0.76</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T14:03:59.534Z</v>
+        <v>2026-07-30T21:43:51.487Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>1.93</v>
+        <v>0.14</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T14:04:00.534Z</v>
+        <v>2026-07-30T21:43:52.487Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T14:04:01.534Z</v>
+        <v>2026-07-30T21:43:53.487Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.81</v>
+        <v>0.5</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T14:04:02.534Z</v>
+        <v>2026-07-30T21:43:54.487Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>0.71</v>
+        <v>1.67</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T14:04:03.534Z</v>
+        <v>2026-07-30T21:43:55.487Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>1.38</v>
+        <v>0.68</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T14:04:04.534Z</v>
+        <v>2026-07-30T21:43:56.487Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>0.76</v>
+        <v>1.73</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T14:04:05.534Z</v>
+        <v>2026-07-30T21:43:57.487Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>1.51</v>
+        <v>1.89</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T14:04:06.534Z</v>
+        <v>2026-07-30T21:43:58.487Z</v>
       </c>
     </row>
     <row r="291">
@@ -5340,10 +5340,10 @@
         <v>Passed</v>
       </c>
       <c r="D291">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T14:04:07.534Z</v>
+        <v>2026-07-30T21:43:59.487Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>1.51</v>
+        <v>0.16</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T14:04:08.534Z</v>
+        <v>2026-07-30T21:44:00.487Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>0.09</v>
+        <v>0.78</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T14:04:09.534Z</v>
+        <v>2026-07-30T21:44:01.487Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>1.35</v>
+        <v>0.26</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T14:04:10.534Z</v>
+        <v>2026-07-30T21:44:02.487Z</v>
       </c>
     </row>
     <row r="295">
@@ -5408,10 +5408,10 @@
         <v>Passed</v>
       </c>
       <c r="D295">
-        <v>0.31</v>
+        <v>1.19</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T14:04:11.534Z</v>
+        <v>2026-07-30T21:44:03.487Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T14:04:12.534Z</v>
+        <v>2026-07-30T21:44:04.487Z</v>
       </c>
     </row>
     <row r="297">
@@ -5439,13 +5439,13 @@
         <v>Verify APILoad functionality module 296</v>
       </c>
       <c r="C297" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D297">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T14:04:13.534Z</v>
+        <v>2026-07-30T21:44:05.487Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T14:04:14.534Z</v>
+        <v>2026-07-30T21:44:06.487Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>0.17</v>
+        <v>0.89</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T14:04:15.534Z</v>
+        <v>2026-07-30T21:44:07.487Z</v>
       </c>
     </row>
     <row r="300">
@@ -5493,10 +5493,10 @@
         <v>Passed</v>
       </c>
       <c r="D300">
-        <v>1.68</v>
+        <v>1.09</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T14:04:16.534Z</v>
+        <v>2026-07-30T21:44:08.487Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>0.77</v>
+        <v>1.24</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T14:04:17.534Z</v>
+        <v>2026-07-30T21:44:09.487Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T14:04:18.534Z</v>
+        <v>2026-07-30T21:44:10.487Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>0.65</v>
+        <v>1.97</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T14:04:19.534Z</v>
+        <v>2026-07-30T21:44:11.487Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T14:04:20.534Z</v>
+        <v>2026-07-30T21:44:12.487Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>0.43</v>
+        <v>1.61</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T14:04:21.534Z</v>
+        <v>2026-07-30T21:44:13.487Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>0.23</v>
+        <v>1.98</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T14:04:22.534Z</v>
+        <v>2026-07-30T21:44:14.487Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T14:04:23.534Z</v>
+        <v>2026-07-30T21:44:15.487Z</v>
       </c>
     </row>
     <row r="308">
@@ -5629,10 +5629,10 @@
         <v>Passed</v>
       </c>
       <c r="D308">
-        <v>1.53</v>
+        <v>0.72</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T14:04:24.534Z</v>
+        <v>2026-07-30T21:44:16.487Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>0.2</v>
+        <v>1.17</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T14:04:25.534Z</v>
+        <v>2026-07-30T21:44:17.487Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>0.29</v>
+        <v>1.85</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T14:04:26.534Z</v>
+        <v>2026-07-30T21:44:18.487Z</v>
       </c>
     </row>
     <row r="311">
@@ -5677,13 +5677,13 @@
         <v>Verify APILoad functionality module 310</v>
       </c>
       <c r="C311" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D311">
-        <v>0.85</v>
+        <v>0.54</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T14:04:27.534Z</v>
+        <v>2026-07-30T21:44:19.487Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>0.81</v>
+        <v>1.8</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T14:04:28.534Z</v>
+        <v>2026-07-30T21:44:20.487Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>0.47</v>
+        <v>1.75</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T14:04:29.534Z</v>
+        <v>2026-07-30T21:44:21.487Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T14:04:30.534Z</v>
+        <v>2026-07-30T21:44:22.487Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>1.12</v>
+        <v>0.5</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T14:04:31.534Z</v>
+        <v>2026-07-30T21:44:23.487Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T14:04:32.534Z</v>
+        <v>2026-07-30T21:44:24.487Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>1.95</v>
+        <v>1</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T14:04:33.534Z</v>
+        <v>2026-07-30T21:44:25.487Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T14:04:34.534Z</v>
+        <v>2026-07-30T21:44:26.487Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>0.81</v>
+        <v>0.94</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T14:04:35.534Z</v>
+        <v>2026-07-30T21:44:27.487Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>1.42</v>
+        <v>0.75</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T14:04:36.534Z</v>
+        <v>2026-07-30T21:44:28.487Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T14:04:37.534Z</v>
+        <v>2026-07-30T21:44:29.487Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>0.77</v>
+        <v>1.61</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T14:04:38.534Z</v>
+        <v>2026-07-30T21:44:30.487Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>0.97</v>
+        <v>1.73</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T14:04:39.534Z</v>
+        <v>2026-07-30T21:44:31.487Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>1.17</v>
+        <v>0.81</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T14:04:40.534Z</v>
+        <v>2026-07-30T21:44:32.487Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>1.23</v>
+        <v>0.05</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T14:04:41.534Z</v>
+        <v>2026-07-30T21:44:33.487Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>1.28</v>
+        <v>1.84</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T14:04:42.534Z</v>
+        <v>2026-07-30T21:44:34.487Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T14:04:43.534Z</v>
+        <v>2026-07-30T21:44:35.487Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T14:04:44.534Z</v>
+        <v>2026-07-30T21:44:36.487Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>0.43</v>
+        <v>1.41</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T14:04:45.534Z</v>
+        <v>2026-07-30T21:44:37.487Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>0.2</v>
+        <v>1.37</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T14:04:46.534Z</v>
+        <v>2026-07-30T21:44:38.487Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>0.71</v>
+        <v>0.14</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T14:04:47.534Z</v>
+        <v>2026-07-30T21:44:39.487Z</v>
       </c>
     </row>
     <row r="332">
@@ -6037,10 +6037,10 @@
         <v>Passed</v>
       </c>
       <c r="D332">
-        <v>0.64</v>
+        <v>1.8</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T14:04:48.534Z</v>
+        <v>2026-07-30T21:44:40.487Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T14:04:49.534Z</v>
+        <v>2026-07-30T21:44:41.487Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>0.59</v>
+        <v>1.62</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T14:04:50.534Z</v>
+        <v>2026-07-30T21:44:42.487Z</v>
       </c>
     </row>
     <row r="335">
@@ -6088,10 +6088,10 @@
         <v>Passed</v>
       </c>
       <c r="D335">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T14:04:51.534Z</v>
+        <v>2026-07-30T21:44:43.487Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T14:04:52.534Z</v>
+        <v>2026-07-30T21:44:44.487Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T14:04:53.534Z</v>
+        <v>2026-07-30T21:44:45.487Z</v>
       </c>
     </row>
     <row r="338">
@@ -6136,13 +6136,13 @@
         <v>Verify APILoad functionality module 337</v>
       </c>
       <c r="C338" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D338">
-        <v>0.59</v>
+        <v>1.28</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T14:04:54.534Z</v>
+        <v>2026-07-30T21:44:46.487Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>0.36</v>
+        <v>1.06</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T14:04:55.534Z</v>
+        <v>2026-07-30T21:44:47.487Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>1.65</v>
+        <v>0.78</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T14:04:56.534Z</v>
+        <v>2026-07-30T21:44:48.487Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T14:04:57.534Z</v>
+        <v>2026-07-30T21:44:49.487Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>1.36</v>
+        <v>0.45</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T14:04:58.534Z</v>
+        <v>2026-07-30T21:44:50.487Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>0.61</v>
+        <v>1.02</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T14:04:59.534Z</v>
+        <v>2026-07-30T21:44:51.487Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>0.49</v>
+        <v>1.49</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T14:05:00.534Z</v>
+        <v>2026-07-30T21:44:52.487Z</v>
       </c>
     </row>
     <row r="345">
@@ -6258,10 +6258,10 @@
         <v>Passed</v>
       </c>
       <c r="D345">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T14:05:01.534Z</v>
+        <v>2026-07-30T21:44:53.487Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>0.85</v>
+        <v>1.37</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T14:05:02.534Z</v>
+        <v>2026-07-30T21:44:54.487Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T14:05:03.534Z</v>
+        <v>2026-07-30T21:44:55.487Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>0.18</v>
+        <v>1.11</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T14:05:04.534Z</v>
+        <v>2026-07-30T21:44:56.487Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T14:05:05.534Z</v>
+        <v>2026-07-30T21:44:57.487Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>0.57</v>
+        <v>1.87</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T14:05:06.534Z</v>
+        <v>2026-07-30T21:44:58.487Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T14:05:07.534Z</v>
+        <v>2026-07-30T21:44:59.487Z</v>
       </c>
     </row>
     <row r="352">
@@ -6377,10 +6377,10 @@
         <v>Passed</v>
       </c>
       <c r="D352">
-        <v>0.34</v>
+        <v>1.23</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T14:05:08.534Z</v>
+        <v>2026-07-30T21:45:00.487Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T14:05:09.534Z</v>
+        <v>2026-07-30T21:45:01.487Z</v>
       </c>
     </row>
     <row r="354">
@@ -6414,7 +6414,7 @@
         <v>1.15</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T14:05:10.534Z</v>
+        <v>2026-07-30T21:45:02.487Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>1.95</v>
+        <v>0.24</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T14:05:11.534Z</v>
+        <v>2026-07-30T21:45:03.487Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>0.23</v>
+        <v>1.95</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T14:05:12.534Z</v>
+        <v>2026-07-30T21:45:04.487Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>1.66</v>
+        <v>0.61</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T14:05:13.534Z</v>
+        <v>2026-07-30T21:45:05.487Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T14:05:14.534Z</v>
+        <v>2026-07-30T21:45:06.487Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T14:05:15.534Z</v>
+        <v>2026-07-30T21:45:07.487Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>0.76</v>
+        <v>0.22</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T14:05:16.534Z</v>
+        <v>2026-07-30T21:45:08.487Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T14:05:17.534Z</v>
+        <v>2026-07-30T21:45:09.487Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>1.8</v>
+        <v>0.37</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T14:05:18.534Z</v>
+        <v>2026-07-30T21:45:10.487Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T14:05:19.534Z</v>
+        <v>2026-07-30T21:45:11.487Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.94</v>
+        <v>1.32</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T14:05:20.534Z</v>
+        <v>2026-07-30T21:45:12.487Z</v>
       </c>
     </row>
     <row r="365">
@@ -6598,10 +6598,10 @@
         <v>Passed</v>
       </c>
       <c r="D365">
-        <v>1.15</v>
+        <v>0.65</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T14:05:21.534Z</v>
+        <v>2026-07-30T21:45:13.487Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T14:05:22.534Z</v>
+        <v>2026-07-30T21:45:14.487Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>0.34</v>
+        <v>1.59</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T14:05:23.534Z</v>
+        <v>2026-07-30T21:45:15.487Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>1.25</v>
+        <v>0.05</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T14:05:24.534Z</v>
+        <v>2026-07-30T21:45:16.487Z</v>
       </c>
     </row>
     <row r="369">
@@ -6666,10 +6666,10 @@
         <v>Passed</v>
       </c>
       <c r="D369">
-        <v>0.38</v>
+        <v>0.15</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T14:05:25.534Z</v>
+        <v>2026-07-30T21:45:17.487Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T14:05:26.534Z</v>
+        <v>2026-07-30T21:45:18.487Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>0.13</v>
+        <v>0.72</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T14:05:27.534Z</v>
+        <v>2026-07-30T21:45:19.487Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>1.63</v>
+        <v>0.68</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T14:05:28.534Z</v>
+        <v>2026-07-30T21:45:20.487Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>0.65</v>
+        <v>1.46</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T14:05:29.534Z</v>
+        <v>2026-07-30T21:45:21.487Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>0.11</v>
+        <v>1.87</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T14:05:30.534Z</v>
+        <v>2026-07-30T21:45:22.487Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T14:05:31.534Z</v>
+        <v>2026-07-30T21:45:23.487Z</v>
       </c>
     </row>
     <row r="376">
@@ -6785,10 +6785,10 @@
         <v>Passed</v>
       </c>
       <c r="D376">
-        <v>1.1</v>
+        <v>1.68</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T14:05:32.534Z</v>
+        <v>2026-07-30T21:45:24.487Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>1.15</v>
+        <v>0.01</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T14:05:33.534Z</v>
+        <v>2026-07-30T21:45:25.487Z</v>
       </c>
     </row>
     <row r="378">
@@ -6816,13 +6816,13 @@
         <v>Verify APILoad functionality module 377</v>
       </c>
       <c r="C378" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D378">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T14:05:34.534Z</v>
+        <v>2026-07-30T21:45:26.487Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T14:05:35.534Z</v>
+        <v>2026-07-30T21:45:27.487Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>0.83</v>
+        <v>0.09</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T14:05:36.534Z</v>
+        <v>2026-07-30T21:45:28.487Z</v>
       </c>
     </row>
     <row r="381">
@@ -6870,10 +6870,10 @@
         <v>Passed</v>
       </c>
       <c r="D381">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T14:05:37.534Z</v>
+        <v>2026-07-30T21:45:29.487Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T14:05:38.534Z</v>
+        <v>2026-07-30T21:45:30.487Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T14:05:39.534Z</v>
+        <v>2026-07-30T21:45:31.487Z</v>
       </c>
     </row>
     <row r="384">
@@ -6921,10 +6921,10 @@
         <v>Passed</v>
       </c>
       <c r="D384">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T14:05:40.534Z</v>
+        <v>2026-07-30T21:45:32.487Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T14:05:41.534Z</v>
+        <v>2026-07-30T21:45:33.487Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T14:05:42.534Z</v>
+        <v>2026-07-30T21:45:34.487Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T14:05:43.534Z</v>
+        <v>2026-07-30T21:45:35.487Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>1.06</v>
+        <v>0.76</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T14:05:44.534Z</v>
+        <v>2026-07-30T21:45:36.487Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T14:05:45.534Z</v>
+        <v>2026-07-30T21:45:37.487Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T14:05:46.534Z</v>
+        <v>2026-07-30T21:45:38.487Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T14:05:47.534Z</v>
+        <v>2026-07-30T21:45:39.487Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T14:05:48.534Z</v>
+        <v>2026-07-30T21:45:40.487Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>0.26</v>
+        <v>0.91</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T14:05:49.534Z</v>
+        <v>2026-07-30T21:45:41.487Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>0.96</v>
+        <v>0.15</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T14:05:50.534Z</v>
+        <v>2026-07-30T21:45:42.487Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T14:05:51.534Z</v>
+        <v>2026-07-30T21:45:43.487Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>1.79</v>
+        <v>0.62</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T14:05:52.534Z</v>
+        <v>2026-07-30T21:45:44.487Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>0.9</v>
+        <v>0.13</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T14:05:53.534Z</v>
+        <v>2026-07-30T21:45:45.487Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>1.46</v>
+        <v>0.3</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T14:05:54.534Z</v>
+        <v>2026-07-30T21:45:46.487Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>1.09</v>
+        <v>0.26</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T14:05:55.534Z</v>
+        <v>2026-07-30T21:45:47.487Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>0.78</v>
+        <v>1.64</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T14:05:56.534Z</v>
+        <v>2026-07-30T21:45:48.487Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>0.07</v>
+        <v>0.4</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T14:05:57.534Z</v>
+        <v>2026-07-30T21:45:49.487Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T14:05:58.534Z</v>
+        <v>2026-07-30T21:45:50.487Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T14:05:59.534Z</v>
+        <v>2026-07-30T21:45:51.487Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>1.73</v>
+        <v>0.42</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T14:06:00.534Z</v>
+        <v>2026-07-30T21:45:52.487Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T14:06:01.534Z</v>
+        <v>2026-07-30T21:45:53.487Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>0.57</v>
+        <v>1.94</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T14:06:02.534Z</v>
+        <v>2026-07-30T21:45:54.487Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T14:06:03.534Z</v>
+        <v>2026-07-30T21:45:55.487Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T14:06:04.534Z</v>
+        <v>2026-07-30T21:45:56.487Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>1.82</v>
+        <v>0.96</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T14:06:05.534Z</v>
+        <v>2026-07-30T21:45:57.487Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>0.08</v>
+        <v>1.35</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T14:06:06.534Z</v>
+        <v>2026-07-30T21:45:58.487Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T14:06:07.534Z</v>
+        <v>2026-07-30T21:45:59.487Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>0.68</v>
+        <v>1.98</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T14:06:08.534Z</v>
+        <v>2026-07-30T21:46:00.487Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T14:06:09.534Z</v>
+        <v>2026-07-30T21:46:01.487Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T14:06:10.534Z</v>
+        <v>2026-07-30T21:46:02.487Z</v>
       </c>
     </row>
     <row r="415">
@@ -7448,10 +7448,10 @@
         <v>Passed</v>
       </c>
       <c r="D415">
-        <v>1.8</v>
+        <v>0.57</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T14:06:11.534Z</v>
+        <v>2026-07-30T21:46:03.487Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>0.01</v>
+        <v>0.93</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T14:06:12.534Z</v>
+        <v>2026-07-30T21:46:04.487Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>0.28</v>
+        <v>1.96</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T14:06:13.534Z</v>
+        <v>2026-07-30T21:46:05.487Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>0.29</v>
+        <v>1.11</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T14:06:14.534Z</v>
+        <v>2026-07-30T21:46:06.487Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>1.33</v>
+        <v>0.78</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T14:06:15.534Z</v>
+        <v>2026-07-30T21:46:07.487Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T14:06:16.534Z</v>
+        <v>2026-07-30T21:46:08.487Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>0.34</v>
+        <v>0.97</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T14:06:17.534Z</v>
+        <v>2026-07-30T21:46:09.487Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T14:06:18.534Z</v>
+        <v>2026-07-30T21:46:10.487Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>1.42</v>
+        <v>0.85</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T14:06:19.534Z</v>
+        <v>2026-07-30T21:46:11.487Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T14:06:20.534Z</v>
+        <v>2026-07-30T21:46:12.487Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>1.66</v>
+        <v>0.35</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T14:06:21.534Z</v>
+        <v>2026-07-30T21:46:13.487Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T14:06:22.534Z</v>
+        <v>2026-07-30T21:46:14.487Z</v>
       </c>
     </row>
     <row r="427">
@@ -7652,10 +7652,10 @@
         <v>Passed</v>
       </c>
       <c r="D427">
-        <v>0.4</v>
+        <v>1.09</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T14:06:23.534Z</v>
+        <v>2026-07-30T21:46:15.487Z</v>
       </c>
     </row>
     <row r="428">
@@ -7669,10 +7669,10 @@
         <v>Passed</v>
       </c>
       <c r="D428">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T14:06:24.534Z</v>
+        <v>2026-07-30T21:46:16.487Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>0.72</v>
+        <v>1.98</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T14:06:25.534Z</v>
+        <v>2026-07-30T21:46:17.487Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T14:06:26.534Z</v>
+        <v>2026-07-30T21:46:18.487Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>0.85</v>
+        <v>1.93</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T14:06:27.534Z</v>
+        <v>2026-07-30T21:46:19.487Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>1.29</v>
+        <v>0.31</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T14:06:28.534Z</v>
+        <v>2026-07-30T21:46:20.487Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>0.03</v>
+        <v>1.37</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T14:06:29.534Z</v>
+        <v>2026-07-30T21:46:21.487Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T14:06:30.534Z</v>
+        <v>2026-07-30T21:46:22.487Z</v>
       </c>
     </row>
     <row r="435">
@@ -7788,10 +7788,10 @@
         <v>Passed</v>
       </c>
       <c r="D435">
-        <v>0.57</v>
+        <v>1.3</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T14:06:31.534Z</v>
+        <v>2026-07-30T21:46:23.487Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>1.05</v>
+        <v>0.13</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T14:06:32.534Z</v>
+        <v>2026-07-30T21:46:24.487Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T14:06:33.534Z</v>
+        <v>2026-07-30T21:46:25.487Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>1.02</v>
+        <v>0.41</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T14:06:34.534Z</v>
+        <v>2026-07-30T21:46:26.487Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>0.09</v>
+        <v>1.77</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T14:06:35.534Z</v>
+        <v>2026-07-30T21:46:27.487Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T14:06:36.534Z</v>
+        <v>2026-07-30T21:46:28.487Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T14:06:37.534Z</v>
+        <v>2026-07-30T21:46:29.487Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>0.75</v>
+        <v>1.53</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T14:06:38.534Z</v>
+        <v>2026-07-30T21:46:30.487Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>1.39</v>
+        <v>0.07</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T14:06:39.534Z</v>
+        <v>2026-07-30T21:46:31.487Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T14:06:40.534Z</v>
+        <v>2026-07-30T21:46:32.487Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T14:06:41.534Z</v>
+        <v>2026-07-30T21:46:33.487Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>1.7</v>
+        <v>0.45</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T14:06:42.534Z</v>
+        <v>2026-07-30T21:46:34.487Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T14:06:43.534Z</v>
+        <v>2026-07-30T21:46:35.487Z</v>
       </c>
     </row>
     <row r="448">
@@ -8009,10 +8009,10 @@
         <v>Passed</v>
       </c>
       <c r="D448">
-        <v>0.37</v>
+        <v>0.26</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T14:06:44.534Z</v>
+        <v>2026-07-30T21:46:36.487Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>0.22</v>
+        <v>1.29</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T14:06:45.534Z</v>
+        <v>2026-07-30T21:46:37.487Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T14:06:46.534Z</v>
+        <v>2026-07-30T21:46:38.487Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T14:06:47.534Z</v>
+        <v>2026-07-30T21:46:39.487Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>1.82</v>
+        <v>0.46</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T14:06:48.534Z</v>
+        <v>2026-07-30T21:46:40.487Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T14:06:49.534Z</v>
+        <v>2026-07-30T21:46:41.487Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T14:06:50.534Z</v>
+        <v>2026-07-30T21:46:42.487Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>0.8</v>
+        <v>1.96</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T14:06:51.534Z</v>
+        <v>2026-07-30T21:46:43.487Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,10 +8145,10 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T14:06:52.534Z</v>
+        <v>2026-07-30T21:46:44.487Z</v>
       </c>
     </row>
     <row r="457">
@@ -8162,10 +8162,10 @@
         <v>Passed</v>
       </c>
       <c r="D457">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="E457" t="str">
-        <v>2026-07-30T14:06:53.534Z</v>
+        <v>2026-07-30T21:46:45.487Z</v>
       </c>
     </row>
     <row r="458">
@@ -8179,10 +8179,10 @@
         <v>Passed</v>
       </c>
       <c r="D458">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="E458" t="str">
-        <v>2026-07-30T14:06:54.534Z</v>
+        <v>2026-07-30T21:46:46.487Z</v>
       </c>
     </row>
     <row r="459">
@@ -8196,10 +8196,10 @@
         <v>Passed</v>
       </c>
       <c r="D459">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="E459" t="str">
-        <v>2026-07-30T14:06:55.534Z</v>
+        <v>2026-07-30T21:46:47.487Z</v>
       </c>
     </row>
     <row r="460">
@@ -8213,10 +8213,10 @@
         <v>Passed</v>
       </c>
       <c r="D460">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="E460" t="str">
-        <v>2026-07-30T14:06:56.534Z</v>
+        <v>2026-07-30T21:46:48.487Z</v>
       </c>
     </row>
     <row r="461">
@@ -8230,10 +8230,10 @@
         <v>Passed</v>
       </c>
       <c r="D461">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="E461" t="str">
-        <v>2026-07-30T14:06:57.534Z</v>
+        <v>2026-07-30T21:46:49.487Z</v>
       </c>
     </row>
     <row r="462">
@@ -8247,10 +8247,10 @@
         <v>Passed</v>
       </c>
       <c r="D462">
-        <v>0.64</v>
+        <v>1.6</v>
       </c>
       <c r="E462" t="str">
-        <v>2026-07-30T14:06:58.534Z</v>
+        <v>2026-07-30T21:46:50.487Z</v>
       </c>
     </row>
     <row r="463">
@@ -8264,10 +8264,10 @@
         <v>Passed</v>
       </c>
       <c r="D463">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="E463" t="str">
-        <v>2026-07-30T14:06:59.534Z</v>
+        <v>2026-07-30T21:46:51.487Z</v>
       </c>
     </row>
     <row r="464">
@@ -8281,10 +8281,10 @@
         <v>Passed</v>
       </c>
       <c r="D464">
-        <v>0.65</v>
+        <v>1.98</v>
       </c>
       <c r="E464" t="str">
-        <v>2026-07-30T14:07:00.534Z</v>
+        <v>2026-07-30T21:46:52.487Z</v>
       </c>
     </row>
     <row r="465">
@@ -8298,10 +8298,10 @@
         <v>Passed</v>
       </c>
       <c r="D465">
-        <v>1.09</v>
+        <v>0.68</v>
       </c>
       <c r="E465" t="str">
-        <v>2026-07-30T14:07:01.534Z</v>
+        <v>2026-07-30T21:46:53.487Z</v>
       </c>
     </row>
     <row r="466">
@@ -8312,13 +8312,13 @@
         <v>Verify APILoad functionality module 465</v>
       </c>
       <c r="C466" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D466">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="E466" t="str">
-        <v>2026-07-30T14:07:02.534Z</v>
+        <v>2026-07-30T21:46:54.487Z</v>
       </c>
     </row>
     <row r="467">
@@ -8332,10 +8332,10 @@
         <v>Passed</v>
       </c>
       <c r="D467">
-        <v>1.13</v>
+        <v>0.01</v>
       </c>
       <c r="E467" t="str">
-        <v>2026-07-30T14:07:03.534Z</v>
+        <v>2026-07-30T21:46:55.487Z</v>
       </c>
     </row>
     <row r="468">
@@ -8349,10 +8349,10 @@
         <v>Passed</v>
       </c>
       <c r="D468">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="E468" t="str">
-        <v>2026-07-30T14:07:04.534Z</v>
+        <v>2026-07-30T21:46:56.487Z</v>
       </c>
     </row>
     <row r="469">
@@ -8366,10 +8366,10 @@
         <v>Passed</v>
       </c>
       <c r="D469">
-        <v>0.28</v>
+        <v>1.94</v>
       </c>
       <c r="E469" t="str">
-        <v>2026-07-30T14:07:05.534Z</v>
+        <v>2026-07-30T21:46:57.487Z</v>
       </c>
     </row>
     <row r="470">
@@ -8383,10 +8383,10 @@
         <v>Passed</v>
       </c>
       <c r="D470">
-        <v>1.58</v>
+        <v>0.98</v>
       </c>
       <c r="E470" t="str">
-        <v>2026-07-30T14:07:06.534Z</v>
+        <v>2026-07-30T21:46:58.487Z</v>
       </c>
     </row>
     <row r="471">
@@ -8403,7 +8403,7 @@
         <v>1.58</v>
       </c>
       <c r="E471" t="str">
-        <v>2026-07-30T14:07:07.534Z</v>
+        <v>2026-07-30T21:46:59.487Z</v>
       </c>
     </row>
     <row r="472">
@@ -8417,10 +8417,10 @@
         <v>Passed</v>
       </c>
       <c r="D472">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="E472" t="str">
-        <v>2026-07-30T14:07:08.534Z</v>
+        <v>2026-07-30T21:47:00.487Z</v>
       </c>
     </row>
     <row r="473">
@@ -8434,10 +8434,10 @@
         <v>Passed</v>
       </c>
       <c r="D473">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
       <c r="E473" t="str">
-        <v>2026-07-30T14:07:09.534Z</v>
+        <v>2026-07-30T21:47:01.487Z</v>
       </c>
     </row>
     <row r="474">
@@ -8451,10 +8451,10 @@
         <v>Passed</v>
       </c>
       <c r="D474">
-        <v>0.73</v>
+        <v>1.71</v>
       </c>
       <c r="E474" t="str">
-        <v>2026-07-30T14:07:10.534Z</v>
+        <v>2026-07-30T21:47:02.487Z</v>
       </c>
     </row>
     <row r="475">
@@ -8468,10 +8468,10 @@
         <v>Passed</v>
       </c>
       <c r="D475">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="E475" t="str">
-        <v>2026-07-30T14:07:11.534Z</v>
+        <v>2026-07-30T21:47:03.487Z</v>
       </c>
     </row>
     <row r="476">
@@ -8485,10 +8485,10 @@
         <v>Passed</v>
       </c>
       <c r="D476">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E476" t="str">
-        <v>2026-07-30T14:07:12.534Z</v>
+        <v>2026-07-30T21:47:04.487Z</v>
       </c>
     </row>
     <row r="477">
@@ -8502,10 +8502,10 @@
         <v>Passed</v>
       </c>
       <c r="D477">
-        <v>1.44</v>
+        <v>0.83</v>
       </c>
       <c r="E477" t="str">
-        <v>2026-07-30T14:07:13.534Z</v>
+        <v>2026-07-30T21:47:05.487Z</v>
       </c>
     </row>
     <row r="478">
@@ -8519,10 +8519,10 @@
         <v>Passed</v>
       </c>
       <c r="D478">
-        <v>1.47</v>
+        <v>0.45</v>
       </c>
       <c r="E478" t="str">
-        <v>2026-07-30T14:07:14.534Z</v>
+        <v>2026-07-30T21:47:06.487Z</v>
       </c>
     </row>
     <row r="479">
@@ -8536,10 +8536,10 @@
         <v>Passed</v>
       </c>
       <c r="D479">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="E479" t="str">
-        <v>2026-07-30T14:07:15.534Z</v>
+        <v>2026-07-30T21:47:07.487Z</v>
       </c>
     </row>
     <row r="480">
@@ -8553,10 +8553,10 @@
         <v>Passed</v>
       </c>
       <c r="D480">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="E480" t="str">
-        <v>2026-07-30T14:07:16.534Z</v>
+        <v>2026-07-30T21:47:08.487Z</v>
       </c>
     </row>
     <row r="481">
@@ -8570,10 +8570,10 @@
         <v>Passed</v>
       </c>
       <c r="D481">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="E481" t="str">
-        <v>2026-07-30T14:07:17.534Z</v>
+        <v>2026-07-30T21:47:09.487Z</v>
       </c>
     </row>
     <row r="482">
@@ -8587,10 +8587,10 @@
         <v>Passed</v>
       </c>
       <c r="D482">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="E482" t="str">
-        <v>2026-07-30T14:07:18.534Z</v>
+        <v>2026-07-30T21:47:10.487Z</v>
       </c>
     </row>
     <row r="483">
@@ -8604,10 +8604,10 @@
         <v>Passed</v>
       </c>
       <c r="D483">
-        <v>0.47</v>
+        <v>1.3</v>
       </c>
       <c r="E483" t="str">
-        <v>2026-07-30T14:07:19.534Z</v>
+        <v>2026-07-30T21:47:11.487Z</v>
       </c>
     </row>
     <row r="484">
@@ -8621,10 +8621,10 @@
         <v>Passed</v>
       </c>
       <c r="D484">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="E484" t="str">
-        <v>2026-07-30T14:07:20.534Z</v>
+        <v>2026-07-30T21:47:12.487Z</v>
       </c>
     </row>
     <row r="485">
@@ -8638,10 +8638,10 @@
         <v>Passed</v>
       </c>
       <c r="D485">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="E485" t="str">
-        <v>2026-07-30T14:07:21.534Z</v>
+        <v>2026-07-30T21:47:13.487Z</v>
       </c>
     </row>
     <row r="486">
@@ -8655,10 +8655,10 @@
         <v>Passed</v>
       </c>
       <c r="D486">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="E486" t="str">
-        <v>2026-07-30T14:07:22.534Z</v>
+        <v>2026-07-30T21:47:14.487Z</v>
       </c>
     </row>
     <row r="487">
@@ -8672,10 +8672,10 @@
         <v>Passed</v>
       </c>
       <c r="D487">
-        <v>0.37</v>
+        <v>0.78</v>
       </c>
       <c r="E487" t="str">
-        <v>2026-07-30T14:07:23.534Z</v>
+        <v>2026-07-30T21:47:15.487Z</v>
       </c>
     </row>
     <row r="488">
@@ -8689,10 +8689,10 @@
         <v>Passed</v>
       </c>
       <c r="D488">
-        <v>1.52</v>
+        <v>0.53</v>
       </c>
       <c r="E488" t="str">
-        <v>2026-07-30T14:07:24.534Z</v>
+        <v>2026-07-30T21:47:16.487Z</v>
       </c>
     </row>
     <row r="489">
@@ -8706,10 +8706,10 @@
         <v>Passed</v>
       </c>
       <c r="D489">
-        <v>0.26</v>
+        <v>1.84</v>
       </c>
       <c r="E489" t="str">
-        <v>2026-07-30T14:07:25.534Z</v>
+        <v>2026-07-30T21:47:17.487Z</v>
       </c>
     </row>
     <row r="490">
@@ -8723,10 +8723,10 @@
         <v>Passed</v>
       </c>
       <c r="D490">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="E490" t="str">
-        <v>2026-07-30T14:07:26.534Z</v>
+        <v>2026-07-30T21:47:18.487Z</v>
       </c>
     </row>
     <row r="491">
@@ -8740,10 +8740,10 @@
         <v>Passed</v>
       </c>
       <c r="D491">
-        <v>1.16</v>
+        <v>0.69</v>
       </c>
       <c r="E491" t="str">
-        <v>2026-07-30T14:07:27.534Z</v>
+        <v>2026-07-30T21:47:19.487Z</v>
       </c>
     </row>
     <row r="492">
@@ -8757,10 +8757,10 @@
         <v>Passed</v>
       </c>
       <c r="D492">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="E492" t="str">
-        <v>2026-07-30T14:07:28.534Z</v>
+        <v>2026-07-30T21:47:20.487Z</v>
       </c>
     </row>
     <row r="493">
@@ -8774,10 +8774,10 @@
         <v>Passed</v>
       </c>
       <c r="D493">
-        <v>0.53</v>
+        <v>1.73</v>
       </c>
       <c r="E493" t="str">
-        <v>2026-07-30T14:07:29.534Z</v>
+        <v>2026-07-30T21:47:21.487Z</v>
       </c>
     </row>
     <row r="494">
@@ -8791,10 +8791,10 @@
         <v>Passed</v>
       </c>
       <c r="D494">
-        <v>0.03</v>
+        <v>0.87</v>
       </c>
       <c r="E494" t="str">
-        <v>2026-07-30T14:07:30.534Z</v>
+        <v>2026-07-30T21:47:22.487Z</v>
       </c>
     </row>
     <row r="495">
@@ -8808,10 +8808,10 @@
         <v>Passed</v>
       </c>
       <c r="D495">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="E495" t="str">
-        <v>2026-07-30T14:07:31.534Z</v>
+        <v>2026-07-30T21:47:23.487Z</v>
       </c>
     </row>
     <row r="496">
@@ -8825,10 +8825,10 @@
         <v>Passed</v>
       </c>
       <c r="D496">
-        <v>0.56</v>
+        <v>1.65</v>
       </c>
       <c r="E496" t="str">
-        <v>2026-07-30T14:07:32.534Z</v>
+        <v>2026-07-30T21:47:24.487Z</v>
       </c>
     </row>
     <row r="497">
@@ -8842,10 +8842,10 @@
         <v>Passed</v>
       </c>
       <c r="D497">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="E497" t="str">
-        <v>2026-07-30T14:07:33.534Z</v>
+        <v>2026-07-30T21:47:25.487Z</v>
       </c>
     </row>
     <row r="498">
@@ -8859,10 +8859,10 @@
         <v>Passed</v>
       </c>
       <c r="D498">
-        <v>0.71</v>
+        <v>0.2</v>
       </c>
       <c r="E498" t="str">
-        <v>2026-07-30T14:07:34.534Z</v>
+        <v>2026-07-30T21:47:26.487Z</v>
       </c>
     </row>
     <row r="499">
@@ -8876,10 +8876,10 @@
         <v>Passed</v>
       </c>
       <c r="D499">
-        <v>0.85</v>
+        <v>0.66</v>
       </c>
       <c r="E499" t="str">
-        <v>2026-07-30T14:07:35.534Z</v>
+        <v>2026-07-30T21:47:27.487Z</v>
       </c>
     </row>
     <row r="500">
@@ -8893,10 +8893,10 @@
         <v>Passed</v>
       </c>
       <c r="D500">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="E500" t="str">
-        <v>2026-07-30T14:07:36.534Z</v>
+        <v>2026-07-30T21:47:28.487Z</v>
       </c>
     </row>
     <row r="501">
@@ -8910,10 +8910,10 @@
         <v>Passed</v>
       </c>
       <c r="D501">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="E501" t="str">
-        <v>2026-07-30T14:07:37.534Z</v>
+        <v>2026-07-30T21:47:29.487Z</v>
       </c>
     </row>
     <row r="502">
@@ -8927,10 +8927,10 @@
         <v>Passed</v>
       </c>
       <c r="D502">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="E502" t="str">
-        <v>2026-07-30T14:07:38.534Z</v>
+        <v>2026-07-30T21:47:30.487Z</v>
       </c>
     </row>
     <row r="503">
@@ -8944,10 +8944,10 @@
         <v>Passed</v>
       </c>
       <c r="D503">
-        <v>0.51</v>
+        <v>1.6</v>
       </c>
       <c r="E503" t="str">
-        <v>2026-07-30T14:07:39.534Z</v>
+        <v>2026-07-30T21:47:31.487Z</v>
       </c>
     </row>
     <row r="504">
@@ -8961,10 +8961,10 @@
         <v>Passed</v>
       </c>
       <c r="D504">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="E504" t="str">
-        <v>2026-07-30T14:07:40.534Z</v>
+        <v>2026-07-30T21:47:32.487Z</v>
       </c>
     </row>
     <row r="505">
@@ -8978,10 +8978,10 @@
         <v>Passed</v>
       </c>
       <c r="D505">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="E505" t="str">
-        <v>2026-07-30T14:07:41.534Z</v>
+        <v>2026-07-30T21:47:33.487Z</v>
       </c>
     </row>
     <row r="506">
@@ -8995,10 +8995,10 @@
         <v>Passed</v>
       </c>
       <c r="D506">
-        <v>0.16</v>
+        <v>1.3</v>
       </c>
       <c r="E506" t="str">
-        <v>2026-07-30T14:07:42.534Z</v>
+        <v>2026-07-30T21:47:34.487Z</v>
       </c>
     </row>
     <row r="507">
@@ -9012,10 +9012,10 @@
         <v>Passed</v>
       </c>
       <c r="D507">
-        <v>1.44</v>
+        <v>0.48</v>
       </c>
       <c r="E507" t="str">
-        <v>2026-07-30T14:07:43.534Z</v>
+        <v>2026-07-30T21:47:35.487Z</v>
       </c>
     </row>
     <row r="508">
@@ -9029,10 +9029,10 @@
         <v>Passed</v>
       </c>
       <c r="D508">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="E508" t="str">
-        <v>2026-07-30T14:07:44.534Z</v>
+        <v>2026-07-30T21:47:36.487Z</v>
       </c>
     </row>
     <row r="509">
@@ -9046,10 +9046,10 @@
         <v>Passed</v>
       </c>
       <c r="D509">
-        <v>0.11</v>
+        <v>1.69</v>
       </c>
       <c r="E509" t="str">
-        <v>2026-07-30T14:07:45.534Z</v>
+        <v>2026-07-30T21:47:37.487Z</v>
       </c>
     </row>
     <row r="510">
@@ -9063,10 +9063,10 @@
         <v>Passed</v>
       </c>
       <c r="D510">
-        <v>1.52</v>
+        <v>0.83</v>
       </c>
       <c r="E510" t="str">
-        <v>2026-07-30T14:07:46.534Z</v>
+        <v>2026-07-30T21:47:38.487Z</v>
       </c>
     </row>
     <row r="511">
@@ -9080,10 +9080,10 @@
         <v>Passed</v>
       </c>
       <c r="D511">
-        <v>0.14</v>
+        <v>0.58</v>
       </c>
       <c r="E511" t="str">
-        <v>2026-07-30T14:07:47.534Z</v>
+        <v>2026-07-30T21:47:39.487Z</v>
       </c>
     </row>
     <row r="512">
@@ -9097,10 +9097,10 @@
         <v>Passed</v>
       </c>
       <c r="D512">
-        <v>0.56</v>
+        <v>0.09</v>
       </c>
       <c r="E512" t="str">
-        <v>2026-07-30T14:07:48.534Z</v>
+        <v>2026-07-30T21:47:40.487Z</v>
       </c>
     </row>
     <row r="513">
@@ -9114,10 +9114,10 @@
         <v>Passed</v>
       </c>
       <c r="D513">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="E513" t="str">
-        <v>2026-07-30T14:07:49.534Z</v>
+        <v>2026-07-30T21:47:41.487Z</v>
       </c>
     </row>
     <row r="514">
@@ -9131,10 +9131,10 @@
         <v>Passed</v>
       </c>
       <c r="D514">
-        <v>1.77</v>
+        <v>0.16</v>
       </c>
       <c r="E514" t="str">
-        <v>2026-07-30T14:07:50.534Z</v>
+        <v>2026-07-30T21:47:42.487Z</v>
       </c>
     </row>
     <row r="515">
@@ -9148,10 +9148,10 @@
         <v>Passed</v>
       </c>
       <c r="D515">
-        <v>1.31</v>
+        <v>0.28</v>
       </c>
       <c r="E515" t="str">
-        <v>2026-07-30T14:07:51.534Z</v>
+        <v>2026-07-30T21:47:43.487Z</v>
       </c>
     </row>
     <row r="516">
@@ -9165,10 +9165,10 @@
         <v>Passed</v>
       </c>
       <c r="D516">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="E516" t="str">
-        <v>2026-07-30T14:07:52.534Z</v>
+        <v>2026-07-30T21:47:44.487Z</v>
       </c>
     </row>
     <row r="517">
@@ -9182,10 +9182,10 @@
         <v>Passed</v>
       </c>
       <c r="D517">
-        <v>0.28</v>
+        <v>1.42</v>
       </c>
       <c r="E517" t="str">
-        <v>2026-07-30T14:07:53.534Z</v>
+        <v>2026-07-30T21:47:45.487Z</v>
       </c>
     </row>
     <row r="518">
@@ -9199,10 +9199,10 @@
         <v>Passed</v>
       </c>
       <c r="D518">
-        <v>1.64</v>
+        <v>0.63</v>
       </c>
       <c r="E518" t="str">
-        <v>2026-07-30T14:07:54.534Z</v>
+        <v>2026-07-30T21:47:46.487Z</v>
       </c>
     </row>
     <row r="519">
@@ -9216,10 +9216,10 @@
         <v>Passed</v>
       </c>
       <c r="D519">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="E519" t="str">
-        <v>2026-07-30T14:07:55.534Z</v>
+        <v>2026-07-30T21:47:47.487Z</v>
       </c>
     </row>
     <row r="520">
@@ -9233,10 +9233,10 @@
         <v>Passed</v>
       </c>
       <c r="D520">
-        <v>0.38</v>
+        <v>0.96</v>
       </c>
       <c r="E520" t="str">
-        <v>2026-07-30T14:07:56.534Z</v>
+        <v>2026-07-30T21:47:48.487Z</v>
       </c>
     </row>
     <row r="521">
@@ -9250,10 +9250,10 @@
         <v>Passed</v>
       </c>
       <c r="D521">
-        <v>1.71</v>
+        <v>0.64</v>
       </c>
       <c r="E521" t="str">
-        <v>2026-07-30T14:07:57.534Z</v>
+        <v>2026-07-30T21:47:49.487Z</v>
       </c>
     </row>
     <row r="522">
@@ -9267,10 +9267,10 @@
         <v>Passed</v>
       </c>
       <c r="D522">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="E522" t="str">
-        <v>2026-07-30T14:07:58.534Z</v>
+        <v>2026-07-30T21:47:50.487Z</v>
       </c>
     </row>
     <row r="523">
@@ -9284,10 +9284,10 @@
         <v>Passed</v>
       </c>
       <c r="D523">
-        <v>0.74</v>
+        <v>1.64</v>
       </c>
       <c r="E523" t="str">
-        <v>2026-07-30T14:07:59.534Z</v>
+        <v>2026-07-30T21:47:51.487Z</v>
       </c>
     </row>
     <row r="524">
@@ -9301,10 +9301,10 @@
         <v>Passed</v>
       </c>
       <c r="D524">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="E524" t="str">
-        <v>2026-07-30T14:08:00.534Z</v>
+        <v>2026-07-30T21:47:52.487Z</v>
       </c>
     </row>
     <row r="525">
@@ -9318,10 +9318,10 @@
         <v>Passed</v>
       </c>
       <c r="D525">
-        <v>0.98</v>
+        <v>1.76</v>
       </c>
       <c r="E525" t="str">
-        <v>2026-07-30T14:08:01.534Z</v>
+        <v>2026-07-30T21:47:53.487Z</v>
       </c>
     </row>
     <row r="526">
@@ -9335,10 +9335,10 @@
         <v>Passed</v>
       </c>
       <c r="D526">
-        <v>0.01</v>
+        <v>1.36</v>
       </c>
       <c r="E526" t="str">
-        <v>2026-07-30T14:08:02.534Z</v>
+        <v>2026-07-30T21:47:54.487Z</v>
       </c>
     </row>
     <row r="527">
@@ -9352,10 +9352,10 @@
         <v>Passed</v>
       </c>
       <c r="D527">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="E527" t="str">
-        <v>2026-07-30T14:08:03.534Z</v>
+        <v>2026-07-30T21:47:55.487Z</v>
       </c>
     </row>
     <row r="528">
@@ -9372,7 +9372,7 @@
         <v>1.98</v>
       </c>
       <c r="E528" t="str">
-        <v>2026-07-30T14:08:04.534Z</v>
+        <v>2026-07-30T21:47:56.487Z</v>
       </c>
     </row>
     <row r="529">
@@ -9386,10 +9386,10 @@
         <v>Passed</v>
       </c>
       <c r="D529">
-        <v>0.46</v>
+        <v>1.77</v>
       </c>
       <c r="E529" t="str">
-        <v>2026-07-30T14:08:05.534Z</v>
+        <v>2026-07-30T21:47:57.487Z</v>
       </c>
     </row>
     <row r="530">
@@ -9403,10 +9403,10 @@
         <v>Passed</v>
       </c>
       <c r="D530">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="E530" t="str">
-        <v>2026-07-30T14:08:06.534Z</v>
+        <v>2026-07-30T21:47:58.487Z</v>
       </c>
     </row>
     <row r="531">
@@ -9420,10 +9420,10 @@
         <v>Passed</v>
       </c>
       <c r="D531">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
       <c r="E531" t="str">
-        <v>2026-07-30T14:08:07.534Z</v>
+        <v>2026-07-30T21:47:59.487Z</v>
       </c>
     </row>
     <row r="532">
@@ -9437,10 +9437,10 @@
         <v>Passed</v>
       </c>
       <c r="D532">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="E532" t="str">
-        <v>2026-07-30T14:08:08.534Z</v>
+        <v>2026-07-30T21:48:00.487Z</v>
       </c>
     </row>
     <row r="533">
@@ -9454,10 +9454,10 @@
         <v>Passed</v>
       </c>
       <c r="D533">
-        <v>0.47</v>
+        <v>0.03</v>
       </c>
       <c r="E533" t="str">
-        <v>2026-07-30T14:08:09.534Z</v>
+        <v>2026-07-30T21:48:01.487Z</v>
       </c>
     </row>
     <row r="534">
@@ -9471,10 +9471,10 @@
         <v>Passed</v>
       </c>
       <c r="D534">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="E534" t="str">
-        <v>2026-07-30T14:08:10.534Z</v>
+        <v>2026-07-30T21:48:02.487Z</v>
       </c>
     </row>
     <row r="535">
@@ -9488,10 +9488,10 @@
         <v>Passed</v>
       </c>
       <c r="D535">
-        <v>0.58</v>
+        <v>0.69</v>
       </c>
       <c r="E535" t="str">
-        <v>2026-07-30T14:08:11.534Z</v>
+        <v>2026-07-30T21:48:03.487Z</v>
       </c>
     </row>
     <row r="536">
@@ -9505,10 +9505,10 @@
         <v>Passed</v>
       </c>
       <c r="D536">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="E536" t="str">
-        <v>2026-07-30T14:08:12.534Z</v>
+        <v>2026-07-30T21:48:04.487Z</v>
       </c>
     </row>
     <row r="537">
@@ -9522,10 +9522,10 @@
         <v>Passed</v>
       </c>
       <c r="D537">
-        <v>0.25</v>
+        <v>1.69</v>
       </c>
       <c r="E537" t="str">
-        <v>2026-07-30T14:08:13.534Z</v>
+        <v>2026-07-30T21:48:05.487Z</v>
       </c>
     </row>
     <row r="538">
@@ -9539,10 +9539,10 @@
         <v>Passed</v>
       </c>
       <c r="D538">
-        <v>0.77</v>
+        <v>1.58</v>
       </c>
       <c r="E538" t="str">
-        <v>2026-07-30T14:08:14.534Z</v>
+        <v>2026-07-30T21:48:06.487Z</v>
       </c>
     </row>
     <row r="539">
@@ -9556,10 +9556,10 @@
         <v>Passed</v>
       </c>
       <c r="D539">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="E539" t="str">
-        <v>2026-07-30T14:08:15.534Z</v>
+        <v>2026-07-30T21:48:07.487Z</v>
       </c>
     </row>
     <row r="540">
@@ -9570,13 +9570,13 @@
         <v>Verify APILoad functionality module 539</v>
       </c>
       <c r="C540" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D540">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="E540" t="str">
-        <v>2026-07-30T14:08:16.534Z</v>
+        <v>2026-07-30T21:48:08.487Z</v>
       </c>
     </row>
     <row r="541">
@@ -9590,10 +9590,10 @@
         <v>Passed</v>
       </c>
       <c r="D541">
-        <v>1.86</v>
+        <v>0.05</v>
       </c>
       <c r="E541" t="str">
-        <v>2026-07-30T14:08:17.534Z</v>
+        <v>2026-07-30T21:48:09.487Z</v>
       </c>
     </row>
     <row r="542">
@@ -9607,10 +9607,10 @@
         <v>Passed</v>
       </c>
       <c r="D542">
-        <v>0.09</v>
+        <v>1.55</v>
       </c>
       <c r="E542" t="str">
-        <v>2026-07-30T14:08:18.534Z</v>
+        <v>2026-07-30T21:48:10.487Z</v>
       </c>
     </row>
     <row r="543">
@@ -9624,10 +9624,10 @@
         <v>Passed</v>
       </c>
       <c r="D543">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="E543" t="str">
-        <v>2026-07-30T14:08:19.534Z</v>
+        <v>2026-07-30T21:48:11.487Z</v>
       </c>
     </row>
     <row r="544">
@@ -9641,10 +9641,10 @@
         <v>Passed</v>
       </c>
       <c r="D544">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="E544" t="str">
-        <v>2026-07-30T14:08:20.534Z</v>
+        <v>2026-07-30T21:48:12.487Z</v>
       </c>
     </row>
     <row r="545">
@@ -9658,10 +9658,10 @@
         <v>Passed</v>
       </c>
       <c r="D545">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E545" t="str">
-        <v>2026-07-30T14:08:21.534Z</v>
+        <v>2026-07-30T21:48:13.487Z</v>
       </c>
     </row>
     <row r="546">
@@ -9675,10 +9675,10 @@
         <v>Passed</v>
       </c>
       <c r="D546">
-        <v>1.97</v>
+        <v>0.65</v>
       </c>
       <c r="E546" t="str">
-        <v>2026-07-30T14:08:22.534Z</v>
+        <v>2026-07-30T21:48:14.487Z</v>
       </c>
     </row>
     <row r="547">
@@ -9692,10 +9692,10 @@
         <v>Passed</v>
       </c>
       <c r="D547">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="E547" t="str">
-        <v>2026-07-30T14:08:23.534Z</v>
+        <v>2026-07-30T21:48:15.487Z</v>
       </c>
     </row>
     <row r="548">
@@ -9709,10 +9709,10 @@
         <v>Passed</v>
       </c>
       <c r="D548">
-        <v>0.76</v>
+        <v>0.15</v>
       </c>
       <c r="E548" t="str">
-        <v>2026-07-30T14:08:24.534Z</v>
+        <v>2026-07-30T21:48:16.487Z</v>
       </c>
     </row>
     <row r="549">
@@ -9726,10 +9726,10 @@
         <v>Passed</v>
       </c>
       <c r="D549">
-        <v>0.5</v>
+        <v>0.97</v>
       </c>
       <c r="E549" t="str">
-        <v>2026-07-30T14:08:25.534Z</v>
+        <v>2026-07-30T21:48:17.487Z</v>
       </c>
     </row>
     <row r="550">
@@ -9743,10 +9743,10 @@
         <v>Passed</v>
       </c>
       <c r="D550">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="E550" t="str">
-        <v>2026-07-30T14:08:26.534Z</v>
+        <v>2026-07-30T21:48:18.487Z</v>
       </c>
     </row>
     <row r="551">
@@ -9760,10 +9760,10 @@
         <v>Passed</v>
       </c>
       <c r="D551">
-        <v>0.77</v>
+        <v>0.07</v>
       </c>
       <c r="E551" t="str">
-        <v>2026-07-30T14:08:27.534Z</v>
+        <v>2026-07-30T21:48:19.487Z</v>
       </c>
     </row>
     <row r="552">
@@ -9780,7 +9780,7 @@
         <v>0.05</v>
       </c>
       <c r="E552" t="str">
-        <v>2026-07-30T14:08:28.534Z</v>
+        <v>2026-07-30T21:48:20.487Z</v>
       </c>
     </row>
     <row r="553">
@@ -9794,10 +9794,10 @@
         <v>Passed</v>
       </c>
       <c r="D553">
-        <v>1.42</v>
+        <v>0.97</v>
       </c>
       <c r="E553" t="str">
-        <v>2026-07-30T14:08:29.534Z</v>
+        <v>2026-07-30T21:48:21.487Z</v>
       </c>
     </row>
     <row r="554">
@@ -9811,10 +9811,10 @@
         <v>Passed</v>
       </c>
       <c r="D554">
-        <v>1.8</v>
+        <v>0.67</v>
       </c>
       <c r="E554" t="str">
-        <v>2026-07-30T14:08:30.534Z</v>
+        <v>2026-07-30T21:48:22.487Z</v>
       </c>
     </row>
     <row r="555">
@@ -9828,10 +9828,10 @@
         <v>Passed</v>
       </c>
       <c r="D555">
-        <v>0.07</v>
+        <v>1.31</v>
       </c>
       <c r="E555" t="str">
-        <v>2026-07-30T14:08:31.534Z</v>
+        <v>2026-07-30T21:48:23.487Z</v>
       </c>
     </row>
     <row r="556">
@@ -9845,10 +9845,10 @@
         <v>Passed</v>
       </c>
       <c r="D556">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="E556" t="str">
-        <v>2026-07-30T14:08:32.534Z</v>
+        <v>2026-07-30T21:48:24.487Z</v>
       </c>
     </row>
     <row r="557">
@@ -9862,10 +9862,10 @@
         <v>Passed</v>
       </c>
       <c r="D557">
-        <v>1.28</v>
+        <v>0.87</v>
       </c>
       <c r="E557" t="str">
-        <v>2026-07-30T14:08:33.534Z</v>
+        <v>2026-07-30T21:48:25.487Z</v>
       </c>
     </row>
     <row r="558">
@@ -9879,10 +9879,10 @@
         <v>Passed</v>
       </c>
       <c r="D558">
-        <v>0.99</v>
+        <v>1.29</v>
       </c>
       <c r="E558" t="str">
-        <v>2026-07-30T14:08:34.534Z</v>
+        <v>2026-07-30T21:48:26.487Z</v>
       </c>
     </row>
     <row r="559">
@@ -9896,10 +9896,10 @@
         <v>Passed</v>
       </c>
       <c r="D559">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="E559" t="str">
-        <v>2026-07-30T14:08:35.534Z</v>
+        <v>2026-07-30T21:48:27.487Z</v>
       </c>
     </row>
     <row r="560">
@@ -9910,13 +9910,13 @@
         <v>Verify APILoad functionality module 559</v>
       </c>
       <c r="C560" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D560">
-        <v>0.21</v>
+        <v>1.67</v>
       </c>
       <c r="E560" t="str">
-        <v>2026-07-30T14:08:36.534Z</v>
+        <v>2026-07-30T21:48:28.487Z</v>
       </c>
     </row>
     <row r="561">
@@ -9930,10 +9930,10 @@
         <v>Passed</v>
       </c>
       <c r="D561">
-        <v>1.86</v>
+        <v>0.27</v>
       </c>
       <c r="E561" t="str">
-        <v>2026-07-30T14:08:37.534Z</v>
+        <v>2026-07-30T21:48:29.487Z</v>
       </c>
     </row>
     <row r="562">
@@ -9947,10 +9947,10 @@
         <v>Passed</v>
       </c>
       <c r="D562">
-        <v>1.99</v>
+        <v>0.74</v>
       </c>
       <c r="E562" t="str">
-        <v>2026-07-30T14:08:38.534Z</v>
+        <v>2026-07-30T21:48:30.487Z</v>
       </c>
     </row>
     <row r="563">
@@ -9961,13 +9961,13 @@
         <v>Verify APILoad functionality module 562</v>
       </c>
       <c r="C563" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D563">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="E563" t="str">
-        <v>2026-07-30T14:08:39.534Z</v>
+        <v>2026-07-30T21:48:31.487Z</v>
       </c>
     </row>
     <row r="564">
@@ -9981,10 +9981,10 @@
         <v>Passed</v>
       </c>
       <c r="D564">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="E564" t="str">
-        <v>2026-07-30T14:08:40.534Z</v>
+        <v>2026-07-30T21:48:32.487Z</v>
       </c>
     </row>
     <row r="565">
@@ -9998,10 +9998,10 @@
         <v>Passed</v>
       </c>
       <c r="D565">
-        <v>1.49</v>
+        <v>1</v>
       </c>
       <c r="E565" t="str">
-        <v>2026-07-30T14:08:41.534Z</v>
+        <v>2026-07-30T21:48:33.487Z</v>
       </c>
     </row>
     <row r="566">
@@ -10015,10 +10015,10 @@
         <v>Passed</v>
       </c>
       <c r="D566">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="E566" t="str">
-        <v>2026-07-30T14:08:42.534Z</v>
+        <v>2026-07-30T21:48:34.487Z</v>
       </c>
     </row>
     <row r="567">
@@ -10032,10 +10032,10 @@
         <v>Passed</v>
       </c>
       <c r="D567">
-        <v>1.31</v>
+        <v>0.86</v>
       </c>
       <c r="E567" t="str">
-        <v>2026-07-30T14:08:43.534Z</v>
+        <v>2026-07-30T21:48:35.487Z</v>
       </c>
     </row>
     <row r="568">
@@ -10049,10 +10049,10 @@
         <v>Passed</v>
       </c>
       <c r="D568">
-        <v>0.88</v>
+        <v>1.84</v>
       </c>
       <c r="E568" t="str">
-        <v>2026-07-30T14:08:44.534Z</v>
+        <v>2026-07-30T21:48:36.487Z</v>
       </c>
     </row>
     <row r="569">
@@ -10066,10 +10066,10 @@
         <v>Passed</v>
       </c>
       <c r="D569">
-        <v>0.07</v>
+        <v>1.1</v>
       </c>
       <c r="E569" t="str">
-        <v>2026-07-30T14:08:45.534Z</v>
+        <v>2026-07-30T21:48:37.487Z</v>
       </c>
     </row>
     <row r="570">
@@ -10083,10 +10083,10 @@
         <v>Passed</v>
       </c>
       <c r="D570">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="E570" t="str">
-        <v>2026-07-30T14:08:46.534Z</v>
+        <v>2026-07-30T21:48:38.487Z</v>
       </c>
     </row>
     <row r="571">
@@ -10100,10 +10100,10 @@
         <v>Passed</v>
       </c>
       <c r="D571">
-        <v>1.88</v>
+        <v>0.64</v>
       </c>
       <c r="E571" t="str">
-        <v>2026-07-30T14:08:47.534Z</v>
+        <v>2026-07-30T21:48:39.487Z</v>
       </c>
     </row>
     <row r="572">
@@ -10117,10 +10117,10 @@
         <v>Passed</v>
       </c>
       <c r="D572">
-        <v>1.45</v>
+        <v>0.87</v>
       </c>
       <c r="E572" t="str">
-        <v>2026-07-30T14:08:48.534Z</v>
+        <v>2026-07-30T21:48:40.487Z</v>
       </c>
     </row>
     <row r="573">
@@ -10134,10 +10134,10 @@
         <v>Passed</v>
       </c>
       <c r="D573">
-        <v>1.16</v>
+        <v>0.14</v>
       </c>
       <c r="E573" t="str">
-        <v>2026-07-30T14:08:49.534Z</v>
+        <v>2026-07-30T21:48:41.487Z</v>
       </c>
     </row>
     <row r="574">
@@ -10151,10 +10151,10 @@
         <v>Passed</v>
       </c>
       <c r="D574">
-        <v>0.51</v>
+        <v>0.19</v>
       </c>
       <c r="E574" t="str">
-        <v>2026-07-30T14:08:50.534Z</v>
+        <v>2026-07-30T21:48:42.487Z</v>
       </c>
     </row>
     <row r="575">
@@ -10168,10 +10168,10 @@
         <v>Passed</v>
       </c>
       <c r="D575">
-        <v>1.12</v>
+        <v>0.24</v>
       </c>
       <c r="E575" t="str">
-        <v>2026-07-30T14:08:51.534Z</v>
+        <v>2026-07-30T21:48:43.487Z</v>
       </c>
     </row>
     <row r="576">
@@ -10185,10 +10185,10 @@
         <v>Passed</v>
       </c>
       <c r="D576">
-        <v>1.54</v>
+        <v>0.72</v>
       </c>
       <c r="E576" t="str">
-        <v>2026-07-30T14:08:52.534Z</v>
+        <v>2026-07-30T21:48:44.487Z</v>
       </c>
     </row>
     <row r="577">
@@ -10202,10 +10202,10 @@
         <v>Passed</v>
       </c>
       <c r="D577">
-        <v>0.34</v>
+        <v>1.42</v>
       </c>
       <c r="E577" t="str">
-        <v>2026-07-30T14:08:53.534Z</v>
+        <v>2026-07-30T21:48:45.487Z</v>
       </c>
     </row>
     <row r="578">
@@ -10219,10 +10219,10 @@
         <v>Passed</v>
       </c>
       <c r="D578">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="E578" t="str">
-        <v>2026-07-30T14:08:54.534Z</v>
+        <v>2026-07-30T21:48:46.487Z</v>
       </c>
     </row>
     <row r="579">
@@ -10236,10 +10236,10 @@
         <v>Passed</v>
       </c>
       <c r="D579">
-        <v>0.29</v>
+        <v>1.86</v>
       </c>
       <c r="E579" t="str">
-        <v>2026-07-30T14:08:55.534Z</v>
+        <v>2026-07-30T21:48:47.487Z</v>
       </c>
     </row>
     <row r="580">
@@ -10253,10 +10253,10 @@
         <v>Passed</v>
       </c>
       <c r="D580">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="E580" t="str">
-        <v>2026-07-30T14:08:56.534Z</v>
+        <v>2026-07-30T21:48:48.487Z</v>
       </c>
     </row>
     <row r="581">
@@ -10270,10 +10270,10 @@
         <v>Passed</v>
       </c>
       <c r="D581">
-        <v>1.71</v>
+        <v>0.46</v>
       </c>
       <c r="E581" t="str">
-        <v>2026-07-30T14:08:57.534Z</v>
+        <v>2026-07-30T21:48:49.487Z</v>
       </c>
     </row>
     <row r="582">
@@ -10287,10 +10287,10 @@
         <v>Passed</v>
       </c>
       <c r="D582">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="E582" t="str">
-        <v>2026-07-30T14:08:58.534Z</v>
+        <v>2026-07-30T21:48:50.487Z</v>
       </c>
     </row>
     <row r="583">
@@ -10304,10 +10304,10 @@
         <v>Passed</v>
       </c>
       <c r="D583">
-        <v>0.12</v>
+        <v>1.58</v>
       </c>
       <c r="E583" t="str">
-        <v>2026-07-30T14:08:59.534Z</v>
+        <v>2026-07-30T21:48:51.487Z</v>
       </c>
     </row>
     <row r="584">
@@ -10321,10 +10321,10 @@
         <v>Passed</v>
       </c>
       <c r="D584">
-        <v>0.4</v>
+        <v>1.88</v>
       </c>
       <c r="E584" t="str">
-        <v>2026-07-30T14:09:00.534Z</v>
+        <v>2026-07-30T21:48:52.487Z</v>
       </c>
     </row>
     <row r="585">
@@ -10338,10 +10338,10 @@
         <v>Passed</v>
       </c>
       <c r="D585">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="E585" t="str">
-        <v>2026-07-30T14:09:01.534Z</v>
+        <v>2026-07-30T21:48:53.487Z</v>
       </c>
     </row>
     <row r="586">
@@ -10355,10 +10355,10 @@
         <v>Passed</v>
       </c>
       <c r="D586">
-        <v>0.81</v>
+        <v>0.02</v>
       </c>
       <c r="E586" t="str">
-        <v>2026-07-30T14:09:02.534Z</v>
+        <v>2026-07-30T21:48:54.487Z</v>
       </c>
     </row>
     <row r="587">
@@ -10372,10 +10372,10 @@
         <v>Passed</v>
       </c>
       <c r="D587">
-        <v>0.86</v>
+        <v>0.6</v>
       </c>
       <c r="E587" t="str">
-        <v>2026-07-30T14:09:03.534Z</v>
+        <v>2026-07-30T21:48:55.487Z</v>
       </c>
     </row>
     <row r="588">
@@ -10389,10 +10389,10 @@
         <v>Passed</v>
       </c>
       <c r="D588">
-        <v>0.25</v>
+        <v>1.21</v>
       </c>
       <c r="E588" t="str">
-        <v>2026-07-30T14:09:04.534Z</v>
+        <v>2026-07-30T21:48:56.487Z</v>
       </c>
     </row>
     <row r="589">
@@ -10406,10 +10406,10 @@
         <v>Passed</v>
       </c>
       <c r="D589">
-        <v>1.02</v>
+        <v>0.59</v>
       </c>
       <c r="E589" t="str">
-        <v>2026-07-30T14:09:05.534Z</v>
+        <v>2026-07-30T21:48:57.487Z</v>
       </c>
     </row>
     <row r="590">
@@ -10423,10 +10423,10 @@
         <v>Passed</v>
       </c>
       <c r="D590">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="E590" t="str">
-        <v>2026-07-30T14:09:06.534Z</v>
+        <v>2026-07-30T21:48:58.487Z</v>
       </c>
     </row>
     <row r="591">
@@ -10440,10 +10440,10 @@
         <v>Passed</v>
       </c>
       <c r="D591">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="E591" t="str">
-        <v>2026-07-30T14:09:07.534Z</v>
+        <v>2026-07-30T21:48:59.487Z</v>
       </c>
     </row>
     <row r="592">
@@ -10457,10 +10457,10 @@
         <v>Passed</v>
       </c>
       <c r="D592">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="E592" t="str">
-        <v>2026-07-30T14:09:08.534Z</v>
+        <v>2026-07-30T21:49:00.487Z</v>
       </c>
     </row>
     <row r="593">
@@ -10474,10 +10474,10 @@
         <v>Passed</v>
       </c>
       <c r="D593">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="E593" t="str">
-        <v>2026-07-30T14:09:09.534Z</v>
+        <v>2026-07-30T21:49:01.487Z</v>
       </c>
     </row>
     <row r="594">
@@ -10491,10 +10491,10 @@
         <v>Passed</v>
       </c>
       <c r="D594">
-        <v>0.28</v>
+        <v>1.15</v>
       </c>
       <c r="E594" t="str">
-        <v>2026-07-30T14:09:10.534Z</v>
+        <v>2026-07-30T21:49:02.487Z</v>
       </c>
     </row>
     <row r="595">
@@ -10508,10 +10508,10 @@
         <v>Passed</v>
       </c>
       <c r="D595">
-        <v>1.92</v>
+        <v>0.92</v>
       </c>
       <c r="E595" t="str">
-        <v>2026-07-30T14:09:11.534Z</v>
+        <v>2026-07-30T21:49:03.487Z</v>
       </c>
     </row>
     <row r="596">
@@ -10525,10 +10525,10 @@
         <v>Passed</v>
       </c>
       <c r="D596">
-        <v>0.98</v>
+        <v>0.06</v>
       </c>
       <c r="E596" t="str">
-        <v>2026-07-30T14:09:12.534Z</v>
+        <v>2026-07-30T21:49:04.487Z</v>
       </c>
     </row>
     <row r="597">
@@ -10542,10 +10542,10 @@
         <v>Passed</v>
       </c>
       <c r="D597">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
       <c r="E597" t="str">
-        <v>2026-07-30T14:09:13.534Z</v>
+        <v>2026-07-30T21:49:05.487Z</v>
       </c>
     </row>
     <row r="598">
@@ -10559,10 +10559,10 @@
         <v>Passed</v>
       </c>
       <c r="D598">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="E598" t="str">
-        <v>2026-07-30T14:09:14.534Z</v>
+        <v>2026-07-30T21:49:06.487Z</v>
       </c>
     </row>
     <row r="599">
@@ -10576,10 +10576,10 @@
         <v>Passed</v>
       </c>
       <c r="D599">
-        <v>0.04</v>
+        <v>1.7</v>
       </c>
       <c r="E599" t="str">
-        <v>2026-07-30T14:09:15.534Z</v>
+        <v>2026-07-30T21:49:07.487Z</v>
       </c>
     </row>
     <row r="600">
@@ -10593,10 +10593,10 @@
         <v>Passed</v>
       </c>
       <c r="D600">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="E600" t="str">
-        <v>2026-07-30T14:09:16.534Z</v>
+        <v>2026-07-30T21:49:08.487Z</v>
       </c>
     </row>
     <row r="601">
@@ -10610,389 +10610,15 @@
         <v>Passed</v>
       </c>
       <c r="D601">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="E601" t="str">
-        <v>2026-07-30T14:09:17.534Z</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="str">
-        <v>APILoad-TC-0601</v>
-      </c>
-      <c r="B602" t="str">
-        <v>Verify APILoad functionality module 601</v>
-      </c>
-      <c r="C602" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D602">
-        <v>0.41</v>
-      </c>
-      <c r="E602" t="str">
-        <v>2026-07-30T14:09:18.534Z</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="str">
-        <v>APILoad-TC-0602</v>
-      </c>
-      <c r="B603" t="str">
-        <v>Verify APILoad functionality module 602</v>
-      </c>
-      <c r="C603" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D603">
-        <v>0.97</v>
-      </c>
-      <c r="E603" t="str">
-        <v>2026-07-30T14:09:19.534Z</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="str">
-        <v>APILoad-TC-0603</v>
-      </c>
-      <c r="B604" t="str">
-        <v>Verify APILoad functionality module 603</v>
-      </c>
-      <c r="C604" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D604">
-        <v>0.65</v>
-      </c>
-      <c r="E604" t="str">
-        <v>2026-07-30T14:09:20.534Z</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="str">
-        <v>APILoad-TC-0604</v>
-      </c>
-      <c r="B605" t="str">
-        <v>Verify APILoad functionality module 604</v>
-      </c>
-      <c r="C605" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D605">
-        <v>0.92</v>
-      </c>
-      <c r="E605" t="str">
-        <v>2026-07-30T14:09:21.534Z</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="str">
-        <v>APILoad-TC-0605</v>
-      </c>
-      <c r="B606" t="str">
-        <v>Verify APILoad functionality module 605</v>
-      </c>
-      <c r="C606" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D606">
-        <v>0.52</v>
-      </c>
-      <c r="E606" t="str">
-        <v>2026-07-30T14:09:22.534Z</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="str">
-        <v>APILoad-TC-0606</v>
-      </c>
-      <c r="B607" t="str">
-        <v>Verify APILoad functionality module 606</v>
-      </c>
-      <c r="C607" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D607">
-        <v>1.7</v>
-      </c>
-      <c r="E607" t="str">
-        <v>2026-07-30T14:09:23.534Z</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="str">
-        <v>APILoad-TC-0607</v>
-      </c>
-      <c r="B608" t="str">
-        <v>Verify APILoad functionality module 607</v>
-      </c>
-      <c r="C608" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D608">
-        <v>0.24</v>
-      </c>
-      <c r="E608" t="str">
-        <v>2026-07-30T14:09:24.534Z</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="str">
-        <v>APILoad-TC-0608</v>
-      </c>
-      <c r="B609" t="str">
-        <v>Verify APILoad functionality module 608</v>
-      </c>
-      <c r="C609" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D609">
-        <v>0.85</v>
-      </c>
-      <c r="E609" t="str">
-        <v>2026-07-30T14:09:25.534Z</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="str">
-        <v>APILoad-TC-0609</v>
-      </c>
-      <c r="B610" t="str">
-        <v>Verify APILoad functionality module 609</v>
-      </c>
-      <c r="C610" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D610">
-        <v>1.2</v>
-      </c>
-      <c r="E610" t="str">
-        <v>2026-07-30T14:09:26.534Z</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="str">
-        <v>APILoad-TC-0610</v>
-      </c>
-      <c r="B611" t="str">
-        <v>Verify APILoad functionality module 610</v>
-      </c>
-      <c r="C611" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D611">
-        <v>0.14</v>
-      </c>
-      <c r="E611" t="str">
-        <v>2026-07-30T14:09:27.534Z</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="str">
-        <v>APILoad-TC-0611</v>
-      </c>
-      <c r="B612" t="str">
-        <v>Verify APILoad functionality module 611</v>
-      </c>
-      <c r="C612" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D612">
-        <v>0.24</v>
-      </c>
-      <c r="E612" t="str">
-        <v>2026-07-30T14:09:28.534Z</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="str">
-        <v>APILoad-TC-0612</v>
-      </c>
-      <c r="B613" t="str">
-        <v>Verify APILoad functionality module 612</v>
-      </c>
-      <c r="C613" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D613">
-        <v>1.96</v>
-      </c>
-      <c r="E613" t="str">
-        <v>2026-07-30T14:09:29.534Z</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="str">
-        <v>APILoad-TC-0613</v>
-      </c>
-      <c r="B614" t="str">
-        <v>Verify APILoad functionality module 613</v>
-      </c>
-      <c r="C614" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D614">
-        <v>1.44</v>
-      </c>
-      <c r="E614" t="str">
-        <v>2026-07-30T14:09:30.534Z</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="str">
-        <v>APILoad-TC-0614</v>
-      </c>
-      <c r="B615" t="str">
-        <v>Verify APILoad functionality module 614</v>
-      </c>
-      <c r="C615" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D615">
-        <v>0.56</v>
-      </c>
-      <c r="E615" t="str">
-        <v>2026-07-30T14:09:31.534Z</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="str">
-        <v>APILoad-TC-0615</v>
-      </c>
-      <c r="B616" t="str">
-        <v>Verify APILoad functionality module 615</v>
-      </c>
-      <c r="C616" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D616">
-        <v>0.24</v>
-      </c>
-      <c r="E616" t="str">
-        <v>2026-07-30T14:09:32.534Z</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="str">
-        <v>APILoad-TC-0616</v>
-      </c>
-      <c r="B617" t="str">
-        <v>Verify APILoad functionality module 616</v>
-      </c>
-      <c r="C617" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D617">
-        <v>1.49</v>
-      </c>
-      <c r="E617" t="str">
-        <v>2026-07-30T14:09:33.534Z</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="str">
-        <v>APILoad-TC-0617</v>
-      </c>
-      <c r="B618" t="str">
-        <v>Verify APILoad functionality module 617</v>
-      </c>
-      <c r="C618" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D618">
-        <v>1.68</v>
-      </c>
-      <c r="E618" t="str">
-        <v>2026-07-30T14:09:34.534Z</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="str">
-        <v>APILoad-TC-0618</v>
-      </c>
-      <c r="B619" t="str">
-        <v>Verify APILoad functionality module 618</v>
-      </c>
-      <c r="C619" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D619">
-        <v>0.59</v>
-      </c>
-      <c r="E619" t="str">
-        <v>2026-07-30T14:09:35.534Z</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="str">
-        <v>APILoad-TC-0619</v>
-      </c>
-      <c r="B620" t="str">
-        <v>Verify APILoad functionality module 619</v>
-      </c>
-      <c r="C620" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D620">
-        <v>0.87</v>
-      </c>
-      <c r="E620" t="str">
-        <v>2026-07-30T14:09:36.534Z</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="str">
-        <v>APILoad-TC-0620</v>
-      </c>
-      <c r="B621" t="str">
-        <v>Verify APILoad functionality module 620</v>
-      </c>
-      <c r="C621" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D621">
-        <v>1.58</v>
-      </c>
-      <c r="E621" t="str">
-        <v>2026-07-30T14:09:37.534Z</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="str">
-        <v>APILoad-TC-0621</v>
-      </c>
-      <c r="B622" t="str">
-        <v>Verify APILoad functionality module 621</v>
-      </c>
-      <c r="C622" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D622">
-        <v>1.63</v>
-      </c>
-      <c r="E622" t="str">
-        <v>2026-07-30T14:09:38.534Z</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="str">
-        <v>APILoad-TC-0622</v>
-      </c>
-      <c r="B623" t="str">
-        <v>Verify APILoad functionality module 622</v>
-      </c>
-      <c r="C623" t="str">
-        <v>Passed</v>
-      </c>
-      <c r="D623">
-        <v>1.57</v>
-      </c>
-      <c r="E623" t="str">
-        <v>2026-07-30T14:09:39.534Z</v>
+        <v>2026-07-30T21:49:09.487Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E623"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E601"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/latest/load_testing/Load_Test_Report_Cognify_Latest.xlsx
+++ b/reports/latest/load_testing/Load_Test_Report_Cognify_Latest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Test Results" sheetId="1" r:id="rId1"/>
+    <sheet name="API_Load_Test_Report" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E601"/>
+  <dimension ref="A1:E647"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>1.33</v>
+        <v>0.18</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T21:39:10.487Z</v>
+        <v>2026-07-30T21:44:46.051Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T21:39:11.487Z</v>
+        <v>2026-07-30T21:44:47.051Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>1.97</v>
+        <v>0.07</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T21:39:12.487Z</v>
+        <v>2026-07-30T21:44:48.051Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>0.36</v>
+        <v>1.83</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T21:39:13.487Z</v>
+        <v>2026-07-30T21:44:49.051Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T21:39:14.487Z</v>
+        <v>2026-07-30T21:44:50.051Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>1.74</v>
+        <v>0.77</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T21:39:15.487Z</v>
+        <v>2026-07-30T21:44:51.051Z</v>
       </c>
     </row>
     <row r="8">
@@ -526,13 +526,13 @@
         <v>Verify APILoad functionality module 7</v>
       </c>
       <c r="C8" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D8">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T21:39:16.487Z</v>
+        <v>2026-07-30T21:44:52.051Z</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>Passed</v>
       </c>
       <c r="D9">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T21:39:17.487Z</v>
+        <v>2026-07-30T21:44:53.051Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>0.01</v>
+        <v>0.79</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T21:39:18.487Z</v>
+        <v>2026-07-30T21:44:54.051Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T21:39:19.487Z</v>
+        <v>2026-07-30T21:44:55.051Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T21:39:20.487Z</v>
+        <v>2026-07-30T21:44:56.051Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T21:39:21.487Z</v>
+        <v>2026-07-30T21:44:57.051Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T21:39:22.487Z</v>
+        <v>2026-07-30T21:44:58.051Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T21:39:23.487Z</v>
+        <v>2026-07-30T21:44:59.051Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T21:39:24.487Z</v>
+        <v>2026-07-30T21:45:00.051Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T21:39:25.487Z</v>
+        <v>2026-07-30T21:45:01.051Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>1.82</v>
+        <v>0.89</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T21:39:26.487Z</v>
+        <v>2026-07-30T21:45:02.051Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>0.84</v>
+        <v>1.91</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T21:39:27.487Z</v>
+        <v>2026-07-30T21:45:03.051Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>0.35</v>
+        <v>0.96</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T21:39:28.487Z</v>
+        <v>2026-07-30T21:45:04.051Z</v>
       </c>
     </row>
     <row r="21">
@@ -750,10 +750,10 @@
         <v>Passed</v>
       </c>
       <c r="D21">
-        <v>1.12</v>
+        <v>0.07</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T21:39:29.487Z</v>
+        <v>2026-07-30T21:45:05.051Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>0.4</v>
+        <v>1.57</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T21:39:30.487Z</v>
+        <v>2026-07-30T21:45:06.051Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T21:39:31.487Z</v>
+        <v>2026-07-30T21:45:07.051Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>0.65</v>
+        <v>0.19</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T21:39:32.487Z</v>
+        <v>2026-07-30T21:45:08.051Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T21:39:33.487Z</v>
+        <v>2026-07-30T21:45:09.051Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>0.11</v>
+        <v>1.86</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T21:39:34.487Z</v>
+        <v>2026-07-30T21:45:10.051Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>0.94</v>
+        <v>1.31</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T21:39:35.487Z</v>
+        <v>2026-07-30T21:45:11.051Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T21:39:36.487Z</v>
+        <v>2026-07-30T21:45:12.051Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T21:39:37.487Z</v>
+        <v>2026-07-30T21:45:13.051Z</v>
       </c>
     </row>
     <row r="30">
@@ -900,13 +900,13 @@
         <v>Verify APILoad functionality module 29</v>
       </c>
       <c r="C30" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D30">
-        <v>1.99</v>
+        <v>1.51</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T21:39:38.487Z</v>
+        <v>2026-07-30T21:45:14.051Z</v>
       </c>
     </row>
     <row r="31">
@@ -920,10 +920,10 @@
         <v>Passed</v>
       </c>
       <c r="D31">
-        <v>1.85</v>
+        <v>0.32</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T21:39:39.487Z</v>
+        <v>2026-07-30T21:45:15.051Z</v>
       </c>
     </row>
     <row r="32">
@@ -937,10 +937,10 @@
         <v>Passed</v>
       </c>
       <c r="D32">
-        <v>1.8</v>
+        <v>0.13</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T21:39:40.487Z</v>
+        <v>2026-07-30T21:45:16.051Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T21:39:41.487Z</v>
+        <v>2026-07-30T21:45:17.051Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T21:39:42.487Z</v>
+        <v>2026-07-30T21:45:18.051Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T21:39:43.487Z</v>
+        <v>2026-07-30T21:45:19.051Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T21:39:44.487Z</v>
+        <v>2026-07-30T21:45:20.051Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>0.26</v>
+        <v>0.03</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T21:39:45.487Z</v>
+        <v>2026-07-30T21:45:21.051Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>0.26</v>
+        <v>0.53</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T21:39:46.487Z</v>
+        <v>2026-07-30T21:45:22.051Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>1.25</v>
+        <v>0.13</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T21:39:47.487Z</v>
+        <v>2026-07-30T21:45:23.051Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T21:39:48.487Z</v>
+        <v>2026-07-30T21:45:24.051Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T21:39:49.487Z</v>
+        <v>2026-07-30T21:45:25.051Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>1.1</v>
+        <v>0.83</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T21:39:50.487Z</v>
+        <v>2026-07-30T21:45:26.051Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>0.54</v>
+        <v>1.26</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T21:39:51.487Z</v>
+        <v>2026-07-30T21:45:27.051Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T21:39:52.487Z</v>
+        <v>2026-07-30T21:45:28.051Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>0.69</v>
+        <v>0.89</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T21:39:53.487Z</v>
+        <v>2026-07-30T21:45:29.051Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>0.46</v>
+        <v>1.3</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T21:39:54.487Z</v>
+        <v>2026-07-30T21:45:30.051Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T21:39:55.487Z</v>
+        <v>2026-07-30T21:45:31.051Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>0.46</v>
+        <v>1.99</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T21:39:56.487Z</v>
+        <v>2026-07-30T21:45:32.051Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T21:39:57.487Z</v>
+        <v>2026-07-30T21:45:33.051Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T21:39:58.487Z</v>
+        <v>2026-07-30T21:45:34.051Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>0.61</v>
+        <v>0.08</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T21:39:59.487Z</v>
+        <v>2026-07-30T21:45:35.051Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>0.6</v>
+        <v>1.77</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T21:40:00.487Z</v>
+        <v>2026-07-30T21:45:36.051Z</v>
       </c>
     </row>
     <row r="53">
@@ -1297,7 +1297,7 @@
         <v>0.96</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T21:40:01.487Z</v>
+        <v>2026-07-30T21:45:37.051Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>1.82</v>
+        <v>0.63</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T21:40:02.487Z</v>
+        <v>2026-07-30T21:45:38.051Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>1.14</v>
+        <v>1.94</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T21:40:03.487Z</v>
+        <v>2026-07-30T21:45:39.051Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>0.15</v>
+        <v>0.57</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T21:40:04.487Z</v>
+        <v>2026-07-30T21:45:40.051Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>0.95</v>
+        <v>1.95</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T21:40:05.487Z</v>
+        <v>2026-07-30T21:45:41.051Z</v>
       </c>
     </row>
     <row r="58">
@@ -1379,10 +1379,10 @@
         <v>Passed</v>
       </c>
       <c r="D58">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T21:40:06.487Z</v>
+        <v>2026-07-30T21:45:42.051Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>1.9</v>
+        <v>0.19</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T21:40:07.487Z</v>
+        <v>2026-07-30T21:45:43.051Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T21:40:08.487Z</v>
+        <v>2026-07-30T21:45:44.051Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>0.07</v>
+        <v>0.14</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T21:40:09.487Z</v>
+        <v>2026-07-30T21:45:45.051Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>0.02</v>
+        <v>0.31</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T21:40:10.487Z</v>
+        <v>2026-07-30T21:45:46.051Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>0.91</v>
+        <v>1.44</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T21:40:11.487Z</v>
+        <v>2026-07-30T21:45:47.051Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T21:40:12.487Z</v>
+        <v>2026-07-30T21:45:48.051Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>0.23</v>
+        <v>1.41</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T21:40:13.487Z</v>
+        <v>2026-07-30T21:45:49.051Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T21:40:14.487Z</v>
+        <v>2026-07-30T21:45:50.051Z</v>
       </c>
     </row>
     <row r="67">
@@ -1532,10 +1532,10 @@
         <v>Passed</v>
       </c>
       <c r="D67">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T21:40:15.487Z</v>
+        <v>2026-07-30T21:45:51.051Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>1.06</v>
+        <v>1.58</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T21:40:16.487Z</v>
+        <v>2026-07-30T21:45:52.051Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>1.53</v>
+        <v>0.5</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T21:40:17.487Z</v>
+        <v>2026-07-30T21:45:53.051Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T21:40:18.487Z</v>
+        <v>2026-07-30T21:45:54.051Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T21:40:19.487Z</v>
+        <v>2026-07-30T21:45:55.051Z</v>
       </c>
     </row>
     <row r="72">
@@ -1620,7 +1620,7 @@
         <v>1.13</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T21:40:20.487Z</v>
+        <v>2026-07-30T21:45:56.051Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T21:40:21.487Z</v>
+        <v>2026-07-30T21:45:57.051Z</v>
       </c>
     </row>
     <row r="74">
@@ -1651,10 +1651,10 @@
         <v>Passed</v>
       </c>
       <c r="D74">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T21:40:22.487Z</v>
+        <v>2026-07-30T21:45:58.051Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T21:40:23.487Z</v>
+        <v>2026-07-30T21:45:59.051Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>1.42</v>
+        <v>0.19</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T21:40:24.487Z</v>
+        <v>2026-07-30T21:46:00.051Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>1.25</v>
+        <v>0.87</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T21:40:25.487Z</v>
+        <v>2026-07-30T21:46:01.051Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>0.59</v>
+        <v>0.11</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T21:40:26.487Z</v>
+        <v>2026-07-30T21:46:02.051Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>0.86</v>
+        <v>1.63</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T21:40:27.487Z</v>
+        <v>2026-07-30T21:46:03.051Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>1.47</v>
+        <v>0.38</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T21:40:28.487Z</v>
+        <v>2026-07-30T21:46:04.051Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.67</v>
+        <v>0.36</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T21:40:29.487Z</v>
+        <v>2026-07-30T21:46:05.051Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>0.77</v>
+        <v>0.13</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T21:40:30.487Z</v>
+        <v>2026-07-30T21:46:06.051Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T21:40:31.487Z</v>
+        <v>2026-07-30T21:46:07.051Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T21:40:32.487Z</v>
+        <v>2026-07-30T21:46:08.051Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>1.93</v>
+        <v>0.88</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T21:40:33.487Z</v>
+        <v>2026-07-30T21:46:09.051Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T21:40:34.487Z</v>
+        <v>2026-07-30T21:46:10.051Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>0.03</v>
+        <v>0.43</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T21:40:35.487Z</v>
+        <v>2026-07-30T21:46:11.051Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T21:40:36.487Z</v>
+        <v>2026-07-30T21:46:12.051Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T21:40:37.487Z</v>
+        <v>2026-07-30T21:46:13.051Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>0.57</v>
+        <v>1.39</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T21:40:38.487Z</v>
+        <v>2026-07-30T21:46:14.051Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>1.68</v>
+        <v>0.6</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T21:40:39.487Z</v>
+        <v>2026-07-30T21:46:15.051Z</v>
       </c>
     </row>
     <row r="92">
@@ -1957,10 +1957,10 @@
         <v>Passed</v>
       </c>
       <c r="D92">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T21:40:40.487Z</v>
+        <v>2026-07-30T21:46:16.051Z</v>
       </c>
     </row>
     <row r="93">
@@ -1974,10 +1974,10 @@
         <v>Passed</v>
       </c>
       <c r="D93">
-        <v>1.53</v>
+        <v>0.34</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T21:40:41.487Z</v>
+        <v>2026-07-30T21:46:17.051Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>0.89</v>
+        <v>1.65</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T21:40:42.487Z</v>
+        <v>2026-07-30T21:46:18.051Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>1.17</v>
+        <v>0.46</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T21:40:43.487Z</v>
+        <v>2026-07-30T21:46:19.051Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T21:40:44.487Z</v>
+        <v>2026-07-30T21:46:20.051Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T21:40:45.487Z</v>
+        <v>2026-07-30T21:46:21.051Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>1.17</v>
+        <v>0.88</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T21:40:46.487Z</v>
+        <v>2026-07-30T21:46:22.051Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>0.2</v>
+        <v>1.88</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T21:40:47.487Z</v>
+        <v>2026-07-30T21:46:23.051Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>1.35</v>
+        <v>0.31</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T21:40:48.487Z</v>
+        <v>2026-07-30T21:46:24.051Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>0.97</v>
+        <v>0.51</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T21:40:49.487Z</v>
+        <v>2026-07-30T21:46:25.051Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>1.28</v>
+        <v>0.89</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T21:40:50.487Z</v>
+        <v>2026-07-30T21:46:26.051Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>1.28</v>
+        <v>0.73</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T21:40:51.487Z</v>
+        <v>2026-07-30T21:46:27.051Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T21:40:52.487Z</v>
+        <v>2026-07-30T21:46:28.051Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T21:40:53.487Z</v>
+        <v>2026-07-30T21:46:29.051Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>1.48</v>
+        <v>0.27</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T21:40:54.487Z</v>
+        <v>2026-07-30T21:46:30.051Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T21:40:55.487Z</v>
+        <v>2026-07-30T21:46:31.051Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T21:40:56.487Z</v>
+        <v>2026-07-30T21:46:32.051Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>0.42</v>
+        <v>1.73</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T21:40:57.487Z</v>
+        <v>2026-07-30T21:46:33.051Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>1.87</v>
+        <v>0.07</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T21:40:58.487Z</v>
+        <v>2026-07-30T21:46:34.051Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>1.63</v>
+        <v>0.43</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T21:40:59.487Z</v>
+        <v>2026-07-30T21:46:35.051Z</v>
       </c>
     </row>
     <row r="112">
@@ -2297,10 +2297,10 @@
         <v>Passed</v>
       </c>
       <c r="D112">
-        <v>0.43</v>
+        <v>1.79</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T21:41:00.487Z</v>
+        <v>2026-07-30T21:46:36.051Z</v>
       </c>
     </row>
     <row r="113">
@@ -2314,10 +2314,10 @@
         <v>Passed</v>
       </c>
       <c r="D113">
-        <v>1.29</v>
+        <v>0.28</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T21:41:01.487Z</v>
+        <v>2026-07-30T21:46:37.051Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>1.03</v>
+        <v>0.03</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T21:41:02.487Z</v>
+        <v>2026-07-30T21:46:38.051Z</v>
       </c>
     </row>
     <row r="115">
@@ -2348,10 +2348,10 @@
         <v>Passed</v>
       </c>
       <c r="D115">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T21:41:03.487Z</v>
+        <v>2026-07-30T21:46:39.051Z</v>
       </c>
     </row>
     <row r="116">
@@ -2365,10 +2365,10 @@
         <v>Passed</v>
       </c>
       <c r="D116">
-        <v>0.81</v>
+        <v>0.03</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T21:41:04.487Z</v>
+        <v>2026-07-30T21:46:40.051Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T21:41:05.487Z</v>
+        <v>2026-07-30T21:46:41.051Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T21:41:06.487Z</v>
+        <v>2026-07-30T21:46:42.051Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>1.69</v>
+        <v>0.86</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T21:41:07.487Z</v>
+        <v>2026-07-30T21:46:43.051Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>0.16</v>
+        <v>0.94</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T21:41:08.487Z</v>
+        <v>2026-07-30T21:46:44.051Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T21:41:09.487Z</v>
+        <v>2026-07-30T21:46:45.051Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>1.34</v>
+        <v>0.95</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T21:41:10.487Z</v>
+        <v>2026-07-30T21:46:46.051Z</v>
       </c>
     </row>
     <row r="123">
@@ -2484,10 +2484,10 @@
         <v>Passed</v>
       </c>
       <c r="D123">
-        <v>0.22</v>
+        <v>1.3</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T21:41:11.487Z</v>
+        <v>2026-07-30T21:46:47.051Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T21:41:12.487Z</v>
+        <v>2026-07-30T21:46:48.051Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T21:41:13.487Z</v>
+        <v>2026-07-30T21:46:49.051Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T21:41:14.487Z</v>
+        <v>2026-07-30T21:46:50.051Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>1.76</v>
+        <v>0.06</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T21:41:15.487Z</v>
+        <v>2026-07-30T21:46:51.051Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T21:41:16.487Z</v>
+        <v>2026-07-30T21:46:52.051Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T21:41:17.487Z</v>
+        <v>2026-07-30T21:46:53.051Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T21:41:18.487Z</v>
+        <v>2026-07-30T21:46:54.051Z</v>
       </c>
     </row>
     <row r="131">
@@ -2620,10 +2620,10 @@
         <v>Passed</v>
       </c>
       <c r="D131">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T21:41:19.487Z</v>
+        <v>2026-07-30T21:46:55.051Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>0.06</v>
+        <v>1.74</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T21:41:20.487Z</v>
+        <v>2026-07-30T21:46:56.051Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>1.17</v>
+        <v>0.31</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T21:41:21.487Z</v>
+        <v>2026-07-30T21:46:57.051Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T21:41:22.487Z</v>
+        <v>2026-07-30T21:46:58.051Z</v>
       </c>
     </row>
     <row r="135">
@@ -2685,13 +2685,13 @@
         <v>Verify APILoad functionality module 134</v>
       </c>
       <c r="C135" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D135">
-        <v>0.21</v>
+        <v>1.95</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T21:41:23.487Z</v>
+        <v>2026-07-30T21:46:59.051Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T21:41:24.487Z</v>
+        <v>2026-07-30T21:47:00.051Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T21:41:25.487Z</v>
+        <v>2026-07-30T21:47:01.051Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T21:41:26.487Z</v>
+        <v>2026-07-30T21:47:02.051Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T21:41:27.487Z</v>
+        <v>2026-07-30T21:47:03.051Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>0.18</v>
+        <v>0.93</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T21:41:28.487Z</v>
+        <v>2026-07-30T21:47:04.051Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>0.96</v>
+        <v>0.48</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T21:41:29.487Z</v>
+        <v>2026-07-30T21:47:05.051Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T21:41:30.487Z</v>
+        <v>2026-07-30T21:47:06.051Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T21:41:31.487Z</v>
+        <v>2026-07-30T21:47:07.051Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>0.93</v>
+        <v>0.03</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T21:41:32.487Z</v>
+        <v>2026-07-30T21:47:08.051Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T21:41:33.487Z</v>
+        <v>2026-07-30T21:47:09.051Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T21:41:34.487Z</v>
+        <v>2026-07-30T21:47:10.051Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>1.5</v>
+        <v>0.17</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T21:41:35.487Z</v>
+        <v>2026-07-30T21:47:11.051Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>0.57</v>
+        <v>1.87</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T21:41:36.487Z</v>
+        <v>2026-07-30T21:47:12.051Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>1.15</v>
+        <v>0.05</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T21:41:37.487Z</v>
+        <v>2026-07-30T21:47:13.051Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>1.46</v>
+        <v>0.35</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T21:41:38.487Z</v>
+        <v>2026-07-30T21:47:14.051Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>0.15</v>
+        <v>0.66</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T21:41:39.487Z</v>
+        <v>2026-07-30T21:47:15.051Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T21:41:40.487Z</v>
+        <v>2026-07-30T21:47:16.051Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>1.99</v>
+        <v>0.12</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T21:41:41.487Z</v>
+        <v>2026-07-30T21:47:17.051Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T21:41:42.487Z</v>
+        <v>2026-07-30T21:47:18.051Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T21:41:43.487Z</v>
+        <v>2026-07-30T21:47:19.051Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>0.23</v>
+        <v>1.92</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T21:41:44.487Z</v>
+        <v>2026-07-30T21:47:20.051Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>1.76</v>
+        <v>0.57</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T21:41:45.487Z</v>
+        <v>2026-07-30T21:47:21.051Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T21:41:46.487Z</v>
+        <v>2026-07-30T21:47:22.051Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>1.87</v>
+        <v>0.94</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T21:41:47.487Z</v>
+        <v>2026-07-30T21:47:23.051Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>1.8</v>
+        <v>0.35</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T21:41:48.487Z</v>
+        <v>2026-07-30T21:47:24.051Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>0.75</v>
+        <v>1.86</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T21:41:49.487Z</v>
+        <v>2026-07-30T21:47:25.051Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>1.51</v>
+        <v>0.89</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T21:41:50.487Z</v>
+        <v>2026-07-30T21:47:26.051Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T21:41:51.487Z</v>
+        <v>2026-07-30T21:47:27.051Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>1.29</v>
+        <v>0.54</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T21:41:52.487Z</v>
+        <v>2026-07-30T21:47:28.051Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>0.58</v>
+        <v>1.64</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T21:41:53.487Z</v>
+        <v>2026-07-30T21:47:29.051Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T21:41:54.487Z</v>
+        <v>2026-07-30T21:47:30.051Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>0.87</v>
+        <v>1.87</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T21:41:55.487Z</v>
+        <v>2026-07-30T21:47:31.051Z</v>
       </c>
     </row>
     <row r="168">
@@ -3249,10 +3249,10 @@
         <v>Passed</v>
       </c>
       <c r="D168">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T21:41:56.487Z</v>
+        <v>2026-07-30T21:47:32.051Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>1.17</v>
+        <v>0.02</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T21:41:57.487Z</v>
+        <v>2026-07-30T21:47:33.051Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T21:41:58.487Z</v>
+        <v>2026-07-30T21:47:34.051Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>1.61</v>
+        <v>0.3</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T21:41:59.487Z</v>
+        <v>2026-07-30T21:47:35.051Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>1.25</v>
+        <v>0.23</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T21:42:00.487Z</v>
+        <v>2026-07-30T21:47:36.051Z</v>
       </c>
     </row>
     <row r="173">
@@ -3334,10 +3334,10 @@
         <v>Passed</v>
       </c>
       <c r="D173">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T21:42:01.487Z</v>
+        <v>2026-07-30T21:47:37.051Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T21:42:02.487Z</v>
+        <v>2026-07-30T21:47:38.051Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>1.59</v>
+        <v>1.13</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T21:42:03.487Z</v>
+        <v>2026-07-30T21:47:39.051Z</v>
       </c>
     </row>
     <row r="176">
@@ -3382,13 +3382,13 @@
         <v>Verify APILoad functionality module 175</v>
       </c>
       <c r="C176" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D176">
-        <v>0.62</v>
+        <v>1.4</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T21:42:04.487Z</v>
+        <v>2026-07-30T21:47:40.051Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>1.98</v>
+        <v>1.06</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T21:42:05.487Z</v>
+        <v>2026-07-30T21:47:41.051Z</v>
       </c>
     </row>
     <row r="178">
@@ -3419,10 +3419,10 @@
         <v>Passed</v>
       </c>
       <c r="D178">
-        <v>1.56</v>
+        <v>1.13</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T21:42:06.487Z</v>
+        <v>2026-07-30T21:47:42.051Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>0.09</v>
+        <v>1.72</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T21:42:07.487Z</v>
+        <v>2026-07-30T21:47:43.051Z</v>
       </c>
     </row>
     <row r="180">
@@ -3453,10 +3453,10 @@
         <v>Passed</v>
       </c>
       <c r="D180">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T21:42:08.487Z</v>
+        <v>2026-07-30T21:47:44.051Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>1.88</v>
+        <v>0.89</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T21:42:09.487Z</v>
+        <v>2026-07-30T21:47:45.051Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T21:42:10.487Z</v>
+        <v>2026-07-30T21:47:46.051Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>0.63</v>
+        <v>1.56</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T21:42:11.487Z</v>
+        <v>2026-07-30T21:47:47.051Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T21:42:12.487Z</v>
+        <v>2026-07-30T21:47:48.051Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>1.44</v>
+        <v>0.34</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T21:42:13.487Z</v>
+        <v>2026-07-30T21:47:49.051Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T21:42:14.487Z</v>
+        <v>2026-07-30T21:47:50.051Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T21:42:15.487Z</v>
+        <v>2026-07-30T21:47:51.051Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>0.9</v>
+        <v>1.89</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T21:42:16.487Z</v>
+        <v>2026-07-30T21:47:52.051Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>0.97</v>
+        <v>1.81</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T21:42:17.487Z</v>
+        <v>2026-07-30T21:47:53.051Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>1.28</v>
+        <v>0.94</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T21:42:18.487Z</v>
+        <v>2026-07-30T21:47:54.051Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T21:42:19.487Z</v>
+        <v>2026-07-30T21:47:55.051Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T21:42:20.487Z</v>
+        <v>2026-07-30T21:47:56.051Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>0.94</v>
+        <v>1.18</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T21:42:21.487Z</v>
+        <v>2026-07-30T21:47:57.051Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>1.2</v>
+        <v>0.82</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T21:42:22.487Z</v>
+        <v>2026-07-30T21:47:58.051Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>0.59</v>
+        <v>1.65</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T21:42:23.487Z</v>
+        <v>2026-07-30T21:47:59.051Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>0.44</v>
+        <v>1.43</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T21:42:24.487Z</v>
+        <v>2026-07-30T21:48:00.051Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>0.27</v>
+        <v>1.37</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T21:42:25.487Z</v>
+        <v>2026-07-30T21:48:01.051Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T21:42:26.487Z</v>
+        <v>2026-07-30T21:48:02.051Z</v>
       </c>
     </row>
     <row r="199">
@@ -3776,10 +3776,10 @@
         <v>Passed</v>
       </c>
       <c r="D199">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T21:42:27.487Z</v>
+        <v>2026-07-30T21:48:03.051Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T21:42:28.487Z</v>
+        <v>2026-07-30T21:48:04.051Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>0.56</v>
+        <v>0.09</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T21:42:29.487Z</v>
+        <v>2026-07-30T21:48:05.051Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T21:42:30.487Z</v>
+        <v>2026-07-30T21:48:06.051Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T21:42:31.487Z</v>
+        <v>2026-07-30T21:48:07.051Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>0.77</v>
+        <v>0.23</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T21:42:32.487Z</v>
+        <v>2026-07-30T21:48:08.051Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T21:42:33.487Z</v>
+        <v>2026-07-30T21:48:09.051Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>0.72</v>
+        <v>1.78</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T21:42:34.487Z</v>
+        <v>2026-07-30T21:48:10.051Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>1.36</v>
+        <v>0.7</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T21:42:35.487Z</v>
+        <v>2026-07-30T21:48:11.051Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>0.59</v>
+        <v>0.13</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T21:42:36.487Z</v>
+        <v>2026-07-30T21:48:12.051Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>1.86</v>
+        <v>0.84</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T21:42:37.487Z</v>
+        <v>2026-07-30T21:48:13.051Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>1.9</v>
+        <v>0.58</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T21:42:38.487Z</v>
+        <v>2026-07-30T21:48:14.051Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T21:42:39.487Z</v>
+        <v>2026-07-30T21:48:15.051Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>1.2</v>
+        <v>0.97</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T21:42:40.487Z</v>
+        <v>2026-07-30T21:48:16.051Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T21:42:41.487Z</v>
+        <v>2026-07-30T21:48:17.051Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T21:42:42.487Z</v>
+        <v>2026-07-30T21:48:18.051Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T21:42:43.487Z</v>
+        <v>2026-07-30T21:48:19.051Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>0.81</v>
+        <v>0.14</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T21:42:44.487Z</v>
+        <v>2026-07-30T21:48:20.051Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T21:42:45.487Z</v>
+        <v>2026-07-30T21:48:21.051Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>0.27</v>
+        <v>0.71</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T21:42:46.487Z</v>
+        <v>2026-07-30T21:48:22.051Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>1.62</v>
+        <v>0.01</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T21:42:47.487Z</v>
+        <v>2026-07-30T21:48:23.051Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>0.13</v>
+        <v>1.19</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T21:42:48.487Z</v>
+        <v>2026-07-30T21:48:24.051Z</v>
       </c>
     </row>
     <row r="221">
@@ -4147,13 +4147,13 @@
         <v>Verify APILoad functionality module 220</v>
       </c>
       <c r="C221" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D221">
-        <v>0.18</v>
+        <v>0.87</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T21:42:49.487Z</v>
+        <v>2026-07-30T21:48:25.051Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T21:42:50.487Z</v>
+        <v>2026-07-30T21:48:26.051Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T21:42:51.487Z</v>
+        <v>2026-07-30T21:48:27.051Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T21:42:52.487Z</v>
+        <v>2026-07-30T21:48:28.051Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>1.98</v>
+        <v>0.36</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T21:42:53.487Z</v>
+        <v>2026-07-30T21:48:29.051Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>0.25</v>
+        <v>1.22</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T21:42:54.487Z</v>
+        <v>2026-07-30T21:48:30.051Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T21:42:55.487Z</v>
+        <v>2026-07-30T21:48:31.051Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>0.52</v>
+        <v>0.16</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T21:42:56.487Z</v>
+        <v>2026-07-30T21:48:32.051Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T21:42:57.487Z</v>
+        <v>2026-07-30T21:48:33.051Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T21:42:58.487Z</v>
+        <v>2026-07-30T21:48:34.051Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T21:42:59.487Z</v>
+        <v>2026-07-30T21:48:35.051Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>0.3</v>
+        <v>1.35</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T21:43:00.487Z</v>
+        <v>2026-07-30T21:48:36.051Z</v>
       </c>
     </row>
     <row r="233">
@@ -4354,10 +4354,10 @@
         <v>Passed</v>
       </c>
       <c r="D233">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T21:43:01.487Z</v>
+        <v>2026-07-30T21:48:37.051Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T21:43:02.487Z</v>
+        <v>2026-07-30T21:48:38.051Z</v>
       </c>
     </row>
     <row r="235">
@@ -4385,13 +4385,13 @@
         <v>Verify APILoad functionality module 234</v>
       </c>
       <c r="C235" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D235">
-        <v>0.91</v>
+        <v>1.41</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T21:43:03.487Z</v>
+        <v>2026-07-30T21:48:39.051Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T21:43:04.487Z</v>
+        <v>2026-07-30T21:48:40.051Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>0.69</v>
+        <v>0.57</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T21:43:05.487Z</v>
+        <v>2026-07-30T21:48:41.051Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T21:43:06.487Z</v>
+        <v>2026-07-30T21:48:42.051Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.58</v>
+        <v>0.43</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T21:43:07.487Z</v>
+        <v>2026-07-30T21:48:43.051Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>1.74</v>
+        <v>0.03</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T21:43:08.487Z</v>
+        <v>2026-07-30T21:48:44.051Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T21:43:09.487Z</v>
+        <v>2026-07-30T21:48:45.051Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>0.05</v>
+        <v>1.64</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T21:43:10.487Z</v>
+        <v>2026-07-30T21:48:46.051Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>0.01</v>
+        <v>1.15</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T21:43:11.487Z</v>
+        <v>2026-07-30T21:48:47.051Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T21:43:12.487Z</v>
+        <v>2026-07-30T21:48:48.051Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>0.88</v>
+        <v>0.3</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T21:43:13.487Z</v>
+        <v>2026-07-30T21:48:49.051Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>0.2</v>
+        <v>1.12</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T21:43:14.487Z</v>
+        <v>2026-07-30T21:48:50.051Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>0.17</v>
+        <v>1.14</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T21:43:15.487Z</v>
+        <v>2026-07-30T21:48:51.051Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>0.38</v>
+        <v>1.78</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T21:43:16.487Z</v>
+        <v>2026-07-30T21:48:52.051Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>1.74</v>
+        <v>0.56</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T21:43:17.487Z</v>
+        <v>2026-07-30T21:48:53.051Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>0.07</v>
+        <v>0.39</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T21:43:18.487Z</v>
+        <v>2026-07-30T21:48:54.051Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T21:43:19.487Z</v>
+        <v>2026-07-30T21:48:55.051Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>0.98</v>
+        <v>0.72</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T21:43:20.487Z</v>
+        <v>2026-07-30T21:48:56.051Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T21:43:21.487Z</v>
+        <v>2026-07-30T21:48:57.051Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>0.49</v>
+        <v>1.49</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T21:43:22.487Z</v>
+        <v>2026-07-30T21:48:58.051Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>0.82</v>
+        <v>1.54</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T21:43:23.487Z</v>
+        <v>2026-07-30T21:48:59.051Z</v>
       </c>
     </row>
     <row r="256">
@@ -4745,10 +4745,10 @@
         <v>Passed</v>
       </c>
       <c r="D256">
-        <v>1.68</v>
+        <v>0.15</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T21:43:24.487Z</v>
+        <v>2026-07-30T21:49:00.051Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T21:43:25.487Z</v>
+        <v>2026-07-30T21:49:01.051Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T21:43:26.487Z</v>
+        <v>2026-07-30T21:49:02.051Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>0.75</v>
+        <v>1.34</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T21:43:27.487Z</v>
+        <v>2026-07-30T21:49:03.051Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T21:43:28.487Z</v>
+        <v>2026-07-30T21:49:04.051Z</v>
       </c>
     </row>
     <row r="261">
@@ -4830,10 +4830,10 @@
         <v>Passed</v>
       </c>
       <c r="D261">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T21:43:29.487Z</v>
+        <v>2026-07-30T21:49:05.051Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>0.34</v>
+        <v>1.35</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T21:43:30.487Z</v>
+        <v>2026-07-30T21:49:06.051Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T21:43:31.487Z</v>
+        <v>2026-07-30T21:49:07.051Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T21:43:32.487Z</v>
+        <v>2026-07-30T21:49:08.051Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T21:43:33.487Z</v>
+        <v>2026-07-30T21:49:09.051Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>1.79</v>
+        <v>0.62</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T21:43:34.487Z</v>
+        <v>2026-07-30T21:49:10.051Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T21:43:35.487Z</v>
+        <v>2026-07-30T21:49:11.051Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>0.11</v>
+        <v>1.59</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T21:43:36.487Z</v>
+        <v>2026-07-30T21:49:12.051Z</v>
       </c>
     </row>
     <row r="269">
@@ -4966,10 +4966,10 @@
         <v>Passed</v>
       </c>
       <c r="D269">
-        <v>0.23</v>
+        <v>0.06</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T21:43:37.487Z</v>
+        <v>2026-07-30T21:49:13.051Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T21:43:38.487Z</v>
+        <v>2026-07-30T21:49:14.051Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>0.47</v>
+        <v>1.56</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T21:43:39.487Z</v>
+        <v>2026-07-30T21:49:15.051Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T21:43:40.487Z</v>
+        <v>2026-07-30T21:49:16.051Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>1.22</v>
+        <v>0.82</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T21:43:41.487Z</v>
+        <v>2026-07-30T21:49:17.051Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>0.97</v>
+        <v>0.7</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T21:43:42.487Z</v>
+        <v>2026-07-30T21:49:18.051Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T21:43:43.487Z</v>
+        <v>2026-07-30T21:49:19.051Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T21:43:44.487Z</v>
+        <v>2026-07-30T21:49:20.051Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>1.73</v>
+        <v>0.64</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T21:43:45.487Z</v>
+        <v>2026-07-30T21:49:21.051Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>0.72</v>
+        <v>1.57</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T21:43:46.487Z</v>
+        <v>2026-07-30T21:49:22.051Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>1.27</v>
+        <v>0.33</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T21:43:47.487Z</v>
+        <v>2026-07-30T21:49:23.051Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>0.63</v>
+        <v>1.1</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T21:43:48.487Z</v>
+        <v>2026-07-30T21:49:24.051Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T21:43:49.487Z</v>
+        <v>2026-07-30T21:49:25.051Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T21:43:50.487Z</v>
+        <v>2026-07-30T21:49:26.051Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T21:43:51.487Z</v>
+        <v>2026-07-30T21:49:27.051Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T21:43:52.487Z</v>
+        <v>2026-07-30T21:49:28.051Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T21:43:53.487Z</v>
+        <v>2026-07-30T21:49:29.051Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.5</v>
+        <v>1.16</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T21:43:54.487Z</v>
+        <v>2026-07-30T21:49:30.051Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>1.67</v>
+        <v>0.69</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T21:43:55.487Z</v>
+        <v>2026-07-30T21:49:31.051Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>0.68</v>
+        <v>1.21</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T21:43:56.487Z</v>
+        <v>2026-07-30T21:49:32.051Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>1.73</v>
+        <v>0.35</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T21:43:57.487Z</v>
+        <v>2026-07-30T21:49:33.051Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T21:43:58.487Z</v>
+        <v>2026-07-30T21:49:34.051Z</v>
       </c>
     </row>
     <row r="291">
@@ -5340,10 +5340,10 @@
         <v>Passed</v>
       </c>
       <c r="D291">
-        <v>0.85</v>
+        <v>1.41</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T21:43:59.487Z</v>
+        <v>2026-07-30T21:49:35.051Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>0.16</v>
+        <v>1.84</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T21:44:00.487Z</v>
+        <v>2026-07-30T21:49:36.051Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T21:44:01.487Z</v>
+        <v>2026-07-30T21:49:37.051Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>0.26</v>
+        <v>0.01</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T21:44:02.487Z</v>
+        <v>2026-07-30T21:49:38.051Z</v>
       </c>
     </row>
     <row r="295">
@@ -5408,10 +5408,10 @@
         <v>Passed</v>
       </c>
       <c r="D295">
-        <v>1.19</v>
+        <v>1.88</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T21:44:03.487Z</v>
+        <v>2026-07-30T21:49:39.051Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T21:44:04.487Z</v>
+        <v>2026-07-30T21:49:40.051Z</v>
       </c>
     </row>
     <row r="297">
@@ -5442,10 +5442,10 @@
         <v>Passed</v>
       </c>
       <c r="D297">
-        <v>1.05</v>
+        <v>0.58</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T21:44:05.487Z</v>
+        <v>2026-07-30T21:49:41.051Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T21:44:06.487Z</v>
+        <v>2026-07-30T21:49:42.051Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T21:44:07.487Z</v>
+        <v>2026-07-30T21:49:43.051Z</v>
       </c>
     </row>
     <row r="300">
@@ -5493,10 +5493,10 @@
         <v>Passed</v>
       </c>
       <c r="D300">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T21:44:08.487Z</v>
+        <v>2026-07-30T21:49:44.051Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T21:44:09.487Z</v>
+        <v>2026-07-30T21:49:45.051Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T21:44:10.487Z</v>
+        <v>2026-07-30T21:49:46.051Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T21:44:11.487Z</v>
+        <v>2026-07-30T21:49:47.051Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T21:44:12.487Z</v>
+        <v>2026-07-30T21:49:48.051Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T21:44:13.487Z</v>
+        <v>2026-07-30T21:49:49.051Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>1.98</v>
+        <v>0.45</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T21:44:14.487Z</v>
+        <v>2026-07-30T21:49:50.051Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T21:44:15.487Z</v>
+        <v>2026-07-30T21:49:51.051Z</v>
       </c>
     </row>
     <row r="308">
@@ -5629,10 +5629,10 @@
         <v>Passed</v>
       </c>
       <c r="D308">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T21:44:16.487Z</v>
+        <v>2026-07-30T21:49:52.051Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>1.17</v>
+        <v>1.77</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T21:44:17.487Z</v>
+        <v>2026-07-30T21:49:53.051Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T21:44:18.487Z</v>
+        <v>2026-07-30T21:49:54.051Z</v>
       </c>
     </row>
     <row r="311">
@@ -5680,10 +5680,10 @@
         <v>Passed</v>
       </c>
       <c r="D311">
-        <v>0.54</v>
+        <v>1.13</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T21:44:19.487Z</v>
+        <v>2026-07-30T21:49:55.051Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T21:44:20.487Z</v>
+        <v>2026-07-30T21:49:56.051Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T21:44:21.487Z</v>
+        <v>2026-07-30T21:49:57.051Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T21:44:22.487Z</v>
+        <v>2026-07-30T21:49:58.051Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T21:44:23.487Z</v>
+        <v>2026-07-30T21:49:59.051Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T21:44:24.487Z</v>
+        <v>2026-07-30T21:50:00.051Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T21:44:25.487Z</v>
+        <v>2026-07-30T21:50:01.051Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>0.78</v>
+        <v>1.57</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T21:44:26.487Z</v>
+        <v>2026-07-30T21:50:02.051Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>0.94</v>
+        <v>1.03</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T21:44:27.487Z</v>
+        <v>2026-07-30T21:50:03.051Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>0.75</v>
+        <v>0.12</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T21:44:28.487Z</v>
+        <v>2026-07-30T21:50:04.051Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>1.29</v>
+        <v>0.12</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T21:44:29.487Z</v>
+        <v>2026-07-30T21:50:05.051Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>1.61</v>
+        <v>0.2</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T21:44:30.487Z</v>
+        <v>2026-07-30T21:50:06.051Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T21:44:31.487Z</v>
+        <v>2026-07-30T21:50:07.051Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>0.81</v>
+        <v>0.58</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T21:44:32.487Z</v>
+        <v>2026-07-30T21:50:08.051Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T21:44:33.487Z</v>
+        <v>2026-07-30T21:50:09.051Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>1.84</v>
+        <v>0.18</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T21:44:34.487Z</v>
+        <v>2026-07-30T21:50:10.051Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>0.76</v>
+        <v>1.34</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T21:44:35.487Z</v>
+        <v>2026-07-30T21:50:11.051Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>0.52</v>
+        <v>1.81</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T21:44:36.487Z</v>
+        <v>2026-07-30T21:50:12.051Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>1.41</v>
+        <v>0.58</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T21:44:37.487Z</v>
+        <v>2026-07-30T21:50:13.051Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T21:44:38.487Z</v>
+        <v>2026-07-30T21:50:14.051Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T21:44:39.487Z</v>
+        <v>2026-07-30T21:50:15.051Z</v>
       </c>
     </row>
     <row r="332">
@@ -6037,10 +6037,10 @@
         <v>Passed</v>
       </c>
       <c r="D332">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T21:44:40.487Z</v>
+        <v>2026-07-30T21:50:16.051Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T21:44:41.487Z</v>
+        <v>2026-07-30T21:50:17.051Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>1.62</v>
+        <v>0.71</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T21:44:42.487Z</v>
+        <v>2026-07-30T21:50:18.051Z</v>
       </c>
     </row>
     <row r="335">
@@ -6085,13 +6085,13 @@
         <v>Verify APILoad functionality module 334</v>
       </c>
       <c r="C335" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D335">
-        <v>0.96</v>
+        <v>0.13</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T21:44:43.487Z</v>
+        <v>2026-07-30T21:50:19.051Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T21:44:44.487Z</v>
+        <v>2026-07-30T21:50:20.051Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>1.33</v>
+        <v>0.18</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T21:44:45.487Z</v>
+        <v>2026-07-30T21:50:21.051Z</v>
       </c>
     </row>
     <row r="338">
@@ -6136,13 +6136,13 @@
         <v>Verify APILoad functionality module 337</v>
       </c>
       <c r="C338" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D338">
-        <v>1.28</v>
+        <v>0.57</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T21:44:46.487Z</v>
+        <v>2026-07-30T21:50:22.051Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>1.06</v>
+        <v>0.34</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T21:44:47.487Z</v>
+        <v>2026-07-30T21:50:23.051Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>0.78</v>
+        <v>1.14</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T21:44:48.487Z</v>
+        <v>2026-07-30T21:50:24.051Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>0.6</v>
+        <v>1.59</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T21:44:49.487Z</v>
+        <v>2026-07-30T21:50:25.051Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>0.45</v>
+        <v>1.01</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T21:44:50.487Z</v>
+        <v>2026-07-30T21:50:26.051Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T21:44:51.487Z</v>
+        <v>2026-07-30T21:50:27.051Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T21:44:52.487Z</v>
+        <v>2026-07-30T21:50:28.051Z</v>
       </c>
     </row>
     <row r="345">
@@ -6258,10 +6258,10 @@
         <v>Passed</v>
       </c>
       <c r="D345">
-        <v>0.01</v>
+        <v>1.42</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T21:44:53.487Z</v>
+        <v>2026-07-30T21:50:29.051Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>1.37</v>
+        <v>1</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T21:44:54.487Z</v>
+        <v>2026-07-30T21:50:30.051Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>0.85</v>
+        <v>1.75</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T21:44:55.487Z</v>
+        <v>2026-07-30T21:50:31.051Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T21:44:56.487Z</v>
+        <v>2026-07-30T21:50:32.051Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T21:44:57.487Z</v>
+        <v>2026-07-30T21:50:33.051Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>1.87</v>
+        <v>0.27</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T21:44:58.487Z</v>
+        <v>2026-07-30T21:50:34.051Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T21:44:59.487Z</v>
+        <v>2026-07-30T21:50:35.051Z</v>
       </c>
     </row>
     <row r="352">
@@ -6377,10 +6377,10 @@
         <v>Passed</v>
       </c>
       <c r="D352">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T21:45:00.487Z</v>
+        <v>2026-07-30T21:50:36.051Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T21:45:01.487Z</v>
+        <v>2026-07-30T21:50:37.051Z</v>
       </c>
     </row>
     <row r="354">
@@ -6411,10 +6411,10 @@
         <v>Passed</v>
       </c>
       <c r="D354">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T21:45:02.487Z</v>
+        <v>2026-07-30T21:50:38.051Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T21:45:03.487Z</v>
+        <v>2026-07-30T21:50:39.051Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T21:45:04.487Z</v>
+        <v>2026-07-30T21:50:40.051Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T21:45:05.487Z</v>
+        <v>2026-07-30T21:50:41.051Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>0.25</v>
+        <v>0.49</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T21:45:06.487Z</v>
+        <v>2026-07-30T21:50:42.051Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T21:45:07.487Z</v>
+        <v>2026-07-30T21:50:43.051Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>0.22</v>
+        <v>1.11</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T21:45:08.487Z</v>
+        <v>2026-07-30T21:50:44.051Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>0.3</v>
+        <v>0.99</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T21:45:09.487Z</v>
+        <v>2026-07-30T21:50:45.051Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>0.37</v>
+        <v>0.28</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T21:45:10.487Z</v>
+        <v>2026-07-30T21:50:46.051Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>1.49</v>
+        <v>0.2</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T21:45:11.487Z</v>
+        <v>2026-07-30T21:50:47.051Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T21:45:12.487Z</v>
+        <v>2026-07-30T21:50:48.051Z</v>
       </c>
     </row>
     <row r="365">
@@ -6598,10 +6598,10 @@
         <v>Passed</v>
       </c>
       <c r="D365">
-        <v>0.65</v>
+        <v>1.91</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T21:45:13.487Z</v>
+        <v>2026-07-30T21:50:49.051Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T21:45:14.487Z</v>
+        <v>2026-07-30T21:50:50.051Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T21:45:15.487Z</v>
+        <v>2026-07-30T21:50:51.051Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>0.05</v>
+        <v>0.65</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T21:45:16.487Z</v>
+        <v>2026-07-30T21:50:52.051Z</v>
       </c>
     </row>
     <row r="369">
@@ -6666,10 +6666,10 @@
         <v>Passed</v>
       </c>
       <c r="D369">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T21:45:17.487Z</v>
+        <v>2026-07-30T21:50:53.051Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>0.2</v>
+        <v>1.36</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T21:45:18.487Z</v>
+        <v>2026-07-30T21:50:54.051Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>0.72</v>
+        <v>0.31</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T21:45:19.487Z</v>
+        <v>2026-07-30T21:50:55.051Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>0.68</v>
+        <v>1.63</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T21:45:20.487Z</v>
+        <v>2026-07-30T21:50:56.051Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T21:45:21.487Z</v>
+        <v>2026-07-30T21:50:57.051Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>1.87</v>
+        <v>0.57</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T21:45:22.487Z</v>
+        <v>2026-07-30T21:50:58.051Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T21:45:23.487Z</v>
+        <v>2026-07-30T21:50:59.051Z</v>
       </c>
     </row>
     <row r="376">
@@ -6785,10 +6785,10 @@
         <v>Passed</v>
       </c>
       <c r="D376">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T21:45:24.487Z</v>
+        <v>2026-07-30T21:51:00.051Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>0.01</v>
+        <v>1.5</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T21:45:25.487Z</v>
+        <v>2026-07-30T21:51:01.051Z</v>
       </c>
     </row>
     <row r="378">
@@ -6819,10 +6819,10 @@
         <v>Passed</v>
       </c>
       <c r="D378">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T21:45:26.487Z</v>
+        <v>2026-07-30T21:51:02.051Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T21:45:27.487Z</v>
+        <v>2026-07-30T21:51:03.051Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T21:45:28.487Z</v>
+        <v>2026-07-30T21:51:04.051Z</v>
       </c>
     </row>
     <row r="381">
@@ -6870,10 +6870,10 @@
         <v>Passed</v>
       </c>
       <c r="D381">
-        <v>1.77</v>
+        <v>0.07</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T21:45:29.487Z</v>
+        <v>2026-07-30T21:51:05.051Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>0.46</v>
+        <v>0.7</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T21:45:30.487Z</v>
+        <v>2026-07-30T21:51:06.051Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T21:45:31.487Z</v>
+        <v>2026-07-30T21:51:07.051Z</v>
       </c>
     </row>
     <row r="384">
@@ -6921,10 +6921,10 @@
         <v>Passed</v>
       </c>
       <c r="D384">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T21:45:32.487Z</v>
+        <v>2026-07-30T21:51:08.051Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T21:45:33.487Z</v>
+        <v>2026-07-30T21:51:09.051Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T21:45:34.487Z</v>
+        <v>2026-07-30T21:51:10.051Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T21:45:35.487Z</v>
+        <v>2026-07-30T21:51:11.051Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T21:45:36.487Z</v>
+        <v>2026-07-30T21:51:12.051Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>0.38</v>
+        <v>1.33</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T21:45:37.487Z</v>
+        <v>2026-07-30T21:51:13.051Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T21:45:38.487Z</v>
+        <v>2026-07-30T21:51:14.051Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T21:45:39.487Z</v>
+        <v>2026-07-30T21:51:15.051Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>1.65</v>
+        <v>0.32</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T21:45:40.487Z</v>
+        <v>2026-07-30T21:51:16.051Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>0.91</v>
+        <v>1.25</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T21:45:41.487Z</v>
+        <v>2026-07-30T21:51:17.051Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T21:45:42.487Z</v>
+        <v>2026-07-30T21:51:18.051Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>1.54</v>
+        <v>0.8</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T21:45:43.487Z</v>
+        <v>2026-07-30T21:51:19.051Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>0.62</v>
+        <v>0.42</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T21:45:44.487Z</v>
+        <v>2026-07-30T21:51:20.051Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>0.13</v>
+        <v>1.05</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T21:45:45.487Z</v>
+        <v>2026-07-30T21:51:21.051Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>0.3</v>
+        <v>0.99</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T21:45:46.487Z</v>
+        <v>2026-07-30T21:51:22.051Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>0.26</v>
+        <v>1.48</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T21:45:47.487Z</v>
+        <v>2026-07-30T21:51:23.051Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T21:45:48.487Z</v>
+        <v>2026-07-30T21:51:24.051Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T21:45:49.487Z</v>
+        <v>2026-07-30T21:51:25.051Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>0.36</v>
+        <v>1.81</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T21:45:50.487Z</v>
+        <v>2026-07-30T21:51:26.051Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>0.93</v>
+        <v>0.25</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T21:45:51.487Z</v>
+        <v>2026-07-30T21:51:27.051Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>0.42</v>
+        <v>1.71</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T21:45:52.487Z</v>
+        <v>2026-07-30T21:51:28.051Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>0.34</v>
+        <v>1.04</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T21:45:53.487Z</v>
+        <v>2026-07-30T21:51:29.051Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T21:45:54.487Z</v>
+        <v>2026-07-30T21:51:30.051Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T21:45:55.487Z</v>
+        <v>2026-07-30T21:51:31.051Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T21:45:56.487Z</v>
+        <v>2026-07-30T21:51:32.051Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>0.96</v>
+        <v>1.4</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T21:45:57.487Z</v>
+        <v>2026-07-30T21:51:33.051Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>1.35</v>
+        <v>0.48</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T21:45:58.487Z</v>
+        <v>2026-07-30T21:51:34.051Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T21:45:59.487Z</v>
+        <v>2026-07-30T21:51:35.051Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>1.98</v>
+        <v>0.41</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T21:46:00.487Z</v>
+        <v>2026-07-30T21:51:36.051Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>0.98</v>
+        <v>0.11</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T21:46:01.487Z</v>
+        <v>2026-07-30T21:51:37.051Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>1.53</v>
+        <v>0.89</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T21:46:02.487Z</v>
+        <v>2026-07-30T21:51:38.051Z</v>
       </c>
     </row>
     <row r="415">
@@ -7448,10 +7448,10 @@
         <v>Passed</v>
       </c>
       <c r="D415">
-        <v>0.57</v>
+        <v>0.97</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T21:46:03.487Z</v>
+        <v>2026-07-30T21:51:39.051Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>0.93</v>
+        <v>0.31</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T21:46:04.487Z</v>
+        <v>2026-07-30T21:51:40.051Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>1.96</v>
+        <v>1.36</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T21:46:05.487Z</v>
+        <v>2026-07-30T21:51:41.051Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T21:46:06.487Z</v>
+        <v>2026-07-30T21:51:42.051Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T21:46:07.487Z</v>
+        <v>2026-07-30T21:51:43.051Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>0.18</v>
+        <v>1.21</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T21:46:08.487Z</v>
+        <v>2026-07-30T21:51:44.051Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>0.97</v>
+        <v>1.78</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T21:46:09.487Z</v>
+        <v>2026-07-30T21:51:45.051Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T21:46:10.487Z</v>
+        <v>2026-07-30T21:51:46.051Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T21:46:11.487Z</v>
+        <v>2026-07-30T21:51:47.051Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>1.7</v>
+        <v>0.81</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T21:46:12.487Z</v>
+        <v>2026-07-30T21:51:48.051Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T21:46:13.487Z</v>
+        <v>2026-07-30T21:51:49.051Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T21:46:14.487Z</v>
+        <v>2026-07-30T21:51:50.051Z</v>
       </c>
     </row>
     <row r="427">
@@ -7652,10 +7652,10 @@
         <v>Passed</v>
       </c>
       <c r="D427">
-        <v>1.09</v>
+        <v>0.69</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T21:46:15.487Z</v>
+        <v>2026-07-30T21:51:51.051Z</v>
       </c>
     </row>
     <row r="428">
@@ -7669,10 +7669,10 @@
         <v>Passed</v>
       </c>
       <c r="D428">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T21:46:16.487Z</v>
+        <v>2026-07-30T21:51:52.051Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>1.98</v>
+        <v>0.72</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T21:46:17.487Z</v>
+        <v>2026-07-30T21:51:53.051Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T21:46:18.487Z</v>
+        <v>2026-07-30T21:51:54.051Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>1.93</v>
+        <v>1.19</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T21:46:19.487Z</v>
+        <v>2026-07-30T21:51:55.051Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>0.31</v>
+        <v>1.25</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T21:46:20.487Z</v>
+        <v>2026-07-30T21:51:56.051Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>1.37</v>
+        <v>1.96</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T21:46:21.487Z</v>
+        <v>2026-07-30T21:51:57.051Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>0.41</v>
+        <v>1.47</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T21:46:22.487Z</v>
+        <v>2026-07-30T21:51:58.051Z</v>
       </c>
     </row>
     <row r="435">
@@ -7788,10 +7788,10 @@
         <v>Passed</v>
       </c>
       <c r="D435">
-        <v>1.3</v>
+        <v>0.62</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T21:46:23.487Z</v>
+        <v>2026-07-30T21:51:59.051Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>0.13</v>
+        <v>0.69</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T21:46:24.487Z</v>
+        <v>2026-07-30T21:52:00.051Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>1.59</v>
+        <v>0.6</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T21:46:25.487Z</v>
+        <v>2026-07-30T21:52:01.051Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>0.41</v>
+        <v>1.16</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T21:46:26.487Z</v>
+        <v>2026-07-30T21:52:02.051Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T21:46:27.487Z</v>
+        <v>2026-07-30T21:52:03.051Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>1.71</v>
+        <v>0.1</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T21:46:28.487Z</v>
+        <v>2026-07-30T21:52:04.051Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T21:46:29.487Z</v>
+        <v>2026-07-30T21:52:05.051Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T21:46:30.487Z</v>
+        <v>2026-07-30T21:52:06.051Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>0.07</v>
+        <v>1.66</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T21:46:31.487Z</v>
+        <v>2026-07-30T21:52:07.051Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>0.06</v>
+        <v>1.63</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T21:46:32.487Z</v>
+        <v>2026-07-30T21:52:08.051Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>0.76</v>
+        <v>1.29</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T21:46:33.487Z</v>
+        <v>2026-07-30T21:52:09.051Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T21:46:34.487Z</v>
+        <v>2026-07-30T21:52:10.051Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T21:46:35.487Z</v>
+        <v>2026-07-30T21:52:11.051Z</v>
       </c>
     </row>
     <row r="448">
@@ -8009,10 +8009,10 @@
         <v>Passed</v>
       </c>
       <c r="D448">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T21:46:36.487Z</v>
+        <v>2026-07-30T21:52:12.051Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T21:46:37.487Z</v>
+        <v>2026-07-30T21:52:13.051Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>1.49</v>
+        <v>0.01</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T21:46:38.487Z</v>
+        <v>2026-07-30T21:52:14.051Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>1.7</v>
+        <v>0.59</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T21:46:39.487Z</v>
+        <v>2026-07-30T21:52:15.051Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T21:46:40.487Z</v>
+        <v>2026-07-30T21:52:16.051Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T21:46:41.487Z</v>
+        <v>2026-07-30T21:52:17.051Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T21:46:42.487Z</v>
+        <v>2026-07-30T21:52:18.051Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>1.96</v>
+        <v>1.12</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T21:46:43.487Z</v>
+        <v>2026-07-30T21:52:19.051Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,10 +8145,10 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T21:46:44.487Z</v>
+        <v>2026-07-30T21:52:20.051Z</v>
       </c>
     </row>
     <row r="457">
@@ -8162,10 +8162,10 @@
         <v>Passed</v>
       </c>
       <c r="D457">
-        <v>1.68</v>
+        <v>0.35</v>
       </c>
       <c r="E457" t="str">
-        <v>2026-07-30T21:46:45.487Z</v>
+        <v>2026-07-30T21:52:21.051Z</v>
       </c>
     </row>
     <row r="458">
@@ -8179,10 +8179,10 @@
         <v>Passed</v>
       </c>
       <c r="D458">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="E458" t="str">
-        <v>2026-07-30T21:46:46.487Z</v>
+        <v>2026-07-30T21:52:22.051Z</v>
       </c>
     </row>
     <row r="459">
@@ -8196,10 +8196,10 @@
         <v>Passed</v>
       </c>
       <c r="D459">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="E459" t="str">
-        <v>2026-07-30T21:46:47.487Z</v>
+        <v>2026-07-30T21:52:23.051Z</v>
       </c>
     </row>
     <row r="460">
@@ -8213,10 +8213,10 @@
         <v>Passed</v>
       </c>
       <c r="D460">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="E460" t="str">
-        <v>2026-07-30T21:46:48.487Z</v>
+        <v>2026-07-30T21:52:24.051Z</v>
       </c>
     </row>
     <row r="461">
@@ -8230,10 +8230,10 @@
         <v>Passed</v>
       </c>
       <c r="D461">
-        <v>1.39</v>
+        <v>0.57</v>
       </c>
       <c r="E461" t="str">
-        <v>2026-07-30T21:46:49.487Z</v>
+        <v>2026-07-30T21:52:25.051Z</v>
       </c>
     </row>
     <row r="462">
@@ -8247,10 +8247,10 @@
         <v>Passed</v>
       </c>
       <c r="D462">
-        <v>1.6</v>
+        <v>0.68</v>
       </c>
       <c r="E462" t="str">
-        <v>2026-07-30T21:46:50.487Z</v>
+        <v>2026-07-30T21:52:26.051Z</v>
       </c>
     </row>
     <row r="463">
@@ -8264,10 +8264,10 @@
         <v>Passed</v>
       </c>
       <c r="D463">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="E463" t="str">
-        <v>2026-07-30T21:46:51.487Z</v>
+        <v>2026-07-30T21:52:27.051Z</v>
       </c>
     </row>
     <row r="464">
@@ -8281,10 +8281,10 @@
         <v>Passed</v>
       </c>
       <c r="D464">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="E464" t="str">
-        <v>2026-07-30T21:46:52.487Z</v>
+        <v>2026-07-30T21:52:28.051Z</v>
       </c>
     </row>
     <row r="465">
@@ -8298,10 +8298,10 @@
         <v>Passed</v>
       </c>
       <c r="D465">
-        <v>0.68</v>
+        <v>1.14</v>
       </c>
       <c r="E465" t="str">
-        <v>2026-07-30T21:46:53.487Z</v>
+        <v>2026-07-30T21:52:29.051Z</v>
       </c>
     </row>
     <row r="466">
@@ -8315,10 +8315,10 @@
         <v>Passed</v>
       </c>
       <c r="D466">
-        <v>1.91</v>
+        <v>0.72</v>
       </c>
       <c r="E466" t="str">
-        <v>2026-07-30T21:46:54.487Z</v>
+        <v>2026-07-30T21:52:30.051Z</v>
       </c>
     </row>
     <row r="467">
@@ -8332,10 +8332,10 @@
         <v>Passed</v>
       </c>
       <c r="D467">
-        <v>0.01</v>
+        <v>0.64</v>
       </c>
       <c r="E467" t="str">
-        <v>2026-07-30T21:46:55.487Z</v>
+        <v>2026-07-30T21:52:31.051Z</v>
       </c>
     </row>
     <row r="468">
@@ -8349,10 +8349,10 @@
         <v>Passed</v>
       </c>
       <c r="D468">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="E468" t="str">
-        <v>2026-07-30T21:46:56.487Z</v>
+        <v>2026-07-30T21:52:32.051Z</v>
       </c>
     </row>
     <row r="469">
@@ -8366,10 +8366,10 @@
         <v>Passed</v>
       </c>
       <c r="D469">
-        <v>1.94</v>
+        <v>0.39</v>
       </c>
       <c r="E469" t="str">
-        <v>2026-07-30T21:46:57.487Z</v>
+        <v>2026-07-30T21:52:33.051Z</v>
       </c>
     </row>
     <row r="470">
@@ -8383,10 +8383,10 @@
         <v>Passed</v>
       </c>
       <c r="D470">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="E470" t="str">
-        <v>2026-07-30T21:46:58.487Z</v>
+        <v>2026-07-30T21:52:34.051Z</v>
       </c>
     </row>
     <row r="471">
@@ -8400,10 +8400,10 @@
         <v>Passed</v>
       </c>
       <c r="D471">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="E471" t="str">
-        <v>2026-07-30T21:46:59.487Z</v>
+        <v>2026-07-30T21:52:35.051Z</v>
       </c>
     </row>
     <row r="472">
@@ -8417,10 +8417,10 @@
         <v>Passed</v>
       </c>
       <c r="D472">
-        <v>0.78</v>
+        <v>0.25</v>
       </c>
       <c r="E472" t="str">
-        <v>2026-07-30T21:47:00.487Z</v>
+        <v>2026-07-30T21:52:36.051Z</v>
       </c>
     </row>
     <row r="473">
@@ -8434,10 +8434,10 @@
         <v>Passed</v>
       </c>
       <c r="D473">
-        <v>1.62</v>
+        <v>0.61</v>
       </c>
       <c r="E473" t="str">
-        <v>2026-07-30T21:47:01.487Z</v>
+        <v>2026-07-30T21:52:37.051Z</v>
       </c>
     </row>
     <row r="474">
@@ -8451,10 +8451,10 @@
         <v>Passed</v>
       </c>
       <c r="D474">
-        <v>1.71</v>
+        <v>0.23</v>
       </c>
       <c r="E474" t="str">
-        <v>2026-07-30T21:47:02.487Z</v>
+        <v>2026-07-30T21:52:38.051Z</v>
       </c>
     </row>
     <row r="475">
@@ -8468,10 +8468,10 @@
         <v>Passed</v>
       </c>
       <c r="D475">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="E475" t="str">
-        <v>2026-07-30T21:47:03.487Z</v>
+        <v>2026-07-30T21:52:39.051Z</v>
       </c>
     </row>
     <row r="476">
@@ -8485,10 +8485,10 @@
         <v>Passed</v>
       </c>
       <c r="D476">
-        <v>0.93</v>
+        <v>0.33</v>
       </c>
       <c r="E476" t="str">
-        <v>2026-07-30T21:47:04.487Z</v>
+        <v>2026-07-30T21:52:40.051Z</v>
       </c>
     </row>
     <row r="477">
@@ -8502,10 +8502,10 @@
         <v>Passed</v>
       </c>
       <c r="D477">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="E477" t="str">
-        <v>2026-07-30T21:47:05.487Z</v>
+        <v>2026-07-30T21:52:41.051Z</v>
       </c>
     </row>
     <row r="478">
@@ -8519,10 +8519,10 @@
         <v>Passed</v>
       </c>
       <c r="D478">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="E478" t="str">
-        <v>2026-07-30T21:47:06.487Z</v>
+        <v>2026-07-30T21:52:42.051Z</v>
       </c>
     </row>
     <row r="479">
@@ -8536,10 +8536,10 @@
         <v>Passed</v>
       </c>
       <c r="D479">
-        <v>0.98</v>
+        <v>0.14</v>
       </c>
       <c r="E479" t="str">
-        <v>2026-07-30T21:47:07.487Z</v>
+        <v>2026-07-30T21:52:43.051Z</v>
       </c>
     </row>
     <row r="480">
@@ -8553,10 +8553,10 @@
         <v>Passed</v>
       </c>
       <c r="D480">
-        <v>0.27</v>
+        <v>1.52</v>
       </c>
       <c r="E480" t="str">
-        <v>2026-07-30T21:47:08.487Z</v>
+        <v>2026-07-30T21:52:44.051Z</v>
       </c>
     </row>
     <row r="481">
@@ -8570,10 +8570,10 @@
         <v>Passed</v>
       </c>
       <c r="D481">
-        <v>0.47</v>
+        <v>1.28</v>
       </c>
       <c r="E481" t="str">
-        <v>2026-07-30T21:47:09.487Z</v>
+        <v>2026-07-30T21:52:45.051Z</v>
       </c>
     </row>
     <row r="482">
@@ -8587,10 +8587,10 @@
         <v>Passed</v>
       </c>
       <c r="D482">
-        <v>0.73</v>
+        <v>0.1</v>
       </c>
       <c r="E482" t="str">
-        <v>2026-07-30T21:47:10.487Z</v>
+        <v>2026-07-30T21:52:46.051Z</v>
       </c>
     </row>
     <row r="483">
@@ -8604,10 +8604,10 @@
         <v>Passed</v>
       </c>
       <c r="D483">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="E483" t="str">
-        <v>2026-07-30T21:47:11.487Z</v>
+        <v>2026-07-30T21:52:47.051Z</v>
       </c>
     </row>
     <row r="484">
@@ -8621,10 +8621,10 @@
         <v>Passed</v>
       </c>
       <c r="D484">
-        <v>1.84</v>
+        <v>0.54</v>
       </c>
       <c r="E484" t="str">
-        <v>2026-07-30T21:47:12.487Z</v>
+        <v>2026-07-30T21:52:48.051Z</v>
       </c>
     </row>
     <row r="485">
@@ -8638,10 +8638,10 @@
         <v>Passed</v>
       </c>
       <c r="D485">
-        <v>0.66</v>
+        <v>0.56</v>
       </c>
       <c r="E485" t="str">
-        <v>2026-07-30T21:47:13.487Z</v>
+        <v>2026-07-30T21:52:49.051Z</v>
       </c>
     </row>
     <row r="486">
@@ -8655,10 +8655,10 @@
         <v>Passed</v>
       </c>
       <c r="D486">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="E486" t="str">
-        <v>2026-07-30T21:47:14.487Z</v>
+        <v>2026-07-30T21:52:50.051Z</v>
       </c>
     </row>
     <row r="487">
@@ -8672,10 +8672,10 @@
         <v>Passed</v>
       </c>
       <c r="D487">
-        <v>0.78</v>
+        <v>1.59</v>
       </c>
       <c r="E487" t="str">
-        <v>2026-07-30T21:47:15.487Z</v>
+        <v>2026-07-30T21:52:51.051Z</v>
       </c>
     </row>
     <row r="488">
@@ -8689,10 +8689,10 @@
         <v>Passed</v>
       </c>
       <c r="D488">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="E488" t="str">
-        <v>2026-07-30T21:47:16.487Z</v>
+        <v>2026-07-30T21:52:52.051Z</v>
       </c>
     </row>
     <row r="489">
@@ -8706,10 +8706,10 @@
         <v>Passed</v>
       </c>
       <c r="D489">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="E489" t="str">
-        <v>2026-07-30T21:47:17.487Z</v>
+        <v>2026-07-30T21:52:53.051Z</v>
       </c>
     </row>
     <row r="490">
@@ -8723,10 +8723,10 @@
         <v>Passed</v>
       </c>
       <c r="D490">
-        <v>0.58</v>
+        <v>1.28</v>
       </c>
       <c r="E490" t="str">
-        <v>2026-07-30T21:47:18.487Z</v>
+        <v>2026-07-30T21:52:54.051Z</v>
       </c>
     </row>
     <row r="491">
@@ -8740,10 +8740,10 @@
         <v>Passed</v>
       </c>
       <c r="D491">
-        <v>0.69</v>
+        <v>1.44</v>
       </c>
       <c r="E491" t="str">
-        <v>2026-07-30T21:47:19.487Z</v>
+        <v>2026-07-30T21:52:55.051Z</v>
       </c>
     </row>
     <row r="492">
@@ -8757,10 +8757,10 @@
         <v>Passed</v>
       </c>
       <c r="D492">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="E492" t="str">
-        <v>2026-07-30T21:47:20.487Z</v>
+        <v>2026-07-30T21:52:56.051Z</v>
       </c>
     </row>
     <row r="493">
@@ -8774,10 +8774,10 @@
         <v>Passed</v>
       </c>
       <c r="D493">
-        <v>1.73</v>
+        <v>0.94</v>
       </c>
       <c r="E493" t="str">
-        <v>2026-07-30T21:47:21.487Z</v>
+        <v>2026-07-30T21:52:57.051Z</v>
       </c>
     </row>
     <row r="494">
@@ -8791,10 +8791,10 @@
         <v>Passed</v>
       </c>
       <c r="D494">
-        <v>0.87</v>
+        <v>1.34</v>
       </c>
       <c r="E494" t="str">
-        <v>2026-07-30T21:47:22.487Z</v>
+        <v>2026-07-30T21:52:58.051Z</v>
       </c>
     </row>
     <row r="495">
@@ -8808,10 +8808,10 @@
         <v>Passed</v>
       </c>
       <c r="D495">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="E495" t="str">
-        <v>2026-07-30T21:47:23.487Z</v>
+        <v>2026-07-30T21:52:59.051Z</v>
       </c>
     </row>
     <row r="496">
@@ -8825,10 +8825,10 @@
         <v>Passed</v>
       </c>
       <c r="D496">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="E496" t="str">
-        <v>2026-07-30T21:47:24.487Z</v>
+        <v>2026-07-30T21:53:00.051Z</v>
       </c>
     </row>
     <row r="497">
@@ -8842,10 +8842,10 @@
         <v>Passed</v>
       </c>
       <c r="D497">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="E497" t="str">
-        <v>2026-07-30T21:47:25.487Z</v>
+        <v>2026-07-30T21:53:01.051Z</v>
       </c>
     </row>
     <row r="498">
@@ -8859,10 +8859,10 @@
         <v>Passed</v>
       </c>
       <c r="D498">
-        <v>0.2</v>
+        <v>1.77</v>
       </c>
       <c r="E498" t="str">
-        <v>2026-07-30T21:47:26.487Z</v>
+        <v>2026-07-30T21:53:02.051Z</v>
       </c>
     </row>
     <row r="499">
@@ -8876,10 +8876,10 @@
         <v>Passed</v>
       </c>
       <c r="D499">
-        <v>0.66</v>
+        <v>1.44</v>
       </c>
       <c r="E499" t="str">
-        <v>2026-07-30T21:47:27.487Z</v>
+        <v>2026-07-30T21:53:03.051Z</v>
       </c>
     </row>
     <row r="500">
@@ -8893,10 +8893,10 @@
         <v>Passed</v>
       </c>
       <c r="D500">
-        <v>0.3</v>
+        <v>1.95</v>
       </c>
       <c r="E500" t="str">
-        <v>2026-07-30T21:47:28.487Z</v>
+        <v>2026-07-30T21:53:04.051Z</v>
       </c>
     </row>
     <row r="501">
@@ -8910,10 +8910,10 @@
         <v>Passed</v>
       </c>
       <c r="D501">
-        <v>1.21</v>
+        <v>0.94</v>
       </c>
       <c r="E501" t="str">
-        <v>2026-07-30T21:47:29.487Z</v>
+        <v>2026-07-30T21:53:05.051Z</v>
       </c>
     </row>
     <row r="502">
@@ -8927,10 +8927,10 @@
         <v>Passed</v>
       </c>
       <c r="D502">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="E502" t="str">
-        <v>2026-07-30T21:47:30.487Z</v>
+        <v>2026-07-30T21:53:06.051Z</v>
       </c>
     </row>
     <row r="503">
@@ -8944,10 +8944,10 @@
         <v>Passed</v>
       </c>
       <c r="D503">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="E503" t="str">
-        <v>2026-07-30T21:47:31.487Z</v>
+        <v>2026-07-30T21:53:07.051Z</v>
       </c>
     </row>
     <row r="504">
@@ -8961,10 +8961,10 @@
         <v>Passed</v>
       </c>
       <c r="D504">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="E504" t="str">
-        <v>2026-07-30T21:47:32.487Z</v>
+        <v>2026-07-30T21:53:08.051Z</v>
       </c>
     </row>
     <row r="505">
@@ -8978,10 +8978,10 @@
         <v>Passed</v>
       </c>
       <c r="D505">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="E505" t="str">
-        <v>2026-07-30T21:47:33.487Z</v>
+        <v>2026-07-30T21:53:09.051Z</v>
       </c>
     </row>
     <row r="506">
@@ -8995,10 +8995,10 @@
         <v>Passed</v>
       </c>
       <c r="D506">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="E506" t="str">
-        <v>2026-07-30T21:47:34.487Z</v>
+        <v>2026-07-30T21:53:10.051Z</v>
       </c>
     </row>
     <row r="507">
@@ -9012,10 +9012,10 @@
         <v>Passed</v>
       </c>
       <c r="D507">
-        <v>0.48</v>
+        <v>0.89</v>
       </c>
       <c r="E507" t="str">
-        <v>2026-07-30T21:47:35.487Z</v>
+        <v>2026-07-30T21:53:11.051Z</v>
       </c>
     </row>
     <row r="508">
@@ -9029,10 +9029,10 @@
         <v>Passed</v>
       </c>
       <c r="D508">
-        <v>1.18</v>
+        <v>0.18</v>
       </c>
       <c r="E508" t="str">
-        <v>2026-07-30T21:47:36.487Z</v>
+        <v>2026-07-30T21:53:12.051Z</v>
       </c>
     </row>
     <row r="509">
@@ -9046,10 +9046,10 @@
         <v>Passed</v>
       </c>
       <c r="D509">
-        <v>1.69</v>
+        <v>0.86</v>
       </c>
       <c r="E509" t="str">
-        <v>2026-07-30T21:47:37.487Z</v>
+        <v>2026-07-30T21:53:13.051Z</v>
       </c>
     </row>
     <row r="510">
@@ -9063,10 +9063,10 @@
         <v>Passed</v>
       </c>
       <c r="D510">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="E510" t="str">
-        <v>2026-07-30T21:47:38.487Z</v>
+        <v>2026-07-30T21:53:14.051Z</v>
       </c>
     </row>
     <row r="511">
@@ -9080,10 +9080,10 @@
         <v>Passed</v>
       </c>
       <c r="D511">
-        <v>0.58</v>
+        <v>1.55</v>
       </c>
       <c r="E511" t="str">
-        <v>2026-07-30T21:47:39.487Z</v>
+        <v>2026-07-30T21:53:15.051Z</v>
       </c>
     </row>
     <row r="512">
@@ -9097,10 +9097,10 @@
         <v>Passed</v>
       </c>
       <c r="D512">
-        <v>0.09</v>
+        <v>1.61</v>
       </c>
       <c r="E512" t="str">
-        <v>2026-07-30T21:47:40.487Z</v>
+        <v>2026-07-30T21:53:16.051Z</v>
       </c>
     </row>
     <row r="513">
@@ -9114,10 +9114,10 @@
         <v>Passed</v>
       </c>
       <c r="D513">
-        <v>1.84</v>
+        <v>0.81</v>
       </c>
       <c r="E513" t="str">
-        <v>2026-07-30T21:47:41.487Z</v>
+        <v>2026-07-30T21:53:17.051Z</v>
       </c>
     </row>
     <row r="514">
@@ -9131,10 +9131,10 @@
         <v>Passed</v>
       </c>
       <c r="D514">
-        <v>0.16</v>
+        <v>0.61</v>
       </c>
       <c r="E514" t="str">
-        <v>2026-07-30T21:47:42.487Z</v>
+        <v>2026-07-30T21:53:18.051Z</v>
       </c>
     </row>
     <row r="515">
@@ -9148,10 +9148,10 @@
         <v>Passed</v>
       </c>
       <c r="D515">
-        <v>0.28</v>
+        <v>1.3</v>
       </c>
       <c r="E515" t="str">
-        <v>2026-07-30T21:47:43.487Z</v>
+        <v>2026-07-30T21:53:19.051Z</v>
       </c>
     </row>
     <row r="516">
@@ -9165,10 +9165,10 @@
         <v>Passed</v>
       </c>
       <c r="D516">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="E516" t="str">
-        <v>2026-07-30T21:47:44.487Z</v>
+        <v>2026-07-30T21:53:20.051Z</v>
       </c>
     </row>
     <row r="517">
@@ -9182,10 +9182,10 @@
         <v>Passed</v>
       </c>
       <c r="D517">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="E517" t="str">
-        <v>2026-07-30T21:47:45.487Z</v>
+        <v>2026-07-30T21:53:21.051Z</v>
       </c>
     </row>
     <row r="518">
@@ -9199,10 +9199,10 @@
         <v>Passed</v>
       </c>
       <c r="D518">
-        <v>0.63</v>
+        <v>1.21</v>
       </c>
       <c r="E518" t="str">
-        <v>2026-07-30T21:47:46.487Z</v>
+        <v>2026-07-30T21:53:22.051Z</v>
       </c>
     </row>
     <row r="519">
@@ -9216,10 +9216,10 @@
         <v>Passed</v>
       </c>
       <c r="D519">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="E519" t="str">
-        <v>2026-07-30T21:47:47.487Z</v>
+        <v>2026-07-30T21:53:23.051Z</v>
       </c>
     </row>
     <row r="520">
@@ -9233,10 +9233,10 @@
         <v>Passed</v>
       </c>
       <c r="D520">
-        <v>0.96</v>
+        <v>1.56</v>
       </c>
       <c r="E520" t="str">
-        <v>2026-07-30T21:47:48.487Z</v>
+        <v>2026-07-30T21:53:24.051Z</v>
       </c>
     </row>
     <row r="521">
@@ -9250,10 +9250,10 @@
         <v>Passed</v>
       </c>
       <c r="D521">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="E521" t="str">
-        <v>2026-07-30T21:47:49.487Z</v>
+        <v>2026-07-30T21:53:25.051Z</v>
       </c>
     </row>
     <row r="522">
@@ -9267,10 +9267,10 @@
         <v>Passed</v>
       </c>
       <c r="D522">
-        <v>1.21</v>
+        <v>0.95</v>
       </c>
       <c r="E522" t="str">
-        <v>2026-07-30T21:47:50.487Z</v>
+        <v>2026-07-30T21:53:26.051Z</v>
       </c>
     </row>
     <row r="523">
@@ -9284,10 +9284,10 @@
         <v>Passed</v>
       </c>
       <c r="D523">
-        <v>1.64</v>
+        <v>0.63</v>
       </c>
       <c r="E523" t="str">
-        <v>2026-07-30T21:47:51.487Z</v>
+        <v>2026-07-30T21:53:27.051Z</v>
       </c>
     </row>
     <row r="524">
@@ -9301,10 +9301,10 @@
         <v>Passed</v>
       </c>
       <c r="D524">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="E524" t="str">
-        <v>2026-07-30T21:47:52.487Z</v>
+        <v>2026-07-30T21:53:28.051Z</v>
       </c>
     </row>
     <row r="525">
@@ -9315,13 +9315,13 @@
         <v>Verify APILoad functionality module 524</v>
       </c>
       <c r="C525" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D525">
-        <v>1.76</v>
+        <v>0.19</v>
       </c>
       <c r="E525" t="str">
-        <v>2026-07-30T21:47:53.487Z</v>
+        <v>2026-07-30T21:53:29.051Z</v>
       </c>
     </row>
     <row r="526">
@@ -9335,10 +9335,10 @@
         <v>Passed</v>
       </c>
       <c r="D526">
-        <v>1.36</v>
+        <v>0.2</v>
       </c>
       <c r="E526" t="str">
-        <v>2026-07-30T21:47:54.487Z</v>
+        <v>2026-07-30T21:53:30.051Z</v>
       </c>
     </row>
     <row r="527">
@@ -9352,10 +9352,10 @@
         <v>Passed</v>
       </c>
       <c r="D527">
-        <v>0.29</v>
+        <v>1.01</v>
       </c>
       <c r="E527" t="str">
-        <v>2026-07-30T21:47:55.487Z</v>
+        <v>2026-07-30T21:53:31.051Z</v>
       </c>
     </row>
     <row r="528">
@@ -9369,10 +9369,10 @@
         <v>Passed</v>
       </c>
       <c r="D528">
-        <v>1.98</v>
+        <v>0.37</v>
       </c>
       <c r="E528" t="str">
-        <v>2026-07-30T21:47:56.487Z</v>
+        <v>2026-07-30T21:53:32.051Z</v>
       </c>
     </row>
     <row r="529">
@@ -9386,10 +9386,10 @@
         <v>Passed</v>
       </c>
       <c r="D529">
-        <v>1.77</v>
+        <v>0.87</v>
       </c>
       <c r="E529" t="str">
-        <v>2026-07-30T21:47:57.487Z</v>
+        <v>2026-07-30T21:53:33.051Z</v>
       </c>
     </row>
     <row r="530">
@@ -9403,10 +9403,10 @@
         <v>Passed</v>
       </c>
       <c r="D530">
-        <v>1.49</v>
+        <v>0.82</v>
       </c>
       <c r="E530" t="str">
-        <v>2026-07-30T21:47:58.487Z</v>
+        <v>2026-07-30T21:53:34.051Z</v>
       </c>
     </row>
     <row r="531">
@@ -9420,10 +9420,10 @@
         <v>Passed</v>
       </c>
       <c r="D531">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="E531" t="str">
-        <v>2026-07-30T21:47:59.487Z</v>
+        <v>2026-07-30T21:53:35.051Z</v>
       </c>
     </row>
     <row r="532">
@@ -9437,10 +9437,10 @@
         <v>Passed</v>
       </c>
       <c r="D532">
-        <v>0.7</v>
+        <v>0.16</v>
       </c>
       <c r="E532" t="str">
-        <v>2026-07-30T21:48:00.487Z</v>
+        <v>2026-07-30T21:53:36.051Z</v>
       </c>
     </row>
     <row r="533">
@@ -9454,10 +9454,10 @@
         <v>Passed</v>
       </c>
       <c r="D533">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="E533" t="str">
-        <v>2026-07-30T21:48:01.487Z</v>
+        <v>2026-07-30T21:53:37.051Z</v>
       </c>
     </row>
     <row r="534">
@@ -9471,10 +9471,10 @@
         <v>Passed</v>
       </c>
       <c r="D534">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="E534" t="str">
-        <v>2026-07-30T21:48:02.487Z</v>
+        <v>2026-07-30T21:53:38.051Z</v>
       </c>
     </row>
     <row r="535">
@@ -9485,13 +9485,13 @@
         <v>Verify APILoad functionality module 534</v>
       </c>
       <c r="C535" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D535">
-        <v>0.69</v>
+        <v>0.78</v>
       </c>
       <c r="E535" t="str">
-        <v>2026-07-30T21:48:03.487Z</v>
+        <v>2026-07-30T21:53:39.051Z</v>
       </c>
     </row>
     <row r="536">
@@ -9505,10 +9505,10 @@
         <v>Passed</v>
       </c>
       <c r="D536">
-        <v>1.58</v>
+        <v>0.8</v>
       </c>
       <c r="E536" t="str">
-        <v>2026-07-30T21:48:04.487Z</v>
+        <v>2026-07-30T21:53:40.051Z</v>
       </c>
     </row>
     <row r="537">
@@ -9522,10 +9522,10 @@
         <v>Passed</v>
       </c>
       <c r="D537">
-        <v>1.69</v>
+        <v>0.92</v>
       </c>
       <c r="E537" t="str">
-        <v>2026-07-30T21:48:05.487Z</v>
+        <v>2026-07-30T21:53:41.051Z</v>
       </c>
     </row>
     <row r="538">
@@ -9539,10 +9539,10 @@
         <v>Passed</v>
       </c>
       <c r="D538">
-        <v>1.58</v>
+        <v>0.79</v>
       </c>
       <c r="E538" t="str">
-        <v>2026-07-30T21:48:06.487Z</v>
+        <v>2026-07-30T21:53:42.051Z</v>
       </c>
     </row>
     <row r="539">
@@ -9556,10 +9556,10 @@
         <v>Passed</v>
       </c>
       <c r="D539">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="E539" t="str">
-        <v>2026-07-30T21:48:07.487Z</v>
+        <v>2026-07-30T21:53:43.051Z</v>
       </c>
     </row>
     <row r="540">
@@ -9573,10 +9573,10 @@
         <v>Passed</v>
       </c>
       <c r="D540">
-        <v>1.17</v>
+        <v>0.19</v>
       </c>
       <c r="E540" t="str">
-        <v>2026-07-30T21:48:08.487Z</v>
+        <v>2026-07-30T21:53:44.051Z</v>
       </c>
     </row>
     <row r="541">
@@ -9590,10 +9590,10 @@
         <v>Passed</v>
       </c>
       <c r="D541">
-        <v>0.05</v>
+        <v>0.66</v>
       </c>
       <c r="E541" t="str">
-        <v>2026-07-30T21:48:09.487Z</v>
+        <v>2026-07-30T21:53:45.051Z</v>
       </c>
     </row>
     <row r="542">
@@ -9607,10 +9607,10 @@
         <v>Passed</v>
       </c>
       <c r="D542">
-        <v>1.55</v>
+        <v>0.37</v>
       </c>
       <c r="E542" t="str">
-        <v>2026-07-30T21:48:10.487Z</v>
+        <v>2026-07-30T21:53:46.051Z</v>
       </c>
     </row>
     <row r="543">
@@ -9624,10 +9624,10 @@
         <v>Passed</v>
       </c>
       <c r="D543">
-        <v>1.65</v>
+        <v>0.72</v>
       </c>
       <c r="E543" t="str">
-        <v>2026-07-30T21:48:11.487Z</v>
+        <v>2026-07-30T21:53:47.051Z</v>
       </c>
     </row>
     <row r="544">
@@ -9641,10 +9641,10 @@
         <v>Passed</v>
       </c>
       <c r="D544">
-        <v>1.75</v>
+        <v>0.73</v>
       </c>
       <c r="E544" t="str">
-        <v>2026-07-30T21:48:12.487Z</v>
+        <v>2026-07-30T21:53:48.051Z</v>
       </c>
     </row>
     <row r="545">
@@ -9658,10 +9658,10 @@
         <v>Passed</v>
       </c>
       <c r="D545">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="E545" t="str">
-        <v>2026-07-30T21:48:13.487Z</v>
+        <v>2026-07-30T21:53:49.051Z</v>
       </c>
     </row>
     <row r="546">
@@ -9675,10 +9675,10 @@
         <v>Passed</v>
       </c>
       <c r="D546">
-        <v>0.65</v>
+        <v>0.83</v>
       </c>
       <c r="E546" t="str">
-        <v>2026-07-30T21:48:14.487Z</v>
+        <v>2026-07-30T21:53:50.051Z</v>
       </c>
     </row>
     <row r="547">
@@ -9692,10 +9692,10 @@
         <v>Passed</v>
       </c>
       <c r="D547">
-        <v>1.22</v>
+        <v>1.97</v>
       </c>
       <c r="E547" t="str">
-        <v>2026-07-30T21:48:15.487Z</v>
+        <v>2026-07-30T21:53:51.051Z</v>
       </c>
     </row>
     <row r="548">
@@ -9709,10 +9709,10 @@
         <v>Passed</v>
       </c>
       <c r="D548">
-        <v>0.15</v>
+        <v>1.87</v>
       </c>
       <c r="E548" t="str">
-        <v>2026-07-30T21:48:16.487Z</v>
+        <v>2026-07-30T21:53:52.051Z</v>
       </c>
     </row>
     <row r="549">
@@ -9726,10 +9726,10 @@
         <v>Passed</v>
       </c>
       <c r="D549">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="E549" t="str">
-        <v>2026-07-30T21:48:17.487Z</v>
+        <v>2026-07-30T21:53:53.051Z</v>
       </c>
     </row>
     <row r="550">
@@ -9743,10 +9743,10 @@
         <v>Passed</v>
       </c>
       <c r="D550">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="E550" t="str">
-        <v>2026-07-30T21:48:18.487Z</v>
+        <v>2026-07-30T21:53:54.051Z</v>
       </c>
     </row>
     <row r="551">
@@ -9760,10 +9760,10 @@
         <v>Passed</v>
       </c>
       <c r="D551">
-        <v>0.07</v>
+        <v>1.93</v>
       </c>
       <c r="E551" t="str">
-        <v>2026-07-30T21:48:19.487Z</v>
+        <v>2026-07-30T21:53:55.051Z</v>
       </c>
     </row>
     <row r="552">
@@ -9777,10 +9777,10 @@
         <v>Passed</v>
       </c>
       <c r="D552">
-        <v>0.05</v>
+        <v>0.54</v>
       </c>
       <c r="E552" t="str">
-        <v>2026-07-30T21:48:20.487Z</v>
+        <v>2026-07-30T21:53:56.051Z</v>
       </c>
     </row>
     <row r="553">
@@ -9794,10 +9794,10 @@
         <v>Passed</v>
       </c>
       <c r="D553">
-        <v>0.97</v>
+        <v>1.66</v>
       </c>
       <c r="E553" t="str">
-        <v>2026-07-30T21:48:21.487Z</v>
+        <v>2026-07-30T21:53:57.051Z</v>
       </c>
     </row>
     <row r="554">
@@ -9811,10 +9811,10 @@
         <v>Passed</v>
       </c>
       <c r="D554">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="E554" t="str">
-        <v>2026-07-30T21:48:22.487Z</v>
+        <v>2026-07-30T21:53:58.051Z</v>
       </c>
     </row>
     <row r="555">
@@ -9828,10 +9828,10 @@
         <v>Passed</v>
       </c>
       <c r="D555">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="E555" t="str">
-        <v>2026-07-30T21:48:23.487Z</v>
+        <v>2026-07-30T21:53:59.051Z</v>
       </c>
     </row>
     <row r="556">
@@ -9845,10 +9845,10 @@
         <v>Passed</v>
       </c>
       <c r="D556">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="E556" t="str">
-        <v>2026-07-30T21:48:24.487Z</v>
+        <v>2026-07-30T21:54:00.051Z</v>
       </c>
     </row>
     <row r="557">
@@ -9862,10 +9862,10 @@
         <v>Passed</v>
       </c>
       <c r="D557">
-        <v>0.87</v>
+        <v>1.59</v>
       </c>
       <c r="E557" t="str">
-        <v>2026-07-30T21:48:25.487Z</v>
+        <v>2026-07-30T21:54:01.051Z</v>
       </c>
     </row>
     <row r="558">
@@ -9879,10 +9879,10 @@
         <v>Passed</v>
       </c>
       <c r="D558">
-        <v>1.29</v>
+        <v>0.73</v>
       </c>
       <c r="E558" t="str">
-        <v>2026-07-30T21:48:26.487Z</v>
+        <v>2026-07-30T21:54:02.051Z</v>
       </c>
     </row>
     <row r="559">
@@ -9896,10 +9896,10 @@
         <v>Passed</v>
       </c>
       <c r="D559">
-        <v>1.49</v>
+        <v>1.13</v>
       </c>
       <c r="E559" t="str">
-        <v>2026-07-30T21:48:27.487Z</v>
+        <v>2026-07-30T21:54:03.051Z</v>
       </c>
     </row>
     <row r="560">
@@ -9910,13 +9910,13 @@
         <v>Verify APILoad functionality module 559</v>
       </c>
       <c r="C560" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D560">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="E560" t="str">
-        <v>2026-07-30T21:48:28.487Z</v>
+        <v>2026-07-30T21:54:04.051Z</v>
       </c>
     </row>
     <row r="561">
@@ -9930,10 +9930,10 @@
         <v>Passed</v>
       </c>
       <c r="D561">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="E561" t="str">
-        <v>2026-07-30T21:48:29.487Z</v>
+        <v>2026-07-30T21:54:05.051Z</v>
       </c>
     </row>
     <row r="562">
@@ -9947,10 +9947,10 @@
         <v>Passed</v>
       </c>
       <c r="D562">
-        <v>0.74</v>
+        <v>1.46</v>
       </c>
       <c r="E562" t="str">
-        <v>2026-07-30T21:48:30.487Z</v>
+        <v>2026-07-30T21:54:06.051Z</v>
       </c>
     </row>
     <row r="563">
@@ -9961,13 +9961,13 @@
         <v>Verify APILoad functionality module 562</v>
       </c>
       <c r="C563" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D563">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="E563" t="str">
-        <v>2026-07-30T21:48:31.487Z</v>
+        <v>2026-07-30T21:54:07.051Z</v>
       </c>
     </row>
     <row r="564">
@@ -9981,10 +9981,10 @@
         <v>Passed</v>
       </c>
       <c r="D564">
-        <v>0.55</v>
+        <v>1.38</v>
       </c>
       <c r="E564" t="str">
-        <v>2026-07-30T21:48:32.487Z</v>
+        <v>2026-07-30T21:54:08.051Z</v>
       </c>
     </row>
     <row r="565">
@@ -9998,10 +9998,10 @@
         <v>Passed</v>
       </c>
       <c r="D565">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="E565" t="str">
-        <v>2026-07-30T21:48:33.487Z</v>
+        <v>2026-07-30T21:54:09.051Z</v>
       </c>
     </row>
     <row r="566">
@@ -10015,10 +10015,10 @@
         <v>Passed</v>
       </c>
       <c r="D566">
-        <v>1.49</v>
+        <v>1.06</v>
       </c>
       <c r="E566" t="str">
-        <v>2026-07-30T21:48:34.487Z</v>
+        <v>2026-07-30T21:54:10.051Z</v>
       </c>
     </row>
     <row r="567">
@@ -10032,10 +10032,10 @@
         <v>Passed</v>
       </c>
       <c r="D567">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="E567" t="str">
-        <v>2026-07-30T21:48:35.487Z</v>
+        <v>2026-07-30T21:54:11.051Z</v>
       </c>
     </row>
     <row r="568">
@@ -10049,10 +10049,10 @@
         <v>Passed</v>
       </c>
       <c r="D568">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="E568" t="str">
-        <v>2026-07-30T21:48:36.487Z</v>
+        <v>2026-07-30T21:54:12.051Z</v>
       </c>
     </row>
     <row r="569">
@@ -10066,10 +10066,10 @@
         <v>Passed</v>
       </c>
       <c r="D569">
-        <v>1.1</v>
+        <v>0.35</v>
       </c>
       <c r="E569" t="str">
-        <v>2026-07-30T21:48:37.487Z</v>
+        <v>2026-07-30T21:54:13.051Z</v>
       </c>
     </row>
     <row r="570">
@@ -10083,10 +10083,10 @@
         <v>Passed</v>
       </c>
       <c r="D570">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="E570" t="str">
-        <v>2026-07-30T21:48:38.487Z</v>
+        <v>2026-07-30T21:54:14.051Z</v>
       </c>
     </row>
     <row r="571">
@@ -10100,10 +10100,10 @@
         <v>Passed</v>
       </c>
       <c r="D571">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="E571" t="str">
-        <v>2026-07-30T21:48:39.487Z</v>
+        <v>2026-07-30T21:54:15.051Z</v>
       </c>
     </row>
     <row r="572">
@@ -10117,10 +10117,10 @@
         <v>Passed</v>
       </c>
       <c r="D572">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="E572" t="str">
-        <v>2026-07-30T21:48:40.487Z</v>
+        <v>2026-07-30T21:54:16.051Z</v>
       </c>
     </row>
     <row r="573">
@@ -10134,10 +10134,10 @@
         <v>Passed</v>
       </c>
       <c r="D573">
-        <v>0.14</v>
+        <v>0.98</v>
       </c>
       <c r="E573" t="str">
-        <v>2026-07-30T21:48:41.487Z</v>
+        <v>2026-07-30T21:54:17.051Z</v>
       </c>
     </row>
     <row r="574">
@@ -10151,10 +10151,10 @@
         <v>Passed</v>
       </c>
       <c r="D574">
-        <v>0.19</v>
+        <v>0.99</v>
       </c>
       <c r="E574" t="str">
-        <v>2026-07-30T21:48:42.487Z</v>
+        <v>2026-07-30T21:54:18.051Z</v>
       </c>
     </row>
     <row r="575">
@@ -10168,10 +10168,10 @@
         <v>Passed</v>
       </c>
       <c r="D575">
-        <v>0.24</v>
+        <v>1.63</v>
       </c>
       <c r="E575" t="str">
-        <v>2026-07-30T21:48:43.487Z</v>
+        <v>2026-07-30T21:54:19.051Z</v>
       </c>
     </row>
     <row r="576">
@@ -10185,10 +10185,10 @@
         <v>Passed</v>
       </c>
       <c r="D576">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="E576" t="str">
-        <v>2026-07-30T21:48:44.487Z</v>
+        <v>2026-07-30T21:54:20.051Z</v>
       </c>
     </row>
     <row r="577">
@@ -10202,10 +10202,10 @@
         <v>Passed</v>
       </c>
       <c r="D577">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="E577" t="str">
-        <v>2026-07-30T21:48:45.487Z</v>
+        <v>2026-07-30T21:54:21.051Z</v>
       </c>
     </row>
     <row r="578">
@@ -10219,10 +10219,10 @@
         <v>Passed</v>
       </c>
       <c r="D578">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E578" t="str">
-        <v>2026-07-30T21:48:46.487Z</v>
+        <v>2026-07-30T21:54:22.051Z</v>
       </c>
     </row>
     <row r="579">
@@ -10236,10 +10236,10 @@
         <v>Passed</v>
       </c>
       <c r="D579">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="E579" t="str">
-        <v>2026-07-30T21:48:47.487Z</v>
+        <v>2026-07-30T21:54:23.051Z</v>
       </c>
     </row>
     <row r="580">
@@ -10253,10 +10253,10 @@
         <v>Passed</v>
       </c>
       <c r="D580">
-        <v>1.69</v>
+        <v>0.09</v>
       </c>
       <c r="E580" t="str">
-        <v>2026-07-30T21:48:48.487Z</v>
+        <v>2026-07-30T21:54:24.051Z</v>
       </c>
     </row>
     <row r="581">
@@ -10270,10 +10270,10 @@
         <v>Passed</v>
       </c>
       <c r="D581">
-        <v>0.46</v>
+        <v>1.93</v>
       </c>
       <c r="E581" t="str">
-        <v>2026-07-30T21:48:49.487Z</v>
+        <v>2026-07-30T21:54:25.051Z</v>
       </c>
     </row>
     <row r="582">
@@ -10287,10 +10287,10 @@
         <v>Passed</v>
       </c>
       <c r="D582">
-        <v>0.6</v>
+        <v>0.02</v>
       </c>
       <c r="E582" t="str">
-        <v>2026-07-30T21:48:50.487Z</v>
+        <v>2026-07-30T21:54:26.051Z</v>
       </c>
     </row>
     <row r="583">
@@ -10304,10 +10304,10 @@
         <v>Passed</v>
       </c>
       <c r="D583">
-        <v>1.58</v>
+        <v>0.51</v>
       </c>
       <c r="E583" t="str">
-        <v>2026-07-30T21:48:51.487Z</v>
+        <v>2026-07-30T21:54:27.051Z</v>
       </c>
     </row>
     <row r="584">
@@ -10321,10 +10321,10 @@
         <v>Passed</v>
       </c>
       <c r="D584">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E584" t="str">
-        <v>2026-07-30T21:48:52.487Z</v>
+        <v>2026-07-30T21:54:28.051Z</v>
       </c>
     </row>
     <row r="585">
@@ -10338,10 +10338,10 @@
         <v>Passed</v>
       </c>
       <c r="D585">
-        <v>1.36</v>
+        <v>0.04</v>
       </c>
       <c r="E585" t="str">
-        <v>2026-07-30T21:48:53.487Z</v>
+        <v>2026-07-30T21:54:29.051Z</v>
       </c>
     </row>
     <row r="586">
@@ -10355,10 +10355,10 @@
         <v>Passed</v>
       </c>
       <c r="D586">
-        <v>0.02</v>
+        <v>0.36</v>
       </c>
       <c r="E586" t="str">
-        <v>2026-07-30T21:48:54.487Z</v>
+        <v>2026-07-30T21:54:30.051Z</v>
       </c>
     </row>
     <row r="587">
@@ -10369,13 +10369,13 @@
         <v>Verify APILoad functionality module 586</v>
       </c>
       <c r="C587" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D587">
-        <v>0.6</v>
+        <v>1.41</v>
       </c>
       <c r="E587" t="str">
-        <v>2026-07-30T21:48:55.487Z</v>
+        <v>2026-07-30T21:54:31.051Z</v>
       </c>
     </row>
     <row r="588">
@@ -10389,10 +10389,10 @@
         <v>Passed</v>
       </c>
       <c r="D588">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="E588" t="str">
-        <v>2026-07-30T21:48:56.487Z</v>
+        <v>2026-07-30T21:54:32.051Z</v>
       </c>
     </row>
     <row r="589">
@@ -10406,10 +10406,10 @@
         <v>Passed</v>
       </c>
       <c r="D589">
-        <v>0.59</v>
+        <v>0.98</v>
       </c>
       <c r="E589" t="str">
-        <v>2026-07-30T21:48:57.487Z</v>
+        <v>2026-07-30T21:54:33.051Z</v>
       </c>
     </row>
     <row r="590">
@@ -10423,10 +10423,10 @@
         <v>Passed</v>
       </c>
       <c r="D590">
-        <v>1.06</v>
+        <v>0.35</v>
       </c>
       <c r="E590" t="str">
-        <v>2026-07-30T21:48:58.487Z</v>
+        <v>2026-07-30T21:54:34.051Z</v>
       </c>
     </row>
     <row r="591">
@@ -10440,10 +10440,10 @@
         <v>Passed</v>
       </c>
       <c r="D591">
-        <v>0.83</v>
+        <v>1.68</v>
       </c>
       <c r="E591" t="str">
-        <v>2026-07-30T21:48:59.487Z</v>
+        <v>2026-07-30T21:54:35.051Z</v>
       </c>
     </row>
     <row r="592">
@@ -10457,10 +10457,10 @@
         <v>Passed</v>
       </c>
       <c r="D592">
-        <v>1.13</v>
+        <v>0.37</v>
       </c>
       <c r="E592" t="str">
-        <v>2026-07-30T21:49:00.487Z</v>
+        <v>2026-07-30T21:54:36.051Z</v>
       </c>
     </row>
     <row r="593">
@@ -10474,10 +10474,10 @@
         <v>Passed</v>
       </c>
       <c r="D593">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
       <c r="E593" t="str">
-        <v>2026-07-30T21:49:01.487Z</v>
+        <v>2026-07-30T21:54:37.051Z</v>
       </c>
     </row>
     <row r="594">
@@ -10491,10 +10491,10 @@
         <v>Passed</v>
       </c>
       <c r="D594">
-        <v>1.15</v>
+        <v>0.89</v>
       </c>
       <c r="E594" t="str">
-        <v>2026-07-30T21:49:02.487Z</v>
+        <v>2026-07-30T21:54:38.051Z</v>
       </c>
     </row>
     <row r="595">
@@ -10508,10 +10508,10 @@
         <v>Passed</v>
       </c>
       <c r="D595">
-        <v>0.92</v>
+        <v>0.06</v>
       </c>
       <c r="E595" t="str">
-        <v>2026-07-30T21:49:03.487Z</v>
+        <v>2026-07-30T21:54:39.051Z</v>
       </c>
     </row>
     <row r="596">
@@ -10525,10 +10525,10 @@
         <v>Passed</v>
       </c>
       <c r="D596">
-        <v>0.06</v>
+        <v>0.65</v>
       </c>
       <c r="E596" t="str">
-        <v>2026-07-30T21:49:04.487Z</v>
+        <v>2026-07-30T21:54:40.051Z</v>
       </c>
     </row>
     <row r="597">
@@ -10542,10 +10542,10 @@
         <v>Passed</v>
       </c>
       <c r="D597">
-        <v>0.09</v>
+        <v>1.32</v>
       </c>
       <c r="E597" t="str">
-        <v>2026-07-30T21:49:05.487Z</v>
+        <v>2026-07-30T21:54:41.051Z</v>
       </c>
     </row>
     <row r="598">
@@ -10559,10 +10559,10 @@
         <v>Passed</v>
       </c>
       <c r="D598">
-        <v>1.69</v>
+        <v>0.44</v>
       </c>
       <c r="E598" t="str">
-        <v>2026-07-30T21:49:06.487Z</v>
+        <v>2026-07-30T21:54:42.051Z</v>
       </c>
     </row>
     <row r="599">
@@ -10576,10 +10576,10 @@
         <v>Passed</v>
       </c>
       <c r="D599">
-        <v>1.7</v>
+        <v>0.39</v>
       </c>
       <c r="E599" t="str">
-        <v>2026-07-30T21:49:07.487Z</v>
+        <v>2026-07-30T21:54:43.051Z</v>
       </c>
     </row>
     <row r="600">
@@ -10593,10 +10593,10 @@
         <v>Passed</v>
       </c>
       <c r="D600">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="E600" t="str">
-        <v>2026-07-30T21:49:08.487Z</v>
+        <v>2026-07-30T21:54:44.051Z</v>
       </c>
     </row>
     <row r="601">
@@ -10610,15 +10610,797 @@
         <v>Passed</v>
       </c>
       <c r="D601">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="E601" t="str">
-        <v>2026-07-30T21:49:09.487Z</v>
+        <v>2026-07-30T21:54:45.051Z</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>APILoad-TC-0601</v>
+      </c>
+      <c r="B602" t="str">
+        <v>Verify APILoad functionality module 601</v>
+      </c>
+      <c r="C602" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D602">
+        <v>0.29</v>
+      </c>
+      <c r="E602" t="str">
+        <v>2026-07-30T21:54:46.051Z</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>APILoad-TC-0602</v>
+      </c>
+      <c r="B603" t="str">
+        <v>Verify APILoad functionality module 602</v>
+      </c>
+      <c r="C603" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D603">
+        <v>0.03</v>
+      </c>
+      <c r="E603" t="str">
+        <v>2026-07-30T21:54:47.051Z</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>APILoad-TC-0603</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Verify APILoad functionality module 603</v>
+      </c>
+      <c r="C604" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D604">
+        <v>0.56</v>
+      </c>
+      <c r="E604" t="str">
+        <v>2026-07-30T21:54:48.051Z</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>APILoad-TC-0604</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Verify APILoad functionality module 604</v>
+      </c>
+      <c r="C605" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D605">
+        <v>0.9</v>
+      </c>
+      <c r="E605" t="str">
+        <v>2026-07-30T21:54:49.051Z</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>APILoad-TC-0605</v>
+      </c>
+      <c r="B606" t="str">
+        <v>Verify APILoad functionality module 605</v>
+      </c>
+      <c r="C606" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D606">
+        <v>0.2</v>
+      </c>
+      <c r="E606" t="str">
+        <v>2026-07-30T21:54:50.051Z</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>APILoad-TC-0606</v>
+      </c>
+      <c r="B607" t="str">
+        <v>Verify APILoad functionality module 606</v>
+      </c>
+      <c r="C607" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D607">
+        <v>0.96</v>
+      </c>
+      <c r="E607" t="str">
+        <v>2026-07-30T21:54:51.051Z</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>APILoad-TC-0607</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Verify APILoad functionality module 607</v>
+      </c>
+      <c r="C608" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D608">
+        <v>0.76</v>
+      </c>
+      <c r="E608" t="str">
+        <v>2026-07-30T21:54:52.051Z</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>APILoad-TC-0608</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Verify APILoad functionality module 608</v>
+      </c>
+      <c r="C609" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D609">
+        <v>1.44</v>
+      </c>
+      <c r="E609" t="str">
+        <v>2026-07-30T21:54:53.051Z</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>APILoad-TC-0609</v>
+      </c>
+      <c r="B610" t="str">
+        <v>Verify APILoad functionality module 609</v>
+      </c>
+      <c r="C610" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D610">
+        <v>1.3</v>
+      </c>
+      <c r="E610" t="str">
+        <v>2026-07-30T21:54:54.051Z</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>APILoad-TC-0610</v>
+      </c>
+      <c r="B611" t="str">
+        <v>Verify APILoad functionality module 610</v>
+      </c>
+      <c r="C611" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D611">
+        <v>1.6</v>
+      </c>
+      <c r="E611" t="str">
+        <v>2026-07-30T21:54:55.051Z</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
+        <v>APILoad-TC-0611</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Verify APILoad functionality module 611</v>
+      </c>
+      <c r="C612" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D612">
+        <v>0.76</v>
+      </c>
+      <c r="E612" t="str">
+        <v>2026-07-30T21:54:56.051Z</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>APILoad-TC-0612</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Verify APILoad functionality module 612</v>
+      </c>
+      <c r="C613" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D613">
+        <v>0.36</v>
+      </c>
+      <c r="E613" t="str">
+        <v>2026-07-30T21:54:57.051Z</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>APILoad-TC-0613</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Verify APILoad functionality module 613</v>
+      </c>
+      <c r="C614" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D614">
+        <v>1.54</v>
+      </c>
+      <c r="E614" t="str">
+        <v>2026-07-30T21:54:58.051Z</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>APILoad-TC-0614</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Verify APILoad functionality module 614</v>
+      </c>
+      <c r="C615" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D615">
+        <v>0.19</v>
+      </c>
+      <c r="E615" t="str">
+        <v>2026-07-30T21:54:59.051Z</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>APILoad-TC-0615</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Verify APILoad functionality module 615</v>
+      </c>
+      <c r="C616" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D616">
+        <v>1.91</v>
+      </c>
+      <c r="E616" t="str">
+        <v>2026-07-30T21:55:00.051Z</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>APILoad-TC-0616</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Verify APILoad functionality module 616</v>
+      </c>
+      <c r="C617" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D617">
+        <v>0.75</v>
+      </c>
+      <c r="E617" t="str">
+        <v>2026-07-30T21:55:01.051Z</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>APILoad-TC-0617</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Verify APILoad functionality module 617</v>
+      </c>
+      <c r="C618" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D618">
+        <v>0.19</v>
+      </c>
+      <c r="E618" t="str">
+        <v>2026-07-30T21:55:02.051Z</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>APILoad-TC-0618</v>
+      </c>
+      <c r="B619" t="str">
+        <v>Verify APILoad functionality module 618</v>
+      </c>
+      <c r="C619" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D619">
+        <v>1.09</v>
+      </c>
+      <c r="E619" t="str">
+        <v>2026-07-30T21:55:03.051Z</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>APILoad-TC-0619</v>
+      </c>
+      <c r="B620" t="str">
+        <v>Verify APILoad functionality module 619</v>
+      </c>
+      <c r="C620" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D620">
+        <v>1.17</v>
+      </c>
+      <c r="E620" t="str">
+        <v>2026-07-30T21:55:04.051Z</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>APILoad-TC-0620</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Verify APILoad functionality module 620</v>
+      </c>
+      <c r="C621" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D621">
+        <v>0.96</v>
+      </c>
+      <c r="E621" t="str">
+        <v>2026-07-30T21:55:05.051Z</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>APILoad-TC-0621</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Verify APILoad functionality module 621</v>
+      </c>
+      <c r="C622" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D622">
+        <v>1.74</v>
+      </c>
+      <c r="E622" t="str">
+        <v>2026-07-30T21:55:06.051Z</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>APILoad-TC-0622</v>
+      </c>
+      <c r="B623" t="str">
+        <v>Verify APILoad functionality module 622</v>
+      </c>
+      <c r="C623" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D623">
+        <v>0.98</v>
+      </c>
+      <c r="E623" t="str">
+        <v>2026-07-30T21:55:07.051Z</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>APILoad-TC-0623</v>
+      </c>
+      <c r="B624" t="str">
+        <v>Verify APILoad functionality module 623</v>
+      </c>
+      <c r="C624" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D624">
+        <v>1.87</v>
+      </c>
+      <c r="E624" t="str">
+        <v>2026-07-30T21:55:08.051Z</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
+        <v>APILoad-TC-0624</v>
+      </c>
+      <c r="B625" t="str">
+        <v>Verify APILoad functionality module 624</v>
+      </c>
+      <c r="C625" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D625">
+        <v>1.97</v>
+      </c>
+      <c r="E625" t="str">
+        <v>2026-07-30T21:55:09.051Z</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>APILoad-TC-0625</v>
+      </c>
+      <c r="B626" t="str">
+        <v>Verify APILoad functionality module 625</v>
+      </c>
+      <c r="C626" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D626">
+        <v>1.82</v>
+      </c>
+      <c r="E626" t="str">
+        <v>2026-07-30T21:55:10.051Z</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
+        <v>APILoad-TC-0626</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Verify APILoad functionality module 626</v>
+      </c>
+      <c r="C627" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D627">
+        <v>1.88</v>
+      </c>
+      <c r="E627" t="str">
+        <v>2026-07-30T21:55:11.051Z</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>APILoad-TC-0627</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Verify APILoad functionality module 627</v>
+      </c>
+      <c r="C628" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D628">
+        <v>1.02</v>
+      </c>
+      <c r="E628" t="str">
+        <v>2026-07-30T21:55:12.051Z</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>APILoad-TC-0628</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Verify APILoad functionality module 628</v>
+      </c>
+      <c r="C629" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D629">
+        <v>1.76</v>
+      </c>
+      <c r="E629" t="str">
+        <v>2026-07-30T21:55:13.051Z</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>APILoad-TC-0629</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Verify APILoad functionality module 629</v>
+      </c>
+      <c r="C630" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D630">
+        <v>1.58</v>
+      </c>
+      <c r="E630" t="str">
+        <v>2026-07-30T21:55:14.051Z</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>APILoad-TC-0630</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Verify APILoad functionality module 630</v>
+      </c>
+      <c r="C631" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D631">
+        <v>0.94</v>
+      </c>
+      <c r="E631" t="str">
+        <v>2026-07-30T21:55:15.051Z</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>APILoad-TC-0631</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Verify APILoad functionality module 631</v>
+      </c>
+      <c r="C632" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D632">
+        <v>0.05</v>
+      </c>
+      <c r="E632" t="str">
+        <v>2026-07-30T21:55:16.051Z</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>APILoad-TC-0632</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Verify APILoad functionality module 632</v>
+      </c>
+      <c r="C633" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D633">
+        <v>0.41</v>
+      </c>
+      <c r="E633" t="str">
+        <v>2026-07-30T21:55:17.051Z</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>APILoad-TC-0633</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Verify APILoad functionality module 633</v>
+      </c>
+      <c r="C634" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D634">
+        <v>0.88</v>
+      </c>
+      <c r="E634" t="str">
+        <v>2026-07-30T21:55:18.051Z</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>APILoad-TC-0634</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Verify APILoad functionality module 634</v>
+      </c>
+      <c r="C635" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D635">
+        <v>1.55</v>
+      </c>
+      <c r="E635" t="str">
+        <v>2026-07-30T21:55:19.051Z</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>APILoad-TC-0635</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Verify APILoad functionality module 635</v>
+      </c>
+      <c r="C636" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D636">
+        <v>1.21</v>
+      </c>
+      <c r="E636" t="str">
+        <v>2026-07-30T21:55:20.051Z</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>APILoad-TC-0636</v>
+      </c>
+      <c r="B637" t="str">
+        <v>Verify APILoad functionality module 636</v>
+      </c>
+      <c r="C637" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D637">
+        <v>1.07</v>
+      </c>
+      <c r="E637" t="str">
+        <v>2026-07-30T21:55:21.051Z</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>APILoad-TC-0637</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Verify APILoad functionality module 637</v>
+      </c>
+      <c r="C638" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D638">
+        <v>0.13</v>
+      </c>
+      <c r="E638" t="str">
+        <v>2026-07-30T21:55:22.051Z</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>APILoad-TC-0638</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Verify APILoad functionality module 638</v>
+      </c>
+      <c r="C639" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D639">
+        <v>0.56</v>
+      </c>
+      <c r="E639" t="str">
+        <v>2026-07-30T21:55:23.051Z</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>APILoad-TC-0639</v>
+      </c>
+      <c r="B640" t="str">
+        <v>Verify APILoad functionality module 639</v>
+      </c>
+      <c r="C640" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D640">
+        <v>0.7</v>
+      </c>
+      <c r="E640" t="str">
+        <v>2026-07-30T21:55:24.051Z</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>APILoad-TC-0640</v>
+      </c>
+      <c r="B641" t="str">
+        <v>Verify APILoad functionality module 640</v>
+      </c>
+      <c r="C641" t="str">
+        <v>Failed</v>
+      </c>
+      <c r="D641">
+        <v>0.86</v>
+      </c>
+      <c r="E641" t="str">
+        <v>2026-07-30T21:55:25.051Z</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>APILoad-TC-0641</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Verify APILoad functionality module 641</v>
+      </c>
+      <c r="C642" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D642">
+        <v>0.64</v>
+      </c>
+      <c r="E642" t="str">
+        <v>2026-07-30T21:55:26.051Z</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>APILoad-TC-0642</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Verify APILoad functionality module 642</v>
+      </c>
+      <c r="C643" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D643">
+        <v>1.22</v>
+      </c>
+      <c r="E643" t="str">
+        <v>2026-07-30T21:55:27.051Z</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>APILoad-TC-0643</v>
+      </c>
+      <c r="B644" t="str">
+        <v>Verify APILoad functionality module 643</v>
+      </c>
+      <c r="C644" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D644">
+        <v>1.04</v>
+      </c>
+      <c r="E644" t="str">
+        <v>2026-07-30T21:55:28.051Z</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>APILoad-TC-0644</v>
+      </c>
+      <c r="B645" t="str">
+        <v>Verify APILoad functionality module 644</v>
+      </c>
+      <c r="C645" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D645">
+        <v>1.31</v>
+      </c>
+      <c r="E645" t="str">
+        <v>2026-07-30T21:55:29.051Z</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>APILoad-TC-0645</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Verify APILoad functionality module 645</v>
+      </c>
+      <c r="C646" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D646">
+        <v>1.56</v>
+      </c>
+      <c r="E646" t="str">
+        <v>2026-07-30T21:55:30.051Z</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>APILoad-TC-0646</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Verify APILoad functionality module 646</v>
+      </c>
+      <c r="C647" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D647">
+        <v>1.77</v>
+      </c>
+      <c r="E647" t="str">
+        <v>2026-07-30T21:55:31.051Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E601"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E647"/>
   </ignoredErrors>
 </worksheet>
 </file>